--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -11440,32 +11440,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129542960</v>
+        <v>129543016</v>
       </c>
       <c r="B102" t="n">
-        <v>80109</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11475,10 +11475,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>458029</v>
+        <v>457699</v>
       </c>
       <c r="R102" t="n">
-        <v>6748413</v>
+        <v>6748197</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11520,12 +11520,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Rikligt på jätteasp</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11552,7 +11547,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543016</v>
+        <v>129543062</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -11587,10 +11582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457699</v>
+        <v>458140</v>
       </c>
       <c r="R103" t="n">
-        <v>6748197</v>
+        <v>6748536</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11622,7 +11617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11632,7 +11627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11659,10 +11654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543062</v>
+        <v>129543083</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11670,21 +11665,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11694,10 +11689,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458140</v>
+        <v>457757</v>
       </c>
       <c r="R104" t="n">
-        <v>6748536</v>
+        <v>6748191</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11729,7 +11724,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11739,7 +11734,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11766,32 +11761,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543083</v>
+        <v>129542960</v>
       </c>
       <c r="B105" t="n">
-        <v>78710</v>
+        <v>80109</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11801,10 +11796,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>457757</v>
+        <v>458029</v>
       </c>
       <c r="R105" t="n">
-        <v>6748191</v>
+        <v>6748413</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11836,7 +11831,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11846,7 +11841,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Rikligt på jätteasp</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,45 +11873,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543095</v>
+        <v>129543111</v>
       </c>
       <c r="B106" t="n">
-        <v>78710</v>
+        <v>5177</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457704</v>
+        <v>457665</v>
       </c>
       <c r="R106" t="n">
-        <v>6748074</v>
+        <v>6748081</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11943,7 +11948,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11953,7 +11958,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11980,50 +11985,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543111</v>
+        <v>129543094</v>
       </c>
       <c r="B107" t="n">
-        <v>5177</v>
+        <v>78710</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457665</v>
+        <v>457728</v>
       </c>
       <c r="R107" t="n">
-        <v>6748081</v>
+        <v>6748093</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12092,32 +12092,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129543094</v>
+        <v>129542981</v>
       </c>
       <c r="B108" t="n">
-        <v>78710</v>
+        <v>91723</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457728</v>
+        <v>457964</v>
       </c>
       <c r="R108" t="n">
-        <v>6748093</v>
+        <v>6748415</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12199,32 +12199,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129542981</v>
+        <v>129543012</v>
       </c>
       <c r="B109" t="n">
-        <v>91723</v>
+        <v>79044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12234,10 +12234,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457964</v>
+        <v>457625</v>
       </c>
       <c r="R109" t="n">
-        <v>6748415</v>
+        <v>6748127</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12306,10 +12306,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543012</v>
+        <v>129543095</v>
       </c>
       <c r="B110" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12317,21 +12317,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12341,10 +12341,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457625</v>
+        <v>457704</v>
       </c>
       <c r="R110" t="n">
-        <v>6748127</v>
+        <v>6748074</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12520,32 +12520,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129542955</v>
+        <v>129542944</v>
       </c>
       <c r="B112" t="n">
-        <v>92192</v>
+        <v>97601</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5454</v>
+        <v>221941</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458015</v>
+        <v>457654</v>
       </c>
       <c r="R112" t="n">
-        <v>6748399</v>
+        <v>6748070</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12627,10 +12627,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129543011</v>
+        <v>129542923</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12638,21 +12638,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12662,10 +12662,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457665</v>
+        <v>457773</v>
       </c>
       <c r="R113" t="n">
-        <v>6748082</v>
+        <v>6748248</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12734,10 +12734,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129542935</v>
+        <v>129542955</v>
       </c>
       <c r="B114" t="n">
-        <v>57724</v>
+        <v>92192</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12745,39 +12745,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>5454</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458060</v>
+        <v>458015</v>
       </c>
       <c r="R114" t="n">
-        <v>6748631</v>
+        <v>6748399</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12809,7 +12804,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12819,7 +12814,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12846,32 +12841,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129542944</v>
+        <v>129543011</v>
       </c>
       <c r="B115" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12881,10 +12876,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457654</v>
+        <v>457665</v>
       </c>
       <c r="R115" t="n">
-        <v>6748070</v>
+        <v>6748082</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12911,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12926,7 +12921,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12953,10 +12948,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129543008</v>
+        <v>129542935</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12964,34 +12959,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457671</v>
+        <v>458060</v>
       </c>
       <c r="R116" t="n">
-        <v>6748048</v>
+        <v>6748631</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13060,10 +13060,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129542923</v>
+        <v>129543008</v>
       </c>
       <c r="B117" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13071,21 +13071,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457773</v>
+        <v>457671</v>
       </c>
       <c r="R117" t="n">
-        <v>6748248</v>
+        <v>6748048</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13279,7 +13279,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129543054</v>
+        <v>129543061</v>
       </c>
       <c r="B119" t="n">
         <v>79044</v>
@@ -13314,10 +13314,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458097</v>
+        <v>458155</v>
       </c>
       <c r="R119" t="n">
-        <v>6748662</v>
+        <v>6748548</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13386,7 +13386,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129543061</v>
+        <v>129543054</v>
       </c>
       <c r="B120" t="n">
         <v>79044</v>
@@ -13421,10 +13421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>458155</v>
+        <v>458097</v>
       </c>
       <c r="R120" t="n">
-        <v>6748548</v>
+        <v>6748662</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14675,10 +14675,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129543040</v>
+        <v>129542916</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14686,21 +14686,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457817</v>
+        <v>457750</v>
       </c>
       <c r="R132" t="n">
-        <v>6748400</v>
+        <v>6748276</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14782,32 +14782,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129543044</v>
+        <v>129542920</v>
       </c>
       <c r="B133" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457939</v>
+        <v>457964</v>
       </c>
       <c r="R133" t="n">
-        <v>6748453</v>
+        <v>6748415</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14889,10 +14889,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129542916</v>
+        <v>129543058</v>
       </c>
       <c r="B134" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14900,21 +14900,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>457750</v>
+        <v>458143</v>
       </c>
       <c r="R134" t="n">
-        <v>6748276</v>
+        <v>6748611</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14996,7 +14996,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129543036</v>
+        <v>129543077</v>
       </c>
       <c r="B135" t="n">
         <v>79044</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457843</v>
+        <v>457938</v>
       </c>
       <c r="R135" t="n">
-        <v>6748341</v>
+        <v>6748409</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15103,32 +15103,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129542920</v>
+        <v>129543040</v>
       </c>
       <c r="B136" t="n">
-        <v>91514</v>
+        <v>79044</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>457964</v>
+        <v>457817</v>
       </c>
       <c r="R136" t="n">
-        <v>6748415</v>
+        <v>6748400</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15210,7 +15210,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129543058</v>
+        <v>129543044</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>458143</v>
+        <v>457939</v>
       </c>
       <c r="R137" t="n">
-        <v>6748611</v>
+        <v>6748453</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15317,7 +15317,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129543077</v>
+        <v>129543050</v>
       </c>
       <c r="B138" t="n">
         <v>79044</v>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>457938</v>
+        <v>458067</v>
       </c>
       <c r="R138" t="n">
-        <v>6748409</v>
+        <v>6748648</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15424,7 +15424,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129543050</v>
+        <v>129543036</v>
       </c>
       <c r="B139" t="n">
         <v>79044</v>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>458067</v>
+        <v>457843</v>
       </c>
       <c r="R139" t="n">
-        <v>6748648</v>
+        <v>6748341</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129542945</v>
+        <v>129543068</v>
       </c>
       <c r="B153" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>457654</v>
+        <v>457935</v>
       </c>
       <c r="R153" t="n">
-        <v>6748079</v>
+        <v>6748390</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17029,7 +17029,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129543068</v>
+        <v>129543067</v>
       </c>
       <c r="B154" t="n">
         <v>79044</v>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457935</v>
+        <v>457946</v>
       </c>
       <c r="R154" t="n">
-        <v>6748390</v>
+        <v>6748380</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17136,32 +17136,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129543067</v>
+        <v>129542980</v>
       </c>
       <c r="B155" t="n">
-        <v>79044</v>
+        <v>91723</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>457946</v>
+        <v>458058</v>
       </c>
       <c r="R155" t="n">
-        <v>6748380</v>
+        <v>6748621</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542980</v>
+        <v>129542959</v>
       </c>
       <c r="B156" t="n">
-        <v>91723</v>
+        <v>81029</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>458058</v>
+        <v>457884</v>
       </c>
       <c r="R156" t="n">
-        <v>6748621</v>
+        <v>6748404</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17350,32 +17350,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129542959</v>
+        <v>129542943</v>
       </c>
       <c r="B157" t="n">
-        <v>81029</v>
+        <v>97595</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1049</v>
+        <v>221945</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457884</v>
+        <v>457999</v>
       </c>
       <c r="R157" t="n">
-        <v>6748404</v>
+        <v>6748381</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17457,32 +17457,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129542943</v>
+        <v>129543033</v>
       </c>
       <c r="B158" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457999</v>
+        <v>457836</v>
       </c>
       <c r="R158" t="n">
-        <v>6748381</v>
+        <v>6748291</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17564,32 +17564,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129543033</v>
+        <v>129542945</v>
       </c>
       <c r="B159" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457836</v>
+        <v>457654</v>
       </c>
       <c r="R159" t="n">
-        <v>6748291</v>
+        <v>6748079</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -996,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129542951</v>
+        <v>129543041</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457817</v>
+        <v>457854</v>
       </c>
       <c r="R5" t="n">
-        <v>6748352</v>
+        <v>6748444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,50 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129542925</v>
+        <v>129543026</v>
       </c>
       <c r="B6" t="n">
-        <v>56917</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457896</v>
+        <v>457758</v>
       </c>
       <c r="R6" t="n">
-        <v>6748335</v>
+        <v>6748263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543041</v>
+        <v>129543056</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457854</v>
+        <v>458120</v>
       </c>
       <c r="R7" t="n">
-        <v>6748444</v>
+        <v>6748624</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,45 +1424,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543026</v>
+        <v>129542925</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457758</v>
+        <v>457896</v>
       </c>
       <c r="R9" t="n">
-        <v>6748263</v>
+        <v>6748335</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,45 +1536,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543056</v>
+        <v>129542951</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458120</v>
+        <v>457817</v>
       </c>
       <c r="R10" t="n">
-        <v>6748624</v>
+        <v>6748352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543043</v>
+        <v>129543081</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457927</v>
+        <v>458131</v>
       </c>
       <c r="R11" t="n">
-        <v>6748447</v>
+        <v>6748547</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129542992</v>
+        <v>129543091</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457763</v>
+        <v>457817</v>
       </c>
       <c r="R12" t="n">
-        <v>6748301</v>
+        <v>6748202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543017</v>
+        <v>129543092</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457657</v>
+        <v>457785</v>
       </c>
       <c r="R13" t="n">
-        <v>6748226</v>
+        <v>6748160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543070</v>
+        <v>129542924</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457936</v>
+        <v>457899</v>
       </c>
       <c r="R14" t="n">
-        <v>6748379</v>
+        <v>6748444</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,32 +2076,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543081</v>
+        <v>129542915</v>
       </c>
       <c r="B15" t="n">
-        <v>91823</v>
+        <v>79663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458131</v>
+        <v>457754</v>
       </c>
       <c r="R15" t="n">
-        <v>6748547</v>
+        <v>6748230</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129542995</v>
+        <v>129543043</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457809</v>
+        <v>457927</v>
       </c>
       <c r="R16" t="n">
-        <v>6748246</v>
+        <v>6748447</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129542915</v>
+        <v>129542992</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457754</v>
+        <v>457763</v>
       </c>
       <c r="R17" t="n">
-        <v>6748230</v>
+        <v>6748301</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543091</v>
+        <v>129543017</v>
       </c>
       <c r="B18" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457817</v>
+        <v>457657</v>
       </c>
       <c r="R18" t="n">
-        <v>6748202</v>
+        <v>6748226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543092</v>
+        <v>129543070</v>
       </c>
       <c r="B19" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457785</v>
+        <v>457936</v>
       </c>
       <c r="R19" t="n">
-        <v>6748160</v>
+        <v>6748379</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129542924</v>
+        <v>129542995</v>
       </c>
       <c r="B20" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457899</v>
+        <v>457809</v>
       </c>
       <c r="R20" t="n">
-        <v>6748444</v>
+        <v>6748246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129542996</v>
+        <v>129543005</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457833</v>
+        <v>457775</v>
       </c>
       <c r="R22" t="n">
-        <v>6748233</v>
+        <v>6748148</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129542913</v>
+        <v>129542982</v>
       </c>
       <c r="B23" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457761</v>
+        <v>457941</v>
       </c>
       <c r="R23" t="n">
-        <v>6748133</v>
+        <v>6748477</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +3017,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543038</v>
+        <v>129543107</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,21 +3060,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457829</v>
+        <v>458144</v>
       </c>
       <c r="R24" t="n">
-        <v>6748366</v>
+        <v>6748538</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543005</v>
+        <v>129542913</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3162,21 +3167,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3186,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457775</v>
+        <v>457761</v>
       </c>
       <c r="R25" t="n">
-        <v>6748148</v>
+        <v>6748133</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543107</v>
+        <v>129542996</v>
       </c>
       <c r="B26" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3269,21 +3274,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458144</v>
+        <v>457833</v>
       </c>
       <c r="R26" t="n">
-        <v>6748538</v>
+        <v>6748233</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3343,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,7 +3370,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543051</v>
+        <v>129543038</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3400,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458077</v>
+        <v>457829</v>
       </c>
       <c r="R27" t="n">
-        <v>6748657</v>
+        <v>6748366</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,7 +3440,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3450,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,7 +3477,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543045</v>
+        <v>129543051</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3507,10 +3512,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457912</v>
+        <v>458077</v>
       </c>
       <c r="R28" t="n">
-        <v>6748485</v>
+        <v>6748657</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,7 +3584,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543032</v>
+        <v>129543045</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3614,10 +3619,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457821</v>
+        <v>457912</v>
       </c>
       <c r="R29" t="n">
-        <v>6748297</v>
+        <v>6748485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,7 +3654,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3664,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,7 +3691,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129542982</v>
+        <v>129543032</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3721,10 +3726,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457941</v>
+        <v>457821</v>
       </c>
       <c r="R30" t="n">
-        <v>6748477</v>
+        <v>6748297</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3756,7 +3761,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,12 +3771,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543018</v>
+        <v>129543090</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457679</v>
+        <v>457883</v>
       </c>
       <c r="R31" t="n">
-        <v>6748231</v>
+        <v>6748264</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3905,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129542966</v>
+        <v>129543018</v>
       </c>
       <c r="B32" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,21 +3916,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457938</v>
+        <v>457679</v>
       </c>
       <c r="R32" t="n">
-        <v>6748466</v>
+        <v>6748231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543063</v>
+        <v>129542966</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458116</v>
+        <v>457938</v>
       </c>
       <c r="R33" t="n">
-        <v>6748548</v>
+        <v>6748466</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,32 +4119,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129542942</v>
+        <v>129543063</v>
       </c>
       <c r="B34" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457951</v>
+        <v>458116</v>
       </c>
       <c r="R34" t="n">
-        <v>6748543</v>
+        <v>6748548</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,10 +4226,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543090</v>
+        <v>129543059</v>
       </c>
       <c r="B35" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457883</v>
+        <v>458174</v>
       </c>
       <c r="R35" t="n">
-        <v>6748264</v>
+        <v>6748599</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543059</v>
+        <v>129543021</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458174</v>
+        <v>457756</v>
       </c>
       <c r="R36" t="n">
-        <v>6748599</v>
+        <v>6748192</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,7 +4440,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129543021</v>
+        <v>129542993</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457756</v>
+        <v>457763</v>
       </c>
       <c r="R37" t="n">
-        <v>6748192</v>
+        <v>6748294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4547,10 +4547,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542949</v>
+        <v>129542942</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>97598</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4558,39 +4558,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457627</v>
+        <v>457951</v>
       </c>
       <c r="R38" t="n">
-        <v>6748161</v>
+        <v>6748543</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4622,7 +4617,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4632,7 +4627,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4659,45 +4654,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129542993</v>
+        <v>129542949</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457763</v>
+        <v>457627</v>
       </c>
       <c r="R39" t="n">
-        <v>6748294</v>
+        <v>6748161</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4980,32 +4980,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129542946</v>
+        <v>129543112</v>
       </c>
       <c r="B42" t="n">
-        <v>91603</v>
+        <v>91610</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>5321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458035</v>
+        <v>458029</v>
       </c>
       <c r="R42" t="n">
-        <v>6748395</v>
+        <v>6748411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5069,6 +5069,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5087,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543071</v>
+        <v>129542946</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5098,21 +5099,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5122,10 +5123,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457928</v>
+        <v>458035</v>
       </c>
       <c r="R43" t="n">
-        <v>6748344</v>
+        <v>6748395</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5157,7 +5158,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5167,7 +5168,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5194,10 +5195,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129542998</v>
+        <v>129542927</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,34 +5206,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457876</v>
+        <v>458027</v>
       </c>
       <c r="R44" t="n">
-        <v>6748240</v>
+        <v>6748413</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5264,7 +5270,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5280,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,32 +5307,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543112</v>
+        <v>129543071</v>
       </c>
       <c r="B45" t="n">
-        <v>91607</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5336,10 +5342,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>458029</v>
+        <v>457928</v>
       </c>
       <c r="R45" t="n">
-        <v>6748411</v>
+        <v>6748344</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5371,7 +5377,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5381,7 +5387,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,7 +5396,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5409,7 +5414,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543003</v>
+        <v>129542998</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5444,10 +5449,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457814</v>
+        <v>457876</v>
       </c>
       <c r="R46" t="n">
-        <v>6748175</v>
+        <v>6748240</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5479,7 +5484,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5489,7 +5494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5516,10 +5521,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129542927</v>
+        <v>129543003</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5527,39 +5532,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458027</v>
+        <v>457814</v>
       </c>
       <c r="R47" t="n">
-        <v>6748413</v>
+        <v>6748175</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6484,50 +6484,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129542950</v>
+        <v>129543042</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457695</v>
+        <v>457922</v>
       </c>
       <c r="R56" t="n">
-        <v>6748215</v>
+        <v>6748447</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6559,7 +6554,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6569,7 +6564,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6596,7 +6591,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543042</v>
+        <v>129543072</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6631,10 +6626,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457922</v>
+        <v>457899</v>
       </c>
       <c r="R57" t="n">
-        <v>6748447</v>
+        <v>6748357</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6666,7 +6661,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6676,7 +6671,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6703,7 +6698,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543072</v>
+        <v>129543035</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6738,10 +6733,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457899</v>
+        <v>457845</v>
       </c>
       <c r="R58" t="n">
-        <v>6748357</v>
+        <v>6748327</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6773,7 +6768,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6783,7 +6778,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6810,7 +6805,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543035</v>
+        <v>129543066</v>
       </c>
       <c r="B59" t="n">
         <v>79044</v>
@@ -6845,10 +6840,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457845</v>
+        <v>458042</v>
       </c>
       <c r="R59" t="n">
-        <v>6748327</v>
+        <v>6748499</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6880,7 +6875,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6890,7 +6885,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6917,45 +6912,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129542914</v>
+        <v>129542950</v>
       </c>
       <c r="B60" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457650</v>
+        <v>457695</v>
       </c>
       <c r="R60" t="n">
-        <v>6748064</v>
+        <v>6748215</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7136,10 +7136,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543066</v>
+        <v>129542914</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7147,21 +7147,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>458042</v>
+        <v>457650</v>
       </c>
       <c r="R62" t="n">
-        <v>6748499</v>
+        <v>6748064</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7671,10 +7671,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543097</v>
+        <v>129543060</v>
       </c>
       <c r="B67" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7682,21 +7682,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457673</v>
+        <v>458177</v>
       </c>
       <c r="R67" t="n">
-        <v>6748071</v>
+        <v>6748587</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7778,7 +7778,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543060</v>
+        <v>129543029</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458177</v>
+        <v>457780</v>
       </c>
       <c r="R68" t="n">
-        <v>6748587</v>
+        <v>6748311</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7885,50 +7885,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129542952</v>
+        <v>129542961</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458156</v>
+        <v>457859</v>
       </c>
       <c r="R69" t="n">
-        <v>6748545</v>
+        <v>6748231</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7960,7 +7955,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7970,7 +7965,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,7 +7992,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543029</v>
+        <v>129543002</v>
       </c>
       <c r="B70" t="n">
         <v>79044</v>
@@ -8032,10 +8027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457780</v>
+        <v>457813</v>
       </c>
       <c r="R70" t="n">
-        <v>6748311</v>
+        <v>6748191</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8067,7 +8062,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8077,7 +8072,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8104,10 +8099,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129542961</v>
+        <v>129543053</v>
       </c>
       <c r="B71" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8115,21 +8110,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8139,10 +8134,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457859</v>
+        <v>458094</v>
       </c>
       <c r="R71" t="n">
-        <v>6748231</v>
+        <v>6748667</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8174,7 +8169,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8184,7 +8179,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8211,45 +8206,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543002</v>
+        <v>129542952</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457813</v>
+        <v>458156</v>
       </c>
       <c r="R72" t="n">
-        <v>6748191</v>
+        <v>6748545</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8318,10 +8318,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543053</v>
+        <v>129543097</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8329,21 +8329,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8353,10 +8353,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458094</v>
+        <v>457673</v>
       </c>
       <c r="R73" t="n">
-        <v>6748667</v>
+        <v>6748071</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8425,10 +8425,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129542997</v>
+        <v>129543101</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8436,21 +8436,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457863</v>
+        <v>457746</v>
       </c>
       <c r="R74" t="n">
-        <v>6748231</v>
+        <v>6748232</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8532,10 +8532,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129542933</v>
+        <v>129543105</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>78710</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8543,39 +8543,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457753</v>
+        <v>457993</v>
       </c>
       <c r="R75" t="n">
-        <v>6748178</v>
+        <v>6748571</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8607,7 +8602,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8617,7 +8612,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8644,7 +8639,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543000</v>
+        <v>129542997</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8679,10 +8674,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457846</v>
+        <v>457863</v>
       </c>
       <c r="R76" t="n">
-        <v>6748214</v>
+        <v>6748231</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8714,7 +8709,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8724,7 +8719,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8751,7 +8746,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129542999</v>
+        <v>129543000</v>
       </c>
       <c r="B77" t="n">
         <v>79044</v>
@@ -8786,10 +8781,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457883</v>
+        <v>457846</v>
       </c>
       <c r="R77" t="n">
-        <v>6748260</v>
+        <v>6748214</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8821,7 +8816,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8831,7 +8826,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8858,7 +8853,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543075</v>
+        <v>129542999</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8893,10 +8888,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457896</v>
+        <v>457883</v>
       </c>
       <c r="R78" t="n">
-        <v>6748336</v>
+        <v>6748260</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8928,7 +8923,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8938,7 +8933,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8965,10 +8960,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543101</v>
+        <v>129543075</v>
       </c>
       <c r="B79" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8976,21 +8971,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9000,10 +8995,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457746</v>
+        <v>457896</v>
       </c>
       <c r="R79" t="n">
-        <v>6748232</v>
+        <v>6748336</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9035,7 +9030,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9045,7 +9040,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9072,10 +9067,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543105</v>
+        <v>129542933</v>
       </c>
       <c r="B80" t="n">
-        <v>78710</v>
+        <v>57724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9083,34 +9078,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457993</v>
+        <v>457753</v>
       </c>
       <c r="R80" t="n">
-        <v>6748571</v>
+        <v>6748178</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9286,10 +9286,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129542991</v>
+        <v>129543088</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457762</v>
+        <v>457797</v>
       </c>
       <c r="R82" t="n">
-        <v>6748312</v>
+        <v>6748261</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9393,10 +9393,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129542964</v>
+        <v>129542991</v>
       </c>
       <c r="B83" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9404,21 +9404,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457767</v>
+        <v>457762</v>
       </c>
       <c r="R83" t="n">
-        <v>6748250</v>
+        <v>6748312</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9500,7 +9500,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129542968</v>
+        <v>129542964</v>
       </c>
       <c r="B84" t="n">
         <v>78801</v>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>458060</v>
+        <v>457767</v>
       </c>
       <c r="R84" t="n">
-        <v>6748629</v>
+        <v>6748250</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9607,10 +9607,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543065</v>
+        <v>129542968</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9618,21 +9618,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458039</v>
+        <v>458060</v>
       </c>
       <c r="R85" t="n">
-        <v>6748504</v>
+        <v>6748629</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9714,10 +9714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543088</v>
+        <v>129543065</v>
       </c>
       <c r="B86" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9725,21 +9725,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457797</v>
+        <v>458039</v>
       </c>
       <c r="R86" t="n">
-        <v>6748261</v>
+        <v>6748504</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9821,32 +9821,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543076</v>
+        <v>129542939</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457917</v>
+        <v>457660</v>
       </c>
       <c r="R87" t="n">
-        <v>6748390</v>
+        <v>6748092</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9928,45 +9928,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543049</v>
+        <v>129542969</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458018</v>
+        <v>457879</v>
       </c>
       <c r="R88" t="n">
-        <v>6748602</v>
+        <v>6748454</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9998,7 +10007,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10008,7 +10017,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10147,54 +10156,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129542969</v>
+        <v>129543076</v>
       </c>
       <c r="B90" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457879</v>
+        <v>457917</v>
       </c>
       <c r="R90" t="n">
-        <v>6748454</v>
+        <v>6748390</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10263,32 +10263,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129542939</v>
+        <v>129543049</v>
       </c>
       <c r="B91" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10298,10 +10298,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457660</v>
+        <v>458018</v>
       </c>
       <c r="R91" t="n">
-        <v>6748092</v>
+        <v>6748602</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10477,7 +10477,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543013</v>
+        <v>129543039</v>
       </c>
       <c r="B93" t="n">
         <v>79044</v>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457621</v>
+        <v>457830</v>
       </c>
       <c r="R93" t="n">
-        <v>6748147</v>
+        <v>6748402</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10584,7 +10584,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543014</v>
+        <v>129543030</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457634</v>
+        <v>457811</v>
       </c>
       <c r="R94" t="n">
-        <v>6748179</v>
+        <v>6748293</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10691,7 +10691,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543037</v>
+        <v>129543016</v>
       </c>
       <c r="B95" t="n">
         <v>79044</v>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457830</v>
+        <v>457699</v>
       </c>
       <c r="R95" t="n">
-        <v>6748350</v>
+        <v>6748197</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10798,7 +10798,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543039</v>
+        <v>129543062</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457830</v>
+        <v>458140</v>
       </c>
       <c r="R96" t="n">
-        <v>6748402</v>
+        <v>6748536</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10905,10 +10905,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543030</v>
+        <v>129543099</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10916,21 +10916,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457811</v>
+        <v>457650</v>
       </c>
       <c r="R97" t="n">
-        <v>6748293</v>
+        <v>6748064</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,7 +11012,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543099</v>
+        <v>129543104</v>
       </c>
       <c r="B98" t="n">
         <v>78710</v>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457650</v>
+        <v>457992</v>
       </c>
       <c r="R98" t="n">
-        <v>6748064</v>
+        <v>6748556</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543104</v>
+        <v>129542956</v>
       </c>
       <c r="B99" t="n">
-        <v>78710</v>
+        <v>81029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11130,21 +11130,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11154,10 +11154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457992</v>
+        <v>457662</v>
       </c>
       <c r="R99" t="n">
-        <v>6748556</v>
+        <v>6748216</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,10 +11226,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543020</v>
+        <v>129543083</v>
       </c>
       <c r="B100" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11237,21 +11237,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457738</v>
+        <v>457757</v>
       </c>
       <c r="R100" t="n">
-        <v>6748205</v>
+        <v>6748191</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,10 +11333,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129542956</v>
+        <v>129543013</v>
       </c>
       <c r="B101" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11344,21 +11344,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11368,10 +11368,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457662</v>
+        <v>457621</v>
       </c>
       <c r="R101" t="n">
-        <v>6748216</v>
+        <v>6748147</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11440,7 +11440,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543016</v>
+        <v>129543014</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11475,10 +11475,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457699</v>
+        <v>457634</v>
       </c>
       <c r="R102" t="n">
-        <v>6748197</v>
+        <v>6748179</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11547,7 +11547,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543062</v>
+        <v>129543037</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -11582,10 +11582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458140</v>
+        <v>457830</v>
       </c>
       <c r="R103" t="n">
-        <v>6748536</v>
+        <v>6748350</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11654,10 +11654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543083</v>
+        <v>129543020</v>
       </c>
       <c r="B104" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11689,10 +11689,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457757</v>
+        <v>457738</v>
       </c>
       <c r="R104" t="n">
-        <v>6748191</v>
+        <v>6748205</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12092,32 +12092,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129542981</v>
+        <v>129543095</v>
       </c>
       <c r="B108" t="n">
-        <v>91723</v>
+        <v>78710</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457964</v>
+        <v>457704</v>
       </c>
       <c r="R108" t="n">
-        <v>6748415</v>
+        <v>6748074</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12199,10 +12199,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543012</v>
+        <v>129543096</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12210,21 +12210,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12234,10 +12234,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457625</v>
+        <v>457671</v>
       </c>
       <c r="R109" t="n">
-        <v>6748127</v>
+        <v>6748048</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12306,10 +12306,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543095</v>
+        <v>129543012</v>
       </c>
       <c r="B110" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12317,21 +12317,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12341,10 +12341,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457704</v>
+        <v>457625</v>
       </c>
       <c r="R110" t="n">
-        <v>6748074</v>
+        <v>6748127</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12413,32 +12413,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543096</v>
+        <v>129542981</v>
       </c>
       <c r="B111" t="n">
-        <v>78710</v>
+        <v>91726</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457671</v>
+        <v>457964</v>
       </c>
       <c r="R111" t="n">
-        <v>6748048</v>
+        <v>6748415</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12523,7 +12523,7 @@
         <v>129542944</v>
       </c>
       <c r="B112" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>129542955</v>
       </c>
       <c r="B114" t="n">
-        <v>92192</v>
+        <v>92195</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12948,10 +12948,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129542935</v>
+        <v>129543008</v>
       </c>
       <c r="B116" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12959,39 +12959,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>458060</v>
+        <v>457671</v>
       </c>
       <c r="R116" t="n">
-        <v>6748631</v>
+        <v>6748048</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13018,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13028,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13060,10 +13055,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129543008</v>
+        <v>129542935</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13071,34 +13066,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457671</v>
+        <v>458060</v>
       </c>
       <c r="R117" t="n">
-        <v>6748048</v>
+        <v>6748631</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13493,10 +13493,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129543046</v>
+        <v>129543102</v>
       </c>
       <c r="B121" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13504,21 +13504,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>457946</v>
+        <v>457761</v>
       </c>
       <c r="R121" t="n">
-        <v>6748493</v>
+        <v>6748256</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13600,10 +13600,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129542967</v>
+        <v>129543046</v>
       </c>
       <c r="B122" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>457939</v>
+        <v>457946</v>
       </c>
       <c r="R122" t="n">
-        <v>6748494</v>
+        <v>6748493</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13707,10 +13707,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129543048</v>
+        <v>129542967</v>
       </c>
       <c r="B123" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13718,21 +13718,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>457954</v>
+        <v>457939</v>
       </c>
       <c r="R123" t="n">
-        <v>6748541</v>
+        <v>6748494</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13814,10 +13814,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129542936</v>
+        <v>129543048</v>
       </c>
       <c r="B124" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13825,39 +13825,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458155</v>
+        <v>457954</v>
       </c>
       <c r="R124" t="n">
-        <v>6748562</v>
+        <v>6748541</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13889,7 +13884,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13899,7 +13894,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14247,32 +14242,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129542940</v>
+        <v>129542978</v>
       </c>
       <c r="B128" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14282,10 +14277,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457879</v>
+        <v>457802</v>
       </c>
       <c r="R128" t="n">
-        <v>6748455</v>
+        <v>6748301</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14317,7 +14312,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14327,7 +14322,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14354,7 +14349,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129542978</v>
+        <v>129543027</v>
       </c>
       <c r="B129" t="n">
         <v>79044</v>
@@ -14389,10 +14384,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>457802</v>
+        <v>457756</v>
       </c>
       <c r="R129" t="n">
-        <v>6748301</v>
+        <v>6748271</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14424,7 +14419,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14434,7 +14429,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14461,10 +14456,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129543102</v>
+        <v>129542936</v>
       </c>
       <c r="B130" t="n">
-        <v>78710</v>
+        <v>57724</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14472,34 +14467,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>457761</v>
+        <v>458155</v>
       </c>
       <c r="R130" t="n">
-        <v>6748256</v>
+        <v>6748562</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14568,32 +14568,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129543027</v>
+        <v>129542940</v>
       </c>
       <c r="B131" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14603,10 +14603,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>457756</v>
+        <v>457879</v>
       </c>
       <c r="R131" t="n">
-        <v>6748271</v>
+        <v>6748455</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14675,32 +14675,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129542916</v>
+        <v>129542920</v>
       </c>
       <c r="B132" t="n">
-        <v>79663</v>
+        <v>91517</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457750</v>
+        <v>457964</v>
       </c>
       <c r="R132" t="n">
-        <v>6748276</v>
+        <v>6748415</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14782,32 +14782,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129542920</v>
+        <v>129542916</v>
       </c>
       <c r="B133" t="n">
-        <v>91514</v>
+        <v>79663</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457964</v>
+        <v>457750</v>
       </c>
       <c r="R133" t="n">
-        <v>6748415</v>
+        <v>6748276</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14889,7 +14889,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129543058</v>
+        <v>129543077</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>458143</v>
+        <v>457938</v>
       </c>
       <c r="R134" t="n">
-        <v>6748611</v>
+        <v>6748409</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14996,7 +14996,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129543077</v>
+        <v>129543040</v>
       </c>
       <c r="B135" t="n">
         <v>79044</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457938</v>
+        <v>457817</v>
       </c>
       <c r="R135" t="n">
-        <v>6748409</v>
+        <v>6748400</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15103,7 +15103,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129543040</v>
+        <v>129543044</v>
       </c>
       <c r="B136" t="n">
         <v>79044</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>457817</v>
+        <v>457939</v>
       </c>
       <c r="R136" t="n">
-        <v>6748400</v>
+        <v>6748453</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15210,7 +15210,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129543044</v>
+        <v>129543050</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>457939</v>
+        <v>458067</v>
       </c>
       <c r="R137" t="n">
-        <v>6748453</v>
+        <v>6748648</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15317,7 +15317,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129543050</v>
+        <v>129543036</v>
       </c>
       <c r="B138" t="n">
         <v>79044</v>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>458067</v>
+        <v>457843</v>
       </c>
       <c r="R138" t="n">
-        <v>6748648</v>
+        <v>6748341</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15424,7 +15424,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129543036</v>
+        <v>129543058</v>
       </c>
       <c r="B139" t="n">
         <v>79044</v>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>457843</v>
+        <v>458143</v>
       </c>
       <c r="R139" t="n">
-        <v>6748341</v>
+        <v>6748611</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15638,10 +15638,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129543089</v>
+        <v>129543074</v>
       </c>
       <c r="B141" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457809</v>
+        <v>457905</v>
       </c>
       <c r="R141" t="n">
-        <v>6748254</v>
+        <v>6748321</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15745,10 +15745,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129543074</v>
+        <v>129542965</v>
       </c>
       <c r="B142" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15756,21 +15756,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457905</v>
+        <v>457760</v>
       </c>
       <c r="R142" t="n">
-        <v>6748321</v>
+        <v>6748255</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15852,10 +15852,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129542965</v>
+        <v>129543022</v>
       </c>
       <c r="B143" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15863,21 +15863,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457760</v>
+        <v>457761</v>
       </c>
       <c r="R143" t="n">
-        <v>6748255</v>
+        <v>6748192</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15959,7 +15959,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129543022</v>
+        <v>129543052</v>
       </c>
       <c r="B144" t="n">
         <v>79044</v>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457761</v>
+        <v>458081</v>
       </c>
       <c r="R144" t="n">
-        <v>6748192</v>
+        <v>6748667</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16066,10 +16066,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129542958</v>
+        <v>129543089</v>
       </c>
       <c r="B145" t="n">
-        <v>81029</v>
+        <v>78710</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16077,21 +16077,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>458029</v>
+        <v>457809</v>
       </c>
       <c r="R145" t="n">
-        <v>6748402</v>
+        <v>6748254</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16173,10 +16173,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129543052</v>
+        <v>129542958</v>
       </c>
       <c r="B146" t="n">
-        <v>79044</v>
+        <v>81029</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16184,21 +16184,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>458081</v>
+        <v>458029</v>
       </c>
       <c r="R146" t="n">
-        <v>6748667</v>
+        <v>6748402</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16280,10 +16280,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129543069</v>
+        <v>129543100</v>
       </c>
       <c r="B147" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16291,21 +16291,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457930</v>
+        <v>457631</v>
       </c>
       <c r="R147" t="n">
-        <v>6748385</v>
+        <v>6748174</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,32 +16387,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129543100</v>
+        <v>129542941</v>
       </c>
       <c r="B148" t="n">
-        <v>78710</v>
+        <v>97598</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457631</v>
+        <v>457929</v>
       </c>
       <c r="R148" t="n">
-        <v>6748174</v>
+        <v>6748448</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16494,32 +16494,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129542941</v>
+        <v>129543069</v>
       </c>
       <c r="B149" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457929</v>
+        <v>457930</v>
       </c>
       <c r="R149" t="n">
-        <v>6748448</v>
+        <v>6748385</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17136,32 +17136,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129542980</v>
+        <v>129543033</v>
       </c>
       <c r="B155" t="n">
-        <v>91723</v>
+        <v>79044</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>458058</v>
+        <v>457836</v>
       </c>
       <c r="R155" t="n">
-        <v>6748621</v>
+        <v>6748291</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542959</v>
+        <v>129542980</v>
       </c>
       <c r="B156" t="n">
-        <v>81029</v>
+        <v>91726</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>457884</v>
+        <v>458058</v>
       </c>
       <c r="R156" t="n">
-        <v>6748404</v>
+        <v>6748621</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17350,32 +17350,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129542943</v>
+        <v>129542959</v>
       </c>
       <c r="B157" t="n">
-        <v>97595</v>
+        <v>81029</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221945</v>
+        <v>1049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457999</v>
+        <v>457884</v>
       </c>
       <c r="R157" t="n">
-        <v>6748381</v>
+        <v>6748404</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17457,32 +17457,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129543033</v>
+        <v>129542945</v>
       </c>
       <c r="B158" t="n">
-        <v>79044</v>
+        <v>97604</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457836</v>
+        <v>457654</v>
       </c>
       <c r="R158" t="n">
-        <v>6748291</v>
+        <v>6748079</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17564,10 +17564,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129542945</v>
+        <v>129542943</v>
       </c>
       <c r="B159" t="n">
-        <v>97601</v>
+        <v>97598</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17575,16 +17575,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457654</v>
+        <v>457999</v>
       </c>
       <c r="R159" t="n">
-        <v>6748079</v>
+        <v>6748381</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129543007</v>
+        <v>129542951</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457677</v>
+        <v>457817</v>
       </c>
       <c r="R2" t="n">
-        <v>6748051</v>
+        <v>6748352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,14 +780,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129543031</v>
+        <v>129543041</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457809</v>
+        <v>457854</v>
       </c>
       <c r="R3" t="n">
-        <v>6748286</v>
+        <v>6748444</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543024</v>
+        <v>129543108</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457755</v>
+        <v>458131</v>
       </c>
       <c r="R4" t="n">
-        <v>6748219</v>
+        <v>6748548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543041</v>
+        <v>129543007</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457854</v>
+        <v>457677</v>
       </c>
       <c r="R5" t="n">
-        <v>6748444</v>
+        <v>6748051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543026</v>
+        <v>129543031</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457758</v>
+        <v>457809</v>
       </c>
       <c r="R6" t="n">
-        <v>6748263</v>
+        <v>6748286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543056</v>
+        <v>129543024</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458120</v>
+        <v>457755</v>
       </c>
       <c r="R7" t="n">
-        <v>6748624</v>
+        <v>6748219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543108</v>
+        <v>129543026</v>
       </c>
       <c r="B8" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458131</v>
+        <v>457758</v>
       </c>
       <c r="R8" t="n">
-        <v>6748548</v>
+        <v>6748263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,50 +1429,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129542925</v>
+        <v>129543056</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457896</v>
+        <v>458120</v>
       </c>
       <c r="R9" t="n">
-        <v>6748335</v>
+        <v>6748624</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129542951</v>
+        <v>129542925</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>56917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,27 +1547,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457817</v>
+        <v>457896</v>
       </c>
       <c r="R10" t="n">
-        <v>6748352</v>
+        <v>6748335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,39 +1641,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543081</v>
+        <v>129542924</v>
       </c>
       <c r="B11" t="n">
-        <v>91826</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458131</v>
+        <v>457899</v>
       </c>
       <c r="R11" t="n">
-        <v>6748547</v>
+        <v>6748444</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129542924</v>
+        <v>129542928</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,34 +1980,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457899</v>
+        <v>457940</v>
       </c>
       <c r="R14" t="n">
-        <v>6748444</v>
+        <v>6748387</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,39 +2074,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129542915</v>
+        <v>129543081</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>91826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457754</v>
+        <v>458131</v>
       </c>
       <c r="R15" t="n">
-        <v>6748230</v>
+        <v>6748547</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2718,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129542928</v>
+        <v>129542915</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>79663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,39 +2734,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457940</v>
+        <v>457754</v>
       </c>
       <c r="R21" t="n">
-        <v>6748387</v>
+        <v>6748230</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543005</v>
+        <v>129543107</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457775</v>
+        <v>458144</v>
       </c>
       <c r="R22" t="n">
-        <v>6748148</v>
+        <v>6748538</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129542982</v>
+        <v>129542996</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457941</v>
+        <v>457833</v>
       </c>
       <c r="R23" t="n">
-        <v>6748477</v>
+        <v>6748233</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,12 +3017,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543107</v>
+        <v>129542913</v>
       </c>
       <c r="B24" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,21 +3055,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458144</v>
+        <v>457761</v>
       </c>
       <c r="R24" t="n">
-        <v>6748538</v>
+        <v>6748133</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,17 +3144,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129542913</v>
+        <v>129543038</v>
       </c>
       <c r="B25" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,21 +3162,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457761</v>
+        <v>457829</v>
       </c>
       <c r="R25" t="n">
-        <v>6748133</v>
+        <v>6748366</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,7 +3258,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129542996</v>
+        <v>129543005</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3298,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457833</v>
+        <v>457775</v>
       </c>
       <c r="R26" t="n">
-        <v>6748233</v>
+        <v>6748148</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3370,7 +3365,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543038</v>
+        <v>129543051</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3405,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457829</v>
+        <v>458077</v>
       </c>
       <c r="R27" t="n">
-        <v>6748366</v>
+        <v>6748657</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3450,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3477,7 +3472,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543051</v>
+        <v>129543045</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3512,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458077</v>
+        <v>457912</v>
       </c>
       <c r="R28" t="n">
-        <v>6748657</v>
+        <v>6748485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3557,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3584,7 +3579,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543045</v>
+        <v>129543032</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3619,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457912</v>
+        <v>457821</v>
       </c>
       <c r="R29" t="n">
-        <v>6748485</v>
+        <v>6748297</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3654,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3664,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3691,7 +3686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543032</v>
+        <v>129542982</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3726,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457821</v>
+        <v>457941</v>
       </c>
       <c r="R30" t="n">
-        <v>6748297</v>
+        <v>6748477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3771,7 +3766,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4759,39 +4759,39 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543098</v>
+        <v>129543112</v>
       </c>
       <c r="B40" t="n">
-        <v>78710</v>
+        <v>91610</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>5321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457657</v>
+        <v>458029</v>
       </c>
       <c r="R40" t="n">
-        <v>6748066</v>
+        <v>6748411</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4855,6 +4855,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4873,10 +4874,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543093</v>
+        <v>129542946</v>
       </c>
       <c r="B41" t="n">
-        <v>78710</v>
+        <v>91606</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4885,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4909,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457737</v>
+        <v>458035</v>
       </c>
       <c r="R41" t="n">
-        <v>6748103</v>
+        <v>6748395</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,7 +4944,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4953,7 +4954,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4973,39 +4974,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543112</v>
+        <v>129543098</v>
       </c>
       <c r="B42" t="n">
-        <v>91610</v>
+        <v>78710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5321</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5016,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458029</v>
+        <v>457657</v>
       </c>
       <c r="R42" t="n">
-        <v>6748411</v>
+        <v>6748066</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5050,7 +5051,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5060,7 +5061,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5069,7 +5070,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129542946</v>
+        <v>129543093</v>
       </c>
       <c r="B43" t="n">
-        <v>91606</v>
+        <v>78710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5099,21 +5099,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>458035</v>
+        <v>457737</v>
       </c>
       <c r="R43" t="n">
-        <v>6748395</v>
+        <v>6748103</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,10 +5195,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129542927</v>
+        <v>129543071</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,39 +5206,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458027</v>
+        <v>457928</v>
       </c>
       <c r="R44" t="n">
-        <v>6748413</v>
+        <v>6748344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5270,7 +5265,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5280,7 +5275,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5307,7 +5302,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543071</v>
+        <v>129542998</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5342,10 +5337,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457928</v>
+        <v>457876</v>
       </c>
       <c r="R45" t="n">
-        <v>6748344</v>
+        <v>6748240</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5377,7 +5372,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5387,7 +5382,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5414,7 +5409,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129542998</v>
+        <v>129543003</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5449,10 +5444,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457876</v>
+        <v>457814</v>
       </c>
       <c r="R46" t="n">
-        <v>6748240</v>
+        <v>6748175</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5484,7 +5479,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5494,7 +5489,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5521,7 +5516,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543003</v>
+        <v>129543057</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5556,10 +5551,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457814</v>
+        <v>458134</v>
       </c>
       <c r="R47" t="n">
-        <v>6748175</v>
+        <v>6748614</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5591,7 +5586,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5601,7 +5596,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543057</v>
+        <v>129542927</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5639,34 +5634,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>458134</v>
+        <v>458027</v>
       </c>
       <c r="R48" t="n">
-        <v>6748614</v>
+        <v>6748413</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5728,17 +5728,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543078</v>
+        <v>129543082</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457875</v>
+        <v>457792</v>
       </c>
       <c r="R49" t="n">
-        <v>6748394</v>
+        <v>6748260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5842,7 +5842,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543010</v>
+        <v>129543078</v>
       </c>
       <c r="B50" t="n">
         <v>79044</v>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457656</v>
+        <v>457875</v>
       </c>
       <c r="R50" t="n">
-        <v>6748084</v>
+        <v>6748394</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5949,7 +5949,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543009</v>
+        <v>129543010</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457654</v>
+        <v>457656</v>
       </c>
       <c r="R51" t="n">
-        <v>6748079</v>
+        <v>6748084</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6056,10 +6056,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543082</v>
+        <v>129543009</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6067,21 +6067,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457792</v>
+        <v>457654</v>
       </c>
       <c r="R52" t="n">
-        <v>6748260</v>
+        <v>6748079</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6484,7 +6484,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543042</v>
+        <v>129543035</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457922</v>
+        <v>457845</v>
       </c>
       <c r="R56" t="n">
-        <v>6748447</v>
+        <v>6748327</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,10 +6591,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543072</v>
+        <v>129542914</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6602,21 +6602,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457899</v>
+        <v>457650</v>
       </c>
       <c r="R57" t="n">
-        <v>6748357</v>
+        <v>6748064</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6691,14 +6691,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543035</v>
+        <v>129543066</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457845</v>
+        <v>458042</v>
       </c>
       <c r="R58" t="n">
-        <v>6748327</v>
+        <v>6748499</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6805,7 +6805,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543066</v>
+        <v>129543042</v>
       </c>
       <c r="B59" t="n">
         <v>79044</v>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458042</v>
+        <v>457922</v>
       </c>
       <c r="R59" t="n">
-        <v>6748499</v>
+        <v>6748447</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,50 +6912,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129542950</v>
+        <v>129543072</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457695</v>
+        <v>457899</v>
       </c>
       <c r="R60" t="n">
-        <v>6748215</v>
+        <v>6748357</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6987,7 +6982,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6997,7 +6992,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7024,7 +7019,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129542948</v>
+        <v>129542950</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -7064,10 +7059,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457777</v>
+        <v>457695</v>
       </c>
       <c r="R61" t="n">
-        <v>6748294</v>
+        <v>6748215</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7099,7 +7094,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7109,7 +7104,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7129,52 +7124,57 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129542914</v>
+        <v>129542948</v>
       </c>
       <c r="B62" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457650</v>
+        <v>457777</v>
       </c>
       <c r="R62" t="n">
-        <v>6748064</v>
+        <v>6748294</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7236,17 +7236,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543073</v>
+        <v>129543097</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457917</v>
+        <v>457673</v>
       </c>
       <c r="R63" t="n">
-        <v>6748303</v>
+        <v>6748071</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7350,10 +7350,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129542962</v>
+        <v>129543002</v>
       </c>
       <c r="B64" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7361,21 +7361,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457762</v>
+        <v>457813</v>
       </c>
       <c r="R64" t="n">
-        <v>6748208</v>
+        <v>6748191</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,7 +7457,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543047</v>
+        <v>129543053</v>
       </c>
       <c r="B65" t="n">
         <v>79044</v>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457952</v>
+        <v>458094</v>
       </c>
       <c r="R65" t="n">
-        <v>6748501</v>
+        <v>6748667</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7564,45 +7564,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543019</v>
+        <v>129542952</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457725</v>
+        <v>458156</v>
       </c>
       <c r="R66" t="n">
-        <v>6748208</v>
+        <v>6748545</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7634,7 +7639,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7644,7 +7649,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7664,14 +7669,14 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543060</v>
+        <v>129543073</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7706,10 +7711,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458177</v>
+        <v>457917</v>
       </c>
       <c r="R67" t="n">
-        <v>6748587</v>
+        <v>6748303</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,7 +7746,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7751,7 +7756,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7778,10 +7783,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543029</v>
+        <v>129542962</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7789,21 +7794,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7813,10 +7818,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457780</v>
+        <v>457762</v>
       </c>
       <c r="R68" t="n">
-        <v>6748311</v>
+        <v>6748208</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7848,7 +7853,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7858,7 +7863,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7878,17 +7883,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129542961</v>
+        <v>129543047</v>
       </c>
       <c r="B69" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7896,21 +7901,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7920,10 +7925,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457859</v>
+        <v>457952</v>
       </c>
       <c r="R69" t="n">
-        <v>6748231</v>
+        <v>6748501</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7955,7 +7960,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7965,7 +7970,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7992,7 +7997,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543002</v>
+        <v>129543019</v>
       </c>
       <c r="B70" t="n">
         <v>79044</v>
@@ -8027,10 +8032,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457813</v>
+        <v>457725</v>
       </c>
       <c r="R70" t="n">
-        <v>6748191</v>
+        <v>6748208</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8062,7 +8067,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8072,7 +8077,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8099,7 +8104,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543053</v>
+        <v>129543060</v>
       </c>
       <c r="B71" t="n">
         <v>79044</v>
@@ -8134,10 +8139,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458094</v>
+        <v>458177</v>
       </c>
       <c r="R71" t="n">
-        <v>6748667</v>
+        <v>6748587</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8169,7 +8174,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8179,7 +8184,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8206,50 +8211,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129542952</v>
+        <v>129543029</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458156</v>
+        <v>457780</v>
       </c>
       <c r="R72" t="n">
-        <v>6748545</v>
+        <v>6748311</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8318,10 +8318,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543097</v>
+        <v>129542961</v>
       </c>
       <c r="B73" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8329,21 +8329,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8353,10 +8353,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457673</v>
+        <v>457859</v>
       </c>
       <c r="R73" t="n">
-        <v>6748071</v>
+        <v>6748231</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129542997</v>
+        <v>129542933</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8650,34 +8650,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457863</v>
+        <v>457753</v>
       </c>
       <c r="R76" t="n">
-        <v>6748231</v>
+        <v>6748178</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,7 +8714,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8719,7 +8724,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8739,14 +8744,14 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543000</v>
+        <v>129542997</v>
       </c>
       <c r="B77" t="n">
         <v>79044</v>
@@ -8781,10 +8786,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457846</v>
+        <v>457863</v>
       </c>
       <c r="R77" t="n">
-        <v>6748214</v>
+        <v>6748231</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8816,7 +8821,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8826,7 +8831,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8853,7 +8858,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129542999</v>
+        <v>129543000</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8888,10 +8893,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457883</v>
+        <v>457846</v>
       </c>
       <c r="R78" t="n">
-        <v>6748260</v>
+        <v>6748214</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,7 +8928,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8933,7 +8938,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8960,7 +8965,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543075</v>
+        <v>129542999</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8995,10 +9000,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457896</v>
+        <v>457883</v>
       </c>
       <c r="R79" t="n">
-        <v>6748336</v>
+        <v>6748260</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,7 +9035,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9040,7 +9045,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9067,10 +9072,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129542933</v>
+        <v>129543075</v>
       </c>
       <c r="B80" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9078,39 +9083,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457753</v>
+        <v>457896</v>
       </c>
       <c r="R80" t="n">
-        <v>6748178</v>
+        <v>6748336</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9821,32 +9821,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129542939</v>
+        <v>129543085</v>
       </c>
       <c r="B87" t="n">
-        <v>97598</v>
+        <v>78710</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457660</v>
+        <v>457880</v>
       </c>
       <c r="R87" t="n">
-        <v>6748092</v>
+        <v>6748247</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9901,7 +9901,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På högstubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9928,54 +9933,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129542969</v>
+        <v>129543076</v>
       </c>
       <c r="B88" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457879</v>
+        <v>457917</v>
       </c>
       <c r="R88" t="n">
-        <v>6748454</v>
+        <v>6748390</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10007,7 +10003,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10017,7 +10013,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10044,10 +10040,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543085</v>
+        <v>129543049</v>
       </c>
       <c r="B89" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10055,21 +10051,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10079,10 +10075,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457880</v>
+        <v>458018</v>
       </c>
       <c r="R89" t="n">
-        <v>6748247</v>
+        <v>6748602</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10114,7 +10110,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10124,12 +10120,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På högstubbe med fem brandljud</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10156,7 +10147,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543076</v>
+        <v>129543028</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -10191,10 +10182,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457917</v>
+        <v>457753</v>
       </c>
       <c r="R90" t="n">
-        <v>6748390</v>
+        <v>6748290</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10226,7 +10217,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10236,7 +10227,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10263,45 +10254,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129543049</v>
+        <v>129542969</v>
       </c>
       <c r="B91" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458018</v>
+        <v>457879</v>
       </c>
       <c r="R91" t="n">
-        <v>6748602</v>
+        <v>6748454</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10363,39 +10363,39 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543028</v>
+        <v>129542939</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457753</v>
+        <v>457660</v>
       </c>
       <c r="R92" t="n">
-        <v>6748290</v>
+        <v>6748092</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10470,39 +10470,39 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543039</v>
+        <v>129542960</v>
       </c>
       <c r="B93" t="n">
-        <v>79044</v>
+        <v>80109</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457830</v>
+        <v>458029</v>
       </c>
       <c r="R93" t="n">
-        <v>6748402</v>
+        <v>6748413</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,7 +10557,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Rikligt på jätteasp</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10577,17 +10582,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543030</v>
+        <v>129542956</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>81029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10595,21 +10600,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10619,10 +10624,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457811</v>
+        <v>457662</v>
       </c>
       <c r="R94" t="n">
-        <v>6748293</v>
+        <v>6748216</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10654,7 +10659,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10664,7 +10669,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10684,17 +10689,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543016</v>
+        <v>129543099</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10702,21 +10707,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10726,10 +10731,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457699</v>
+        <v>457650</v>
       </c>
       <c r="R95" t="n">
-        <v>6748197</v>
+        <v>6748064</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10761,7 +10766,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10771,7 +10776,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10798,10 +10803,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543062</v>
+        <v>129543104</v>
       </c>
       <c r="B96" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10809,21 +10814,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10833,10 +10838,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>458140</v>
+        <v>457992</v>
       </c>
       <c r="R96" t="n">
-        <v>6748536</v>
+        <v>6748556</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10868,7 +10873,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10878,7 +10883,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10905,7 +10910,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543099</v>
+        <v>129543083</v>
       </c>
       <c r="B97" t="n">
         <v>78710</v>
@@ -10940,10 +10945,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457650</v>
+        <v>457757</v>
       </c>
       <c r="R97" t="n">
-        <v>6748064</v>
+        <v>6748191</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10975,7 +10980,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10990,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,10 +11017,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543104</v>
+        <v>129543013</v>
       </c>
       <c r="B98" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11023,21 +11028,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11047,10 +11052,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457992</v>
+        <v>457621</v>
       </c>
       <c r="R98" t="n">
-        <v>6748556</v>
+        <v>6748147</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,7 +11087,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11097,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11124,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129542956</v>
+        <v>129543014</v>
       </c>
       <c r="B99" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11130,21 +11135,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11154,10 +11159,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457662</v>
+        <v>457634</v>
       </c>
       <c r="R99" t="n">
-        <v>6748216</v>
+        <v>6748179</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,7 +11194,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11199,7 +11204,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,10 +11231,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543083</v>
+        <v>129543037</v>
       </c>
       <c r="B100" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11237,21 +11242,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11261,10 +11266,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457757</v>
+        <v>457830</v>
       </c>
       <c r="R100" t="n">
-        <v>6748191</v>
+        <v>6748350</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11296,7 +11301,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11306,7 +11311,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,7 +11338,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543013</v>
+        <v>129543039</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -11368,10 +11373,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457621</v>
+        <v>457830</v>
       </c>
       <c r="R101" t="n">
-        <v>6748147</v>
+        <v>6748402</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,7 +11408,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11413,7 +11418,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11440,7 +11445,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543014</v>
+        <v>129543030</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11475,10 +11480,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457634</v>
+        <v>457811</v>
       </c>
       <c r="R102" t="n">
-        <v>6748179</v>
+        <v>6748293</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,7 +11515,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11520,7 +11525,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11547,7 +11552,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543037</v>
+        <v>129543020</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -11582,10 +11587,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457830</v>
+        <v>457738</v>
       </c>
       <c r="R103" t="n">
-        <v>6748350</v>
+        <v>6748205</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,7 +11622,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11627,7 +11632,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11654,7 +11659,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543020</v>
+        <v>129543016</v>
       </c>
       <c r="B104" t="n">
         <v>79044</v>
@@ -11689,10 +11694,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457738</v>
+        <v>457699</v>
       </c>
       <c r="R104" t="n">
-        <v>6748205</v>
+        <v>6748197</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11724,7 +11729,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11734,7 +11739,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11761,32 +11766,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129542960</v>
+        <v>129543062</v>
       </c>
       <c r="B105" t="n">
-        <v>80109</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11796,10 +11801,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458029</v>
+        <v>458140</v>
       </c>
       <c r="R105" t="n">
-        <v>6748413</v>
+        <v>6748536</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11831,7 +11836,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11841,12 +11846,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Rikligt på jätteasp</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,50 +11873,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543111</v>
+        <v>129542981</v>
       </c>
       <c r="B106" t="n">
-        <v>5177</v>
+        <v>91726</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100526</v>
+        <v>1503</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457665</v>
+        <v>457964</v>
       </c>
       <c r="R106" t="n">
-        <v>6748081</v>
+        <v>6748415</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11948,7 +11943,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11958,7 +11953,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11978,7 +11973,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12306,45 +12301,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543012</v>
+        <v>129543111</v>
       </c>
       <c r="B110" t="n">
-        <v>79044</v>
+        <v>5177</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457625</v>
+        <v>457665</v>
       </c>
       <c r="R110" t="n">
-        <v>6748127</v>
+        <v>6748081</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12413,32 +12413,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129542981</v>
+        <v>129543012</v>
       </c>
       <c r="B111" t="n">
-        <v>91726</v>
+        <v>79044</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457964</v>
+        <v>457625</v>
       </c>
       <c r="R111" t="n">
-        <v>6748415</v>
+        <v>6748127</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12520,32 +12520,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129542944</v>
+        <v>129542923</v>
       </c>
       <c r="B112" t="n">
-        <v>97604</v>
+        <v>79139</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>967</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>457654</v>
+        <v>457773</v>
       </c>
       <c r="R112" t="n">
-        <v>6748070</v>
+        <v>6748248</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12620,17 +12620,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129542923</v>
+        <v>129542955</v>
       </c>
       <c r="B113" t="n">
-        <v>79139</v>
+        <v>92195</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12638,21 +12638,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>967</v>
+        <v>5454</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12662,10 +12662,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457773</v>
+        <v>458015</v>
       </c>
       <c r="R113" t="n">
-        <v>6748248</v>
+        <v>6748399</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12727,39 +12727,39 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129542955</v>
+        <v>129542944</v>
       </c>
       <c r="B114" t="n">
-        <v>92195</v>
+        <v>97604</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5454</v>
+        <v>221941</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12769,10 +12769,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458015</v>
+        <v>457654</v>
       </c>
       <c r="R114" t="n">
-        <v>6748399</v>
+        <v>6748070</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12834,17 +12834,17 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129543011</v>
+        <v>129542935</v>
       </c>
       <c r="B115" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12852,34 +12852,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457665</v>
+        <v>458060</v>
       </c>
       <c r="R115" t="n">
-        <v>6748082</v>
+        <v>6748631</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12911,7 +12916,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12921,7 +12926,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12941,14 +12946,14 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129543008</v>
+        <v>129543011</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12983,10 +12988,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457671</v>
+        <v>457665</v>
       </c>
       <c r="R116" t="n">
-        <v>6748048</v>
+        <v>6748082</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13018,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13028,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13055,10 +13060,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129542935</v>
+        <v>129543008</v>
       </c>
       <c r="B117" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13066,39 +13071,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>458060</v>
+        <v>457671</v>
       </c>
       <c r="R117" t="n">
-        <v>6748631</v>
+        <v>6748048</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13167,50 +13167,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129542947</v>
+        <v>129543061</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>457929</v>
+        <v>458155</v>
       </c>
       <c r="R118" t="n">
-        <v>6748484</v>
+        <v>6748548</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13242,7 +13237,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13252,7 +13247,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13279,7 +13274,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129543061</v>
+        <v>129543054</v>
       </c>
       <c r="B119" t="n">
         <v>79044</v>
@@ -13314,10 +13309,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458155</v>
+        <v>458097</v>
       </c>
       <c r="R119" t="n">
-        <v>6748548</v>
+        <v>6748662</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13349,7 +13344,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13359,7 +13354,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13386,45 +13381,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129543054</v>
+        <v>129542947</v>
       </c>
       <c r="B120" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>458097</v>
+        <v>457929</v>
       </c>
       <c r="R120" t="n">
-        <v>6748662</v>
+        <v>6748484</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129543046</v>
+        <v>129542936</v>
       </c>
       <c r="B122" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13611,34 +13611,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>457946</v>
+        <v>458155</v>
       </c>
       <c r="R122" t="n">
-        <v>6748493</v>
+        <v>6748562</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13670,7 +13675,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13680,7 +13685,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13700,17 +13705,17 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129542967</v>
+        <v>129543046</v>
       </c>
       <c r="B123" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13718,21 +13723,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13742,10 +13747,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>457939</v>
+        <v>457946</v>
       </c>
       <c r="R123" t="n">
-        <v>6748494</v>
+        <v>6748493</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13814,10 +13819,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129543048</v>
+        <v>129542967</v>
       </c>
       <c r="B124" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13825,21 +13830,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13849,10 +13854,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>457954</v>
+        <v>457939</v>
       </c>
       <c r="R124" t="n">
-        <v>6748541</v>
+        <v>6748494</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13884,7 +13889,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13894,7 +13899,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13914,14 +13919,14 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129543004</v>
+        <v>129543048</v>
       </c>
       <c r="B125" t="n">
         <v>79044</v>
@@ -13956,10 +13961,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>457802</v>
+        <v>457954</v>
       </c>
       <c r="R125" t="n">
-        <v>6748157</v>
+        <v>6748541</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13991,7 +13996,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14001,7 +14006,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14028,7 +14033,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129543025</v>
+        <v>129543004</v>
       </c>
       <c r="B126" t="n">
         <v>79044</v>
@@ -14063,10 +14068,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457761</v>
+        <v>457802</v>
       </c>
       <c r="R126" t="n">
-        <v>6748254</v>
+        <v>6748157</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14098,7 +14103,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14108,7 +14113,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14135,7 +14140,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129543015</v>
+        <v>129543025</v>
       </c>
       <c r="B127" t="n">
         <v>79044</v>
@@ -14170,10 +14175,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>457689</v>
+        <v>457761</v>
       </c>
       <c r="R127" t="n">
-        <v>6748165</v>
+        <v>6748254</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14205,7 +14210,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14215,7 +14220,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14242,7 +14247,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129542978</v>
+        <v>129543015</v>
       </c>
       <c r="B128" t="n">
         <v>79044</v>
@@ -14277,10 +14282,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457802</v>
+        <v>457689</v>
       </c>
       <c r="R128" t="n">
-        <v>6748301</v>
+        <v>6748165</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14312,7 +14317,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14322,7 +14327,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14349,7 +14354,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129543027</v>
+        <v>129542978</v>
       </c>
       <c r="B129" t="n">
         <v>79044</v>
@@ -14384,10 +14389,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>457756</v>
+        <v>457802</v>
       </c>
       <c r="R129" t="n">
-        <v>6748271</v>
+        <v>6748301</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14419,7 +14424,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14429,7 +14434,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14449,17 +14454,17 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129542936</v>
+        <v>129543027</v>
       </c>
       <c r="B130" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14467,39 +14472,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>458155</v>
+        <v>457756</v>
       </c>
       <c r="R130" t="n">
-        <v>6748562</v>
+        <v>6748271</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14668,39 +14668,39 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129542920</v>
+        <v>129543077</v>
       </c>
       <c r="B132" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457964</v>
+        <v>457938</v>
       </c>
       <c r="R132" t="n">
-        <v>6748415</v>
+        <v>6748409</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14782,10 +14782,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129542916</v>
+        <v>129543040</v>
       </c>
       <c r="B133" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14793,21 +14793,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457750</v>
+        <v>457817</v>
       </c>
       <c r="R133" t="n">
-        <v>6748276</v>
+        <v>6748400</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14889,7 +14889,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129543077</v>
+        <v>129543044</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>457938</v>
+        <v>457939</v>
       </c>
       <c r="R134" t="n">
-        <v>6748409</v>
+        <v>6748453</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129543040</v>
+        <v>129542916</v>
       </c>
       <c r="B135" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15007,21 +15007,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457817</v>
+        <v>457750</v>
       </c>
       <c r="R135" t="n">
-        <v>6748400</v>
+        <v>6748276</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15096,14 +15096,14 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129543044</v>
+        <v>129543050</v>
       </c>
       <c r="B136" t="n">
         <v>79044</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>457939</v>
+        <v>458067</v>
       </c>
       <c r="R136" t="n">
-        <v>6748453</v>
+        <v>6748648</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15210,7 +15210,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129543050</v>
+        <v>129543036</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>458067</v>
+        <v>457843</v>
       </c>
       <c r="R137" t="n">
-        <v>6748648</v>
+        <v>6748341</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15317,7 +15317,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129543036</v>
+        <v>129543058</v>
       </c>
       <c r="B138" t="n">
         <v>79044</v>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>457843</v>
+        <v>458143</v>
       </c>
       <c r="R138" t="n">
-        <v>6748341</v>
+        <v>6748611</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15424,32 +15424,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129543058</v>
+        <v>129542920</v>
       </c>
       <c r="B139" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>458143</v>
+        <v>457964</v>
       </c>
       <c r="R139" t="n">
-        <v>6748611</v>
+        <v>6748415</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15524,17 +15524,17 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129542963</v>
+        <v>129542958</v>
       </c>
       <c r="B140" t="n">
-        <v>78801</v>
+        <v>81029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>457754</v>
+        <v>458029</v>
       </c>
       <c r="R140" t="n">
-        <v>6748230</v>
+        <v>6748402</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15631,17 +15631,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129543074</v>
+        <v>129543089</v>
       </c>
       <c r="B141" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457905</v>
+        <v>457809</v>
       </c>
       <c r="R141" t="n">
-        <v>6748321</v>
+        <v>6748254</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15745,7 +15745,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129542965</v>
+        <v>129542963</v>
       </c>
       <c r="B142" t="n">
         <v>78801</v>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457760</v>
+        <v>457754</v>
       </c>
       <c r="R142" t="n">
-        <v>6748255</v>
+        <v>6748230</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15845,14 +15845,14 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129543022</v>
+        <v>129543074</v>
       </c>
       <c r="B143" t="n">
         <v>79044</v>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457761</v>
+        <v>457905</v>
       </c>
       <c r="R143" t="n">
-        <v>6748192</v>
+        <v>6748321</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129543052</v>
+        <v>129542965</v>
       </c>
       <c r="B144" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15970,21 +15970,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>458081</v>
+        <v>457760</v>
       </c>
       <c r="R144" t="n">
-        <v>6748667</v>
+        <v>6748255</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16059,17 +16059,17 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129543089</v>
+        <v>129543022</v>
       </c>
       <c r="B145" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16077,21 +16077,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>457809</v>
+        <v>457761</v>
       </c>
       <c r="R145" t="n">
-        <v>6748254</v>
+        <v>6748192</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16173,10 +16173,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129542958</v>
+        <v>129543052</v>
       </c>
       <c r="B146" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16184,21 +16184,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>458029</v>
+        <v>458081</v>
       </c>
       <c r="R146" t="n">
-        <v>6748402</v>
+        <v>6748667</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16280,10 +16280,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129543100</v>
+        <v>129542994</v>
       </c>
       <c r="B147" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16291,21 +16291,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457631</v>
+        <v>457786</v>
       </c>
       <c r="R147" t="n">
-        <v>6748174</v>
+        <v>6748280</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,32 +16387,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129542941</v>
+        <v>129543100</v>
       </c>
       <c r="B148" t="n">
-        <v>97598</v>
+        <v>78710</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457929</v>
+        <v>457631</v>
       </c>
       <c r="R148" t="n">
-        <v>6748448</v>
+        <v>6748174</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16601,7 +16601,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129542994</v>
+        <v>129543006</v>
       </c>
       <c r="B150" t="n">
         <v>79044</v>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457786</v>
+        <v>457712</v>
       </c>
       <c r="R150" t="n">
-        <v>6748280</v>
+        <v>6748081</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16708,7 +16708,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129543006</v>
+        <v>129543023</v>
       </c>
       <c r="B151" t="n">
         <v>79044</v>
@@ -16743,10 +16743,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457712</v>
+        <v>457758</v>
       </c>
       <c r="R151" t="n">
-        <v>6748081</v>
+        <v>6748213</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16815,32 +16815,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129543023</v>
+        <v>129542941</v>
       </c>
       <c r="B152" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457758</v>
+        <v>457929</v>
       </c>
       <c r="R152" t="n">
-        <v>6748213</v>
+        <v>6748448</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -17243,32 +17243,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542980</v>
+        <v>129542943</v>
       </c>
       <c r="B156" t="n">
-        <v>91726</v>
+        <v>97598</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1503</v>
+        <v>221945</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>458058</v>
+        <v>457999</v>
       </c>
       <c r="R156" t="n">
-        <v>6748621</v>
+        <v>6748381</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17343,39 +17343,39 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129542959</v>
+        <v>129542980</v>
       </c>
       <c r="B157" t="n">
-        <v>81029</v>
+        <v>91726</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457884</v>
+        <v>458058</v>
       </c>
       <c r="R157" t="n">
-        <v>6748404</v>
+        <v>6748621</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17450,39 +17450,39 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129542945</v>
+        <v>129542959</v>
       </c>
       <c r="B158" t="n">
-        <v>97604</v>
+        <v>81029</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457654</v>
+        <v>457884</v>
       </c>
       <c r="R158" t="n">
-        <v>6748079</v>
+        <v>6748404</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17557,17 +17557,17 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129542943</v>
+        <v>129542945</v>
       </c>
       <c r="B159" t="n">
-        <v>97598</v>
+        <v>97604</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17575,16 +17575,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457999</v>
+        <v>457654</v>
       </c>
       <c r="R159" t="n">
-        <v>6748381</v>
+        <v>6748079</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129542951</v>
+        <v>129543007</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457817</v>
+        <v>457677</v>
       </c>
       <c r="R2" t="n">
-        <v>6748352</v>
+        <v>6748051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,14 +775,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129543041</v>
+        <v>129543024</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457854</v>
+        <v>457755</v>
       </c>
       <c r="R3" t="n">
-        <v>6748444</v>
+        <v>6748219</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543108</v>
+        <v>129543031</v>
       </c>
       <c r="B4" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458131</v>
+        <v>457809</v>
       </c>
       <c r="R4" t="n">
-        <v>6748548</v>
+        <v>6748286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543007</v>
+        <v>129543041</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457677</v>
+        <v>457854</v>
       </c>
       <c r="R5" t="n">
-        <v>6748051</v>
+        <v>6748444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543031</v>
+        <v>129543026</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457809</v>
+        <v>457758</v>
       </c>
       <c r="R6" t="n">
-        <v>6748286</v>
+        <v>6748263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543024</v>
+        <v>129543056</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457755</v>
+        <v>458120</v>
       </c>
       <c r="R7" t="n">
-        <v>6748219</v>
+        <v>6748624</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543026</v>
+        <v>129543108</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457758</v>
+        <v>458131</v>
       </c>
       <c r="R8" t="n">
-        <v>6748263</v>
+        <v>6748548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,45 +1424,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543056</v>
+        <v>129542925</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458120</v>
+        <v>457896</v>
       </c>
       <c r="R9" t="n">
-        <v>6748624</v>
+        <v>6748335</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129542925</v>
+        <v>129542951</v>
       </c>
       <c r="B10" t="n">
-        <v>56917</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,27 +1547,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457896</v>
+        <v>457817</v>
       </c>
       <c r="R10" t="n">
-        <v>6748335</v>
+        <v>6748352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,39 +1641,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129542924</v>
+        <v>129543081</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>91826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457899</v>
+        <v>458131</v>
       </c>
       <c r="R11" t="n">
-        <v>6748444</v>
+        <v>6748547</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129542928</v>
+        <v>129542924</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,39 +1980,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457940</v>
+        <v>457899</v>
       </c>
       <c r="R14" t="n">
-        <v>6748387</v>
+        <v>6748444</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2074,39 +2069,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543081</v>
+        <v>129542995</v>
       </c>
       <c r="B15" t="n">
-        <v>91826</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458131</v>
+        <v>457809</v>
       </c>
       <c r="R15" t="n">
-        <v>6748547</v>
+        <v>6748246</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2616,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129542995</v>
+        <v>129542915</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457809</v>
+        <v>457754</v>
       </c>
       <c r="R20" t="n">
-        <v>6748246</v>
+        <v>6748230</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129542915</v>
+        <v>129542928</v>
       </c>
       <c r="B21" t="n">
-        <v>79663</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,34 +2729,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457754</v>
+        <v>457940</v>
       </c>
       <c r="R21" t="n">
-        <v>6748230</v>
+        <v>6748387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129542996</v>
+        <v>129542913</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457833</v>
+        <v>457761</v>
       </c>
       <c r="R23" t="n">
-        <v>6748233</v>
+        <v>6748133</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129542913</v>
+        <v>129543051</v>
       </c>
       <c r="B24" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,21 +3055,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457761</v>
+        <v>458077</v>
       </c>
       <c r="R24" t="n">
-        <v>6748133</v>
+        <v>6748657</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543038</v>
+        <v>129543045</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457829</v>
+        <v>457912</v>
       </c>
       <c r="R25" t="n">
-        <v>6748366</v>
+        <v>6748485</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,7 +3258,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543005</v>
+        <v>129543032</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457775</v>
+        <v>457821</v>
       </c>
       <c r="R26" t="n">
-        <v>6748148</v>
+        <v>6748297</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,7 +3365,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543051</v>
+        <v>129542996</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458077</v>
+        <v>457833</v>
       </c>
       <c r="R27" t="n">
-        <v>6748657</v>
+        <v>6748233</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,7 +3472,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543045</v>
+        <v>129542982</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457912</v>
+        <v>457941</v>
       </c>
       <c r="R28" t="n">
-        <v>6748485</v>
+        <v>6748477</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3552,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,7 +3584,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543032</v>
+        <v>129543038</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3614,10 +3619,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457821</v>
+        <v>457829</v>
       </c>
       <c r="R29" t="n">
-        <v>6748297</v>
+        <v>6748366</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,7 +3654,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3664,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,7 +3691,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129542982</v>
+        <v>129543005</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3721,10 +3726,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457941</v>
+        <v>457775</v>
       </c>
       <c r="R30" t="n">
-        <v>6748477</v>
+        <v>6748148</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3756,7 +3761,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,12 +3771,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543090</v>
+        <v>129542966</v>
       </c>
       <c r="B31" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457883</v>
+        <v>457938</v>
       </c>
       <c r="R31" t="n">
-        <v>6748264</v>
+        <v>6748466</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3905,7 +3905,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543018</v>
+        <v>129543059</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457679</v>
+        <v>458174</v>
       </c>
       <c r="R32" t="n">
-        <v>6748231</v>
+        <v>6748599</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129542966</v>
+        <v>129543090</v>
       </c>
       <c r="B33" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457938</v>
+        <v>457883</v>
       </c>
       <c r="R33" t="n">
-        <v>6748466</v>
+        <v>6748264</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543063</v>
+        <v>129543021</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458116</v>
+        <v>457756</v>
       </c>
       <c r="R34" t="n">
-        <v>6748548</v>
+        <v>6748192</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,7 +4226,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543059</v>
+        <v>129543063</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458174</v>
+        <v>458116</v>
       </c>
       <c r="R35" t="n">
-        <v>6748599</v>
+        <v>6748548</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543021</v>
+        <v>129543018</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457756</v>
+        <v>457679</v>
       </c>
       <c r="R36" t="n">
-        <v>6748192</v>
+        <v>6748231</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4547,10 +4547,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542942</v>
+        <v>129542949</v>
       </c>
       <c r="B38" t="n">
-        <v>97598</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4558,34 +4558,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457951</v>
+        <v>457627</v>
       </c>
       <c r="R38" t="n">
-        <v>6748543</v>
+        <v>6748161</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4617,7 +4622,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4627,7 +4632,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4647,17 +4652,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129542949</v>
+        <v>129542942</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>97598</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4665,39 +4670,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457627</v>
+        <v>457951</v>
       </c>
       <c r="R39" t="n">
-        <v>6748161</v>
+        <v>6748543</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,52 +4759,57 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543112</v>
+        <v>129542927</v>
       </c>
       <c r="B40" t="n">
-        <v>91610</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5321</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458029</v>
+        <v>458027</v>
       </c>
       <c r="R40" t="n">
-        <v>6748411</v>
+        <v>6748413</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4855,7 +4860,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4974,39 +4978,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543098</v>
+        <v>129543112</v>
       </c>
       <c r="B42" t="n">
-        <v>78710</v>
+        <v>91610</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>5321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5016,10 +5020,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457657</v>
+        <v>458029</v>
       </c>
       <c r="R42" t="n">
-        <v>6748066</v>
+        <v>6748411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5051,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5061,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5070,6 +5074,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5088,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543093</v>
+        <v>129543003</v>
       </c>
       <c r="B43" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5099,21 +5104,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5123,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457737</v>
+        <v>457814</v>
       </c>
       <c r="R43" t="n">
-        <v>6748103</v>
+        <v>6748175</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5158,7 +5163,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5168,7 +5173,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,7 +5200,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543071</v>
+        <v>129542998</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5230,10 +5235,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457928</v>
+        <v>457876</v>
       </c>
       <c r="R44" t="n">
-        <v>6748344</v>
+        <v>6748240</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5265,7 +5270,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5275,7 +5280,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,7 +5307,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129542998</v>
+        <v>129543071</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5337,10 +5342,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457876</v>
+        <v>457928</v>
       </c>
       <c r="R45" t="n">
-        <v>6748240</v>
+        <v>6748344</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5372,7 +5377,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5382,7 +5387,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5409,7 +5414,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543003</v>
+        <v>129543057</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5444,10 +5449,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457814</v>
+        <v>458134</v>
       </c>
       <c r="R46" t="n">
-        <v>6748175</v>
+        <v>6748614</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5479,7 +5484,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5489,7 +5494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5516,10 +5521,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543057</v>
+        <v>129543098</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5527,21 +5532,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5551,10 +5556,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458134</v>
+        <v>457657</v>
       </c>
       <c r="R47" t="n">
-        <v>6748614</v>
+        <v>6748066</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5586,7 +5591,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5596,7 +5601,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5623,10 +5628,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129542927</v>
+        <v>129543093</v>
       </c>
       <c r="B48" t="n">
-        <v>57887</v>
+        <v>78710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5634,39 +5639,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>458027</v>
+        <v>457737</v>
       </c>
       <c r="R48" t="n">
-        <v>6748413</v>
+        <v>6748103</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6163,45 +6163,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543034</v>
+        <v>129542950</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457852</v>
+        <v>457695</v>
       </c>
       <c r="R53" t="n">
-        <v>6748316</v>
+        <v>6748215</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6233,7 +6238,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6243,7 +6248,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6270,45 +6275,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543001</v>
+        <v>129542948</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457838</v>
+        <v>457777</v>
       </c>
       <c r="R54" t="n">
-        <v>6748208</v>
+        <v>6748294</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6350,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6350,7 +6360,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6377,7 +6387,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543064</v>
+        <v>129543035</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6412,10 +6422,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458049</v>
+        <v>457845</v>
       </c>
       <c r="R55" t="n">
-        <v>6748509</v>
+        <v>6748327</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6447,7 +6457,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6457,7 +6467,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6484,7 +6494,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543035</v>
+        <v>129543066</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6519,10 +6529,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457845</v>
+        <v>458042</v>
       </c>
       <c r="R56" t="n">
-        <v>6748327</v>
+        <v>6748499</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6554,7 +6564,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6564,7 +6574,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,10 +6601,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129542914</v>
+        <v>129543034</v>
       </c>
       <c r="B57" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6602,21 +6612,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6626,10 +6636,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457650</v>
+        <v>457852</v>
       </c>
       <c r="R57" t="n">
-        <v>6748064</v>
+        <v>6748316</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6671,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6671,7 +6681,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6691,14 +6701,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543066</v>
+        <v>129543072</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6733,10 +6743,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458042</v>
+        <v>457899</v>
       </c>
       <c r="R58" t="n">
-        <v>6748499</v>
+        <v>6748357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6768,7 +6778,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6778,7 +6788,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6805,7 +6815,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543042</v>
+        <v>129543001</v>
       </c>
       <c r="B59" t="n">
         <v>79044</v>
@@ -6840,10 +6850,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457922</v>
+        <v>457838</v>
       </c>
       <c r="R59" t="n">
-        <v>6748447</v>
+        <v>6748208</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6875,7 +6885,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6885,7 +6895,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,7 +6922,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543072</v>
+        <v>129543064</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6947,10 +6957,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457899</v>
+        <v>458049</v>
       </c>
       <c r="R60" t="n">
-        <v>6748357</v>
+        <v>6748509</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6982,7 +6992,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6992,7 +7002,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7019,50 +7029,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129542950</v>
+        <v>129543042</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457695</v>
+        <v>457922</v>
       </c>
       <c r="R61" t="n">
-        <v>6748215</v>
+        <v>6748447</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7094,7 +7099,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7104,7 +7109,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7124,57 +7129,52 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129542948</v>
+        <v>129542914</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457777</v>
+        <v>457650</v>
       </c>
       <c r="R62" t="n">
-        <v>6748294</v>
+        <v>6748064</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543002</v>
+        <v>129543060</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457813</v>
+        <v>458177</v>
       </c>
       <c r="R64" t="n">
-        <v>6748191</v>
+        <v>6748587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7564,50 +7564,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129542952</v>
+        <v>129543029</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458156</v>
+        <v>457780</v>
       </c>
       <c r="R66" t="n">
-        <v>6748545</v>
+        <v>6748311</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7639,7 +7634,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7649,7 +7644,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7669,14 +7664,14 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543073</v>
+        <v>129543002</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7711,10 +7706,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457917</v>
+        <v>457813</v>
       </c>
       <c r="R67" t="n">
-        <v>6748303</v>
+        <v>6748191</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7746,7 +7741,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7756,7 +7751,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7783,10 +7778,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129542962</v>
+        <v>129543047</v>
       </c>
       <c r="B68" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7794,21 +7789,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7818,10 +7813,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457762</v>
+        <v>457952</v>
       </c>
       <c r="R68" t="n">
-        <v>6748208</v>
+        <v>6748501</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7853,7 +7848,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7863,7 +7858,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7883,14 +7878,14 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543047</v>
+        <v>129543073</v>
       </c>
       <c r="B69" t="n">
         <v>79044</v>
@@ -7925,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457952</v>
+        <v>457917</v>
       </c>
       <c r="R69" t="n">
-        <v>6748501</v>
+        <v>6748303</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7960,7 +7955,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7970,7 +7965,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,10 +7992,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543019</v>
+        <v>129542962</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8008,21 +8003,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8032,7 +8027,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457725</v>
+        <v>457762</v>
       </c>
       <c r="R70" t="n">
         <v>6748208</v>
@@ -8067,7 +8062,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8077,7 +8072,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8104,7 +8099,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543060</v>
+        <v>129543019</v>
       </c>
       <c r="B71" t="n">
         <v>79044</v>
@@ -8139,10 +8134,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458177</v>
+        <v>457725</v>
       </c>
       <c r="R71" t="n">
-        <v>6748587</v>
+        <v>6748208</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8174,7 +8169,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8184,7 +8179,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8211,10 +8206,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543029</v>
+        <v>129542961</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8222,21 +8217,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8246,10 +8241,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457780</v>
+        <v>457859</v>
       </c>
       <c r="R72" t="n">
-        <v>6748311</v>
+        <v>6748231</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8281,7 +8276,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8291,7 +8286,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8318,45 +8313,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129542961</v>
+        <v>129542952</v>
       </c>
       <c r="B73" t="n">
-        <v>78801</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457859</v>
+        <v>458156</v>
       </c>
       <c r="R73" t="n">
-        <v>6748231</v>
+        <v>6748545</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8418,17 +8418,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543101</v>
+        <v>129543000</v>
       </c>
       <c r="B74" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8436,21 +8436,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457746</v>
+        <v>457846</v>
       </c>
       <c r="R74" t="n">
-        <v>6748232</v>
+        <v>6748214</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8532,10 +8532,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543105</v>
+        <v>129542997</v>
       </c>
       <c r="B75" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457993</v>
+        <v>457863</v>
       </c>
       <c r="R75" t="n">
-        <v>6748571</v>
+        <v>6748231</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129542933</v>
+        <v>129542999</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8650,39 +8650,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457753</v>
+        <v>457883</v>
       </c>
       <c r="R76" t="n">
-        <v>6748178</v>
+        <v>6748260</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8714,7 +8709,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8724,7 +8719,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8744,14 +8739,14 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129542997</v>
+        <v>129543075</v>
       </c>
       <c r="B77" t="n">
         <v>79044</v>
@@ -8786,10 +8781,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457863</v>
+        <v>457896</v>
       </c>
       <c r="R77" t="n">
-        <v>6748231</v>
+        <v>6748336</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8821,7 +8816,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8831,7 +8826,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8858,10 +8853,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543000</v>
+        <v>129542933</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,34 +8864,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457846</v>
+        <v>457753</v>
       </c>
       <c r="R78" t="n">
-        <v>6748214</v>
+        <v>6748178</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8965,10 +8965,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129542999</v>
+        <v>129543101</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8976,21 +8976,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457883</v>
+        <v>457746</v>
       </c>
       <c r="R79" t="n">
-        <v>6748260</v>
+        <v>6748232</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9072,10 +9072,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543075</v>
+        <v>129543105</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9083,21 +9083,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9107,10 +9107,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457896</v>
+        <v>457993</v>
       </c>
       <c r="R80" t="n">
-        <v>6748336</v>
+        <v>6748571</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9393,7 +9393,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129542991</v>
+        <v>129543065</v>
       </c>
       <c r="B83" t="n">
         <v>79044</v>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457762</v>
+        <v>458039</v>
       </c>
       <c r="R83" t="n">
-        <v>6748312</v>
+        <v>6748504</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9493,17 +9493,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129542964</v>
+        <v>129542991</v>
       </c>
       <c r="B84" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9511,21 +9511,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457767</v>
+        <v>457762</v>
       </c>
       <c r="R84" t="n">
-        <v>6748250</v>
+        <v>6748312</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9600,14 +9600,14 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129542968</v>
+        <v>129542964</v>
       </c>
       <c r="B85" t="n">
         <v>78801</v>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458060</v>
+        <v>457767</v>
       </c>
       <c r="R85" t="n">
-        <v>6748629</v>
+        <v>6748250</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9707,17 +9707,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543065</v>
+        <v>129542968</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9725,21 +9725,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458039</v>
+        <v>458060</v>
       </c>
       <c r="R86" t="n">
-        <v>6748504</v>
+        <v>6748629</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9821,10 +9821,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543085</v>
+        <v>129543028</v>
       </c>
       <c r="B87" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9832,21 +9832,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457880</v>
+        <v>457753</v>
       </c>
       <c r="R87" t="n">
-        <v>6748247</v>
+        <v>6748290</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9901,12 +9901,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På högstubbe med fem brandljud</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10040,10 +10035,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543049</v>
+        <v>129543085</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10051,21 +10046,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10075,10 +10070,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458018</v>
+        <v>457880</v>
       </c>
       <c r="R89" t="n">
-        <v>6748602</v>
+        <v>6748247</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10110,7 +10105,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10120,7 +10115,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På högstubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10147,7 +10147,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543028</v>
+        <v>129543049</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457753</v>
+        <v>458018</v>
       </c>
       <c r="R90" t="n">
-        <v>6748290</v>
+        <v>6748602</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10254,54 +10254,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129542969</v>
+        <v>129542939</v>
       </c>
       <c r="B91" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457879</v>
+        <v>457660</v>
       </c>
       <c r="R91" t="n">
-        <v>6748454</v>
+        <v>6748092</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10333,7 +10324,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10343,7 +10334,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10363,52 +10354,61 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129542939</v>
+        <v>129542969</v>
       </c>
       <c r="B92" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457660</v>
+        <v>457879</v>
       </c>
       <c r="R92" t="n">
-        <v>6748092</v>
+        <v>6748454</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10470,39 +10470,39 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129542960</v>
+        <v>129543099</v>
       </c>
       <c r="B93" t="n">
-        <v>80109</v>
+        <v>78710</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>458029</v>
+        <v>457650</v>
       </c>
       <c r="R93" t="n">
-        <v>6748413</v>
+        <v>6748064</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,12 +10557,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Rikligt på jätteasp</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10582,17 +10577,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129542956</v>
+        <v>129543104</v>
       </c>
       <c r="B94" t="n">
-        <v>81029</v>
+        <v>78710</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10600,21 +10595,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10624,10 +10619,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457662</v>
+        <v>457992</v>
       </c>
       <c r="R94" t="n">
-        <v>6748216</v>
+        <v>6748556</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10659,7 +10654,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10669,7 +10664,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10689,17 +10684,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543099</v>
+        <v>129542956</v>
       </c>
       <c r="B95" t="n">
-        <v>78710</v>
+        <v>81029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10707,21 +10702,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10731,10 +10726,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457650</v>
+        <v>457662</v>
       </c>
       <c r="R95" t="n">
-        <v>6748064</v>
+        <v>6748216</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10766,7 +10761,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10776,7 +10771,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10803,7 +10798,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543104</v>
+        <v>129543083</v>
       </c>
       <c r="B96" t="n">
         <v>78710</v>
@@ -10838,10 +10833,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457992</v>
+        <v>457757</v>
       </c>
       <c r="R96" t="n">
-        <v>6748556</v>
+        <v>6748191</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10873,7 +10868,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10883,7 +10878,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10910,10 +10905,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543083</v>
+        <v>129543020</v>
       </c>
       <c r="B97" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10921,21 +10916,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10945,10 +10940,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457757</v>
+        <v>457738</v>
       </c>
       <c r="R97" t="n">
-        <v>6748191</v>
+        <v>6748205</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10980,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10990,7 +10985,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11124,7 +11119,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543014</v>
+        <v>129543062</v>
       </c>
       <c r="B99" t="n">
         <v>79044</v>
@@ -11159,10 +11154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457634</v>
+        <v>458140</v>
       </c>
       <c r="R99" t="n">
-        <v>6748179</v>
+        <v>6748536</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11194,7 +11189,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11204,7 +11199,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11231,7 +11226,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543037</v>
+        <v>129543014</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -11266,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457830</v>
+        <v>457634</v>
       </c>
       <c r="R100" t="n">
-        <v>6748350</v>
+        <v>6748179</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11301,7 +11296,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11311,7 +11306,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11338,7 +11333,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543039</v>
+        <v>129543037</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -11376,7 +11371,7 @@
         <v>457830</v>
       </c>
       <c r="R101" t="n">
-        <v>6748402</v>
+        <v>6748350</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11408,7 +11403,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11418,7 +11413,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11445,7 +11440,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543030</v>
+        <v>129543039</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11480,10 +11475,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457811</v>
+        <v>457830</v>
       </c>
       <c r="R102" t="n">
-        <v>6748293</v>
+        <v>6748402</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11515,7 +11510,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11525,7 +11520,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11552,7 +11547,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543020</v>
+        <v>129543030</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -11587,10 +11582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457738</v>
+        <v>457811</v>
       </c>
       <c r="R103" t="n">
-        <v>6748205</v>
+        <v>6748293</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11622,7 +11617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11632,7 +11627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11766,32 +11761,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543062</v>
+        <v>129542960</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>80109</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11801,10 +11796,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458140</v>
+        <v>458029</v>
       </c>
       <c r="R105" t="n">
-        <v>6748536</v>
+        <v>6748413</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11836,7 +11831,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11846,7 +11841,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Rikligt på jätteasp</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,32 +11873,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129542981</v>
+        <v>129543094</v>
       </c>
       <c r="B106" t="n">
-        <v>91726</v>
+        <v>78710</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457964</v>
+        <v>457728</v>
       </c>
       <c r="R106" t="n">
-        <v>6748415</v>
+        <v>6748093</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11973,39 +11973,39 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543094</v>
+        <v>129542981</v>
       </c>
       <c r="B107" t="n">
-        <v>78710</v>
+        <v>91726</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457728</v>
+        <v>457964</v>
       </c>
       <c r="R107" t="n">
-        <v>6748093</v>
+        <v>6748415</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12301,50 +12301,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543111</v>
+        <v>129543012</v>
       </c>
       <c r="B110" t="n">
-        <v>5177</v>
+        <v>79044</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457665</v>
+        <v>457625</v>
       </c>
       <c r="R110" t="n">
-        <v>6748081</v>
+        <v>6748127</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12371,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12381,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12413,45 +12408,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543012</v>
+        <v>129543111</v>
       </c>
       <c r="B111" t="n">
-        <v>79044</v>
+        <v>5177</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457625</v>
+        <v>457665</v>
       </c>
       <c r="R111" t="n">
-        <v>6748127</v>
+        <v>6748081</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12520,10 +12520,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129542923</v>
+        <v>129543011</v>
       </c>
       <c r="B112" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12531,21 +12531,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>457773</v>
+        <v>457665</v>
       </c>
       <c r="R112" t="n">
-        <v>6748248</v>
+        <v>6748082</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12620,17 +12620,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129542955</v>
+        <v>129543008</v>
       </c>
       <c r="B113" t="n">
-        <v>92195</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12638,21 +12638,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5454</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12662,10 +12662,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458015</v>
+        <v>457671</v>
       </c>
       <c r="R113" t="n">
-        <v>6748399</v>
+        <v>6748048</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12727,52 +12727,57 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129542944</v>
+        <v>129542935</v>
       </c>
       <c r="B114" t="n">
-        <v>97604</v>
+        <v>57724</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>457654</v>
+        <v>458060</v>
       </c>
       <c r="R114" t="n">
-        <v>6748070</v>
+        <v>6748631</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12804,7 +12809,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12814,7 +12819,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12834,17 +12839,17 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129542935</v>
+        <v>129542923</v>
       </c>
       <c r="B115" t="n">
-        <v>57724</v>
+        <v>79139</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12852,39 +12857,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458060</v>
+        <v>457773</v>
       </c>
       <c r="R115" t="n">
-        <v>6748631</v>
+        <v>6748248</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12946,17 +12946,17 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129543011</v>
+        <v>129542955</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>92195</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12964,21 +12964,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457665</v>
+        <v>458015</v>
       </c>
       <c r="R116" t="n">
-        <v>6748082</v>
+        <v>6748399</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13060,32 +13060,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129543008</v>
+        <v>129542944</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>97604</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457671</v>
+        <v>457654</v>
       </c>
       <c r="R117" t="n">
-        <v>6748048</v>
+        <v>6748070</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13167,7 +13167,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129543061</v>
+        <v>129543054</v>
       </c>
       <c r="B118" t="n">
         <v>79044</v>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458155</v>
+        <v>458097</v>
       </c>
       <c r="R118" t="n">
-        <v>6748548</v>
+        <v>6748662</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13274,7 +13274,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129543054</v>
+        <v>129543061</v>
       </c>
       <c r="B119" t="n">
         <v>79044</v>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458097</v>
+        <v>458155</v>
       </c>
       <c r="R119" t="n">
-        <v>6748662</v>
+        <v>6748548</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13344,7 +13344,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129542936</v>
+        <v>129543004</v>
       </c>
       <c r="B122" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13611,39 +13611,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>458155</v>
+        <v>457802</v>
       </c>
       <c r="R122" t="n">
-        <v>6748562</v>
+        <v>6748157</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13675,7 +13670,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13685,7 +13680,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13705,7 +13700,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13819,10 +13814,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129542967</v>
+        <v>129543025</v>
       </c>
       <c r="B124" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13830,21 +13825,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13854,10 +13849,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>457939</v>
+        <v>457761</v>
       </c>
       <c r="R124" t="n">
-        <v>6748494</v>
+        <v>6748254</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13889,7 +13884,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13899,7 +13894,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13919,14 +13914,14 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129543048</v>
+        <v>129543027</v>
       </c>
       <c r="B125" t="n">
         <v>79044</v>
@@ -13961,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>457954</v>
+        <v>457756</v>
       </c>
       <c r="R125" t="n">
-        <v>6748541</v>
+        <v>6748271</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13996,7 +13991,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14006,7 +14001,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14033,7 +14028,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129543004</v>
+        <v>129543048</v>
       </c>
       <c r="B126" t="n">
         <v>79044</v>
@@ -14068,10 +14063,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457802</v>
+        <v>457954</v>
       </c>
       <c r="R126" t="n">
-        <v>6748157</v>
+        <v>6748541</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14103,7 +14098,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14113,7 +14108,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14140,7 +14135,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129543025</v>
+        <v>129543015</v>
       </c>
       <c r="B127" t="n">
         <v>79044</v>
@@ -14175,10 +14170,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>457761</v>
+        <v>457689</v>
       </c>
       <c r="R127" t="n">
-        <v>6748254</v>
+        <v>6748165</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14210,7 +14205,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14220,7 +14215,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14247,10 +14242,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129543015</v>
+        <v>129542967</v>
       </c>
       <c r="B128" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14258,21 +14253,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14282,10 +14277,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457689</v>
+        <v>457939</v>
       </c>
       <c r="R128" t="n">
-        <v>6748165</v>
+        <v>6748494</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14317,7 +14312,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14327,7 +14322,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14454,17 +14449,17 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129543027</v>
+        <v>129542936</v>
       </c>
       <c r="B130" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14472,34 +14467,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>457756</v>
+        <v>458155</v>
       </c>
       <c r="R130" t="n">
-        <v>6748271</v>
+        <v>6748562</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14668,39 +14668,39 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129543077</v>
+        <v>129542920</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457938</v>
+        <v>457964</v>
       </c>
       <c r="R132" t="n">
-        <v>6748409</v>
+        <v>6748415</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14782,7 +14782,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129543040</v>
+        <v>129543036</v>
       </c>
       <c r="B133" t="n">
         <v>79044</v>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457817</v>
+        <v>457843</v>
       </c>
       <c r="R133" t="n">
-        <v>6748400</v>
+        <v>6748341</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14889,7 +14889,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129543044</v>
+        <v>129543058</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>457939</v>
+        <v>458143</v>
       </c>
       <c r="R134" t="n">
-        <v>6748453</v>
+        <v>6748611</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129542916</v>
+        <v>129543044</v>
       </c>
       <c r="B135" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15007,21 +15007,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457750</v>
+        <v>457939</v>
       </c>
       <c r="R135" t="n">
-        <v>6748276</v>
+        <v>6748453</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15096,14 +15096,14 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129543050</v>
+        <v>129543040</v>
       </c>
       <c r="B136" t="n">
         <v>79044</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>458067</v>
+        <v>457817</v>
       </c>
       <c r="R136" t="n">
-        <v>6748648</v>
+        <v>6748400</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15210,7 +15210,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129543036</v>
+        <v>129543077</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>457843</v>
+        <v>457938</v>
       </c>
       <c r="R137" t="n">
-        <v>6748341</v>
+        <v>6748409</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15317,10 +15317,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129543058</v>
+        <v>129542916</v>
       </c>
       <c r="B138" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15328,21 +15328,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>458143</v>
+        <v>457750</v>
       </c>
       <c r="R138" t="n">
-        <v>6748611</v>
+        <v>6748276</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15424,32 +15424,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129542920</v>
+        <v>129543050</v>
       </c>
       <c r="B139" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>457964</v>
+        <v>458067</v>
       </c>
       <c r="R139" t="n">
-        <v>6748415</v>
+        <v>6748648</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15524,17 +15524,17 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129542958</v>
+        <v>129543089</v>
       </c>
       <c r="B140" t="n">
-        <v>81029</v>
+        <v>78710</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>458029</v>
+        <v>457809</v>
       </c>
       <c r="R140" t="n">
-        <v>6748402</v>
+        <v>6748254</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15631,17 +15631,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129543089</v>
+        <v>129542958</v>
       </c>
       <c r="B141" t="n">
-        <v>78710</v>
+        <v>81029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457809</v>
+        <v>458029</v>
       </c>
       <c r="R141" t="n">
-        <v>6748254</v>
+        <v>6748402</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15845,17 +15845,17 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129543074</v>
+        <v>129542965</v>
       </c>
       <c r="B143" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15863,21 +15863,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457905</v>
+        <v>457760</v>
       </c>
       <c r="R143" t="n">
-        <v>6748321</v>
+        <v>6748255</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129542965</v>
+        <v>129543022</v>
       </c>
       <c r="B144" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15970,21 +15970,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457760</v>
+        <v>457761</v>
       </c>
       <c r="R144" t="n">
-        <v>6748255</v>
+        <v>6748192</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16059,14 +16059,14 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129543022</v>
+        <v>129543074</v>
       </c>
       <c r="B145" t="n">
         <v>79044</v>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>457761</v>
+        <v>457905</v>
       </c>
       <c r="R145" t="n">
-        <v>6748192</v>
+        <v>6748321</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16280,32 +16280,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129542994</v>
+        <v>129542941</v>
       </c>
       <c r="B147" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457786</v>
+        <v>457929</v>
       </c>
       <c r="R147" t="n">
-        <v>6748280</v>
+        <v>6748448</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,10 +16387,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129543100</v>
+        <v>129543069</v>
       </c>
       <c r="B148" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16398,21 +16398,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457631</v>
+        <v>457930</v>
       </c>
       <c r="R148" t="n">
-        <v>6748174</v>
+        <v>6748385</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16494,7 +16494,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129543069</v>
+        <v>129542994</v>
       </c>
       <c r="B149" t="n">
         <v>79044</v>
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457930</v>
+        <v>457786</v>
       </c>
       <c r="R149" t="n">
-        <v>6748385</v>
+        <v>6748280</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16601,7 +16601,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129543006</v>
+        <v>129543023</v>
       </c>
       <c r="B150" t="n">
         <v>79044</v>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457712</v>
+        <v>457758</v>
       </c>
       <c r="R150" t="n">
-        <v>6748081</v>
+        <v>6748213</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16708,10 +16708,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129543023</v>
+        <v>129543100</v>
       </c>
       <c r="B151" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16719,21 +16719,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16743,10 +16743,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457758</v>
+        <v>457631</v>
       </c>
       <c r="R151" t="n">
-        <v>6748213</v>
+        <v>6748174</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16815,32 +16815,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129542941</v>
+        <v>129543006</v>
       </c>
       <c r="B152" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457929</v>
+        <v>457712</v>
       </c>
       <c r="R152" t="n">
-        <v>6748448</v>
+        <v>6748081</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16915,39 +16915,39 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129543068</v>
+        <v>129542980</v>
       </c>
       <c r="B153" t="n">
-        <v>79044</v>
+        <v>91726</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>457935</v>
+        <v>458058</v>
       </c>
       <c r="R153" t="n">
-        <v>6748390</v>
+        <v>6748621</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17029,10 +17029,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129543067</v>
+        <v>129542959</v>
       </c>
       <c r="B154" t="n">
-        <v>79044</v>
+        <v>81029</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17040,21 +17040,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457946</v>
+        <v>457884</v>
       </c>
       <c r="R154" t="n">
-        <v>6748380</v>
+        <v>6748404</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17136,7 +17136,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129543033</v>
+        <v>129543068</v>
       </c>
       <c r="B155" t="n">
         <v>79044</v>
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>457836</v>
+        <v>457935</v>
       </c>
       <c r="R155" t="n">
-        <v>6748291</v>
+        <v>6748390</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542943</v>
+        <v>129543067</v>
       </c>
       <c r="B156" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>457999</v>
+        <v>457946</v>
       </c>
       <c r="R156" t="n">
-        <v>6748381</v>
+        <v>6748380</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17343,39 +17343,39 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129542980</v>
+        <v>129543033</v>
       </c>
       <c r="B157" t="n">
-        <v>91726</v>
+        <v>79044</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>458058</v>
+        <v>457836</v>
       </c>
       <c r="R157" t="n">
-        <v>6748621</v>
+        <v>6748291</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17450,39 +17450,39 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129542959</v>
+        <v>129542945</v>
       </c>
       <c r="B158" t="n">
-        <v>81029</v>
+        <v>97604</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1049</v>
+        <v>221941</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457884</v>
+        <v>457654</v>
       </c>
       <c r="R158" t="n">
-        <v>6748404</v>
+        <v>6748079</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17557,17 +17557,17 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129542945</v>
+        <v>129542943</v>
       </c>
       <c r="B159" t="n">
-        <v>97604</v>
+        <v>97598</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17575,16 +17575,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457654</v>
+        <v>457999</v>
       </c>
       <c r="R159" t="n">
-        <v>6748079</v>
+        <v>6748381</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129543024</v>
+        <v>129543031</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457755</v>
+        <v>457809</v>
       </c>
       <c r="R3" t="n">
-        <v>6748219</v>
+        <v>6748286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543031</v>
+        <v>129543024</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457809</v>
+        <v>457755</v>
       </c>
       <c r="R4" t="n">
-        <v>6748286</v>
+        <v>6748219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1317,45 +1317,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543108</v>
+        <v>129542925</v>
       </c>
       <c r="B8" t="n">
-        <v>78710</v>
+        <v>56917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458131</v>
+        <v>457896</v>
       </c>
       <c r="R8" t="n">
-        <v>6748548</v>
+        <v>6748335</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,50 +1429,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129542925</v>
+        <v>129543108</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>78710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457896</v>
+        <v>458131</v>
       </c>
       <c r="R9" t="n">
-        <v>6748335</v>
+        <v>6748548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1648,45 +1648,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543081</v>
+        <v>129542928</v>
       </c>
       <c r="B11" t="n">
-        <v>91826</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458131</v>
+        <v>457940</v>
       </c>
       <c r="R11" t="n">
-        <v>6748547</v>
+        <v>6748387</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543091</v>
+        <v>129543043</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457817</v>
+        <v>457927</v>
       </c>
       <c r="R12" t="n">
-        <v>6748202</v>
+        <v>6748447</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543092</v>
+        <v>129542992</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457785</v>
+        <v>457763</v>
       </c>
       <c r="R13" t="n">
-        <v>6748160</v>
+        <v>6748301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,17 +1967,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129542924</v>
+        <v>129543017</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457899</v>
+        <v>457657</v>
       </c>
       <c r="R14" t="n">
-        <v>6748444</v>
+        <v>6748226</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129542995</v>
+        <v>129543070</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2111,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457809</v>
+        <v>457936</v>
       </c>
       <c r="R15" t="n">
-        <v>6748246</v>
+        <v>6748379</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,17 +2181,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543043</v>
+        <v>129542924</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457927</v>
+        <v>457899</v>
       </c>
       <c r="R16" t="n">
-        <v>6748447</v>
+        <v>6748444</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,32 +2295,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129542992</v>
+        <v>129543081</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>91826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457763</v>
+        <v>458131</v>
       </c>
       <c r="R17" t="n">
-        <v>6748301</v>
+        <v>6748547</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,17 +2395,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543017</v>
+        <v>129543091</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2413,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457657</v>
+        <v>457817</v>
       </c>
       <c r="R18" t="n">
-        <v>6748226</v>
+        <v>6748202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,17 +2502,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543070</v>
+        <v>129543092</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457936</v>
+        <v>457785</v>
       </c>
       <c r="R19" t="n">
-        <v>6748379</v>
+        <v>6748160</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2584,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2609,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2718,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129542928</v>
+        <v>129542995</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,39 +2734,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457940</v>
+        <v>457809</v>
       </c>
       <c r="R21" t="n">
-        <v>6748387</v>
+        <v>6748246</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543051</v>
+        <v>129542996</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458077</v>
+        <v>457833</v>
       </c>
       <c r="R24" t="n">
-        <v>6748657</v>
+        <v>6748233</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543045</v>
+        <v>129543038</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457912</v>
+        <v>457829</v>
       </c>
       <c r="R25" t="n">
-        <v>6748485</v>
+        <v>6748366</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,7 +3258,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543032</v>
+        <v>129543005</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457821</v>
+        <v>457775</v>
       </c>
       <c r="R26" t="n">
-        <v>6748297</v>
+        <v>6748148</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,7 +3365,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129542996</v>
+        <v>129543051</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457833</v>
+        <v>458077</v>
       </c>
       <c r="R27" t="n">
-        <v>6748233</v>
+        <v>6748657</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,7 +3472,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129542982</v>
+        <v>129543045</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457941</v>
+        <v>457912</v>
       </c>
       <c r="R28" t="n">
-        <v>6748477</v>
+        <v>6748485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,12 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3584,7 +3579,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543038</v>
+        <v>129543032</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3619,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457829</v>
+        <v>457821</v>
       </c>
       <c r="R29" t="n">
-        <v>6748366</v>
+        <v>6748297</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3654,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3664,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3691,7 +3686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543005</v>
+        <v>129542982</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3726,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457775</v>
+        <v>457941</v>
       </c>
       <c r="R30" t="n">
-        <v>6748148</v>
+        <v>6748477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3771,7 +3766,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129542966</v>
+        <v>129543018</v>
       </c>
       <c r="B31" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457938</v>
+        <v>457679</v>
       </c>
       <c r="R31" t="n">
-        <v>6748466</v>
+        <v>6748231</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3905,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543059</v>
+        <v>129542966</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,21 +3916,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458174</v>
+        <v>457938</v>
       </c>
       <c r="R32" t="n">
-        <v>6748599</v>
+        <v>6748466</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543090</v>
+        <v>129543063</v>
       </c>
       <c r="B33" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457883</v>
+        <v>458116</v>
       </c>
       <c r="R33" t="n">
-        <v>6748264</v>
+        <v>6748548</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,7 +4119,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543021</v>
+        <v>129543059</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457756</v>
+        <v>458174</v>
       </c>
       <c r="R34" t="n">
-        <v>6748192</v>
+        <v>6748599</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,7 +4226,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543063</v>
+        <v>129543021</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458116</v>
+        <v>457756</v>
       </c>
       <c r="R35" t="n">
-        <v>6748548</v>
+        <v>6748192</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543018</v>
+        <v>129542993</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457679</v>
+        <v>457763</v>
       </c>
       <c r="R36" t="n">
-        <v>6748231</v>
+        <v>6748294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4433,52 +4433,57 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129542993</v>
+        <v>129542949</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457763</v>
+        <v>457627</v>
       </c>
       <c r="R37" t="n">
-        <v>6748294</v>
+        <v>6748161</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4510,7 +4515,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4520,7 +4525,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4547,50 +4552,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542949</v>
+        <v>129543090</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457627</v>
+        <v>457883</v>
       </c>
       <c r="R38" t="n">
-        <v>6748161</v>
+        <v>6748264</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4766,50 +4766,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129542927</v>
+        <v>129543112</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>91610</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>5321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458027</v>
+        <v>458029</v>
       </c>
       <c r="R40" t="n">
-        <v>6748413</v>
+        <v>6748411</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4860,6 +4855,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4871,17 +4867,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129542946</v>
+        <v>129542927</v>
       </c>
       <c r="B41" t="n">
-        <v>91606</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,34 +4885,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458035</v>
+        <v>458027</v>
       </c>
       <c r="R41" t="n">
-        <v>6748395</v>
+        <v>6748413</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4948,7 +4949,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4958,7 +4959,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4985,32 +4986,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543112</v>
+        <v>129542946</v>
       </c>
       <c r="B42" t="n">
-        <v>91610</v>
+        <v>91606</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5321</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5020,10 +5021,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458029</v>
+        <v>458035</v>
       </c>
       <c r="R42" t="n">
-        <v>6748411</v>
+        <v>6748395</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5055,7 +5056,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5065,7 +5066,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5074,7 +5075,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543003</v>
+        <v>129543098</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457814</v>
+        <v>457657</v>
       </c>
       <c r="R43" t="n">
-        <v>6748175</v>
+        <v>6748066</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5193,17 +5193,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129542998</v>
+        <v>129543093</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457876</v>
+        <v>457737</v>
       </c>
       <c r="R44" t="n">
-        <v>6748240</v>
+        <v>6748103</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5407,14 +5407,14 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543057</v>
+        <v>129542998</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458134</v>
+        <v>457876</v>
       </c>
       <c r="R46" t="n">
-        <v>6748614</v>
+        <v>6748240</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5514,17 +5514,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543098</v>
+        <v>129543003</v>
       </c>
       <c r="B47" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457657</v>
+        <v>457814</v>
       </c>
       <c r="R47" t="n">
-        <v>6748066</v>
+        <v>6748175</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,10 +5628,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543093</v>
+        <v>129543057</v>
       </c>
       <c r="B48" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5639,21 +5639,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457737</v>
+        <v>458134</v>
       </c>
       <c r="R48" t="n">
-        <v>6748103</v>
+        <v>6748614</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543082</v>
+        <v>129543009</v>
       </c>
       <c r="B49" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457792</v>
+        <v>457654</v>
       </c>
       <c r="R49" t="n">
-        <v>6748260</v>
+        <v>6748079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5842,10 +5842,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543078</v>
+        <v>129543082</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457875</v>
+        <v>457792</v>
       </c>
       <c r="R50" t="n">
-        <v>6748394</v>
+        <v>6748260</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5942,14 +5942,14 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543010</v>
+        <v>129543078</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457656</v>
+        <v>457875</v>
       </c>
       <c r="R51" t="n">
-        <v>6748084</v>
+        <v>6748394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6049,14 +6049,14 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543009</v>
+        <v>129543010</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457654</v>
+        <v>457656</v>
       </c>
       <c r="R52" t="n">
-        <v>6748079</v>
+        <v>6748084</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6163,50 +6163,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129542950</v>
+        <v>129543034</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457695</v>
+        <v>457852</v>
       </c>
       <c r="R53" t="n">
-        <v>6748215</v>
+        <v>6748316</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6238,7 +6233,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6248,7 +6243,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6275,50 +6270,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129542948</v>
+        <v>129543064</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457777</v>
+        <v>458049</v>
       </c>
       <c r="R54" t="n">
-        <v>6748294</v>
+        <v>6748509</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6350,7 +6340,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6360,7 +6350,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6380,14 +6370,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543035</v>
+        <v>129543042</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6422,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457845</v>
+        <v>457922</v>
       </c>
       <c r="R55" t="n">
-        <v>6748327</v>
+        <v>6748447</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6457,7 +6447,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6467,7 +6457,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6494,7 +6484,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543066</v>
+        <v>129543072</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6529,10 +6519,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458042</v>
+        <v>457899</v>
       </c>
       <c r="R56" t="n">
-        <v>6748499</v>
+        <v>6748357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6564,7 +6554,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6574,7 +6564,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6594,14 +6584,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543034</v>
+        <v>129543035</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6636,10 +6626,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457852</v>
+        <v>457845</v>
       </c>
       <c r="R57" t="n">
-        <v>6748316</v>
+        <v>6748327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6671,7 +6661,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6681,7 +6671,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6708,7 +6698,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543072</v>
+        <v>129543066</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6743,10 +6733,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457899</v>
+        <v>458042</v>
       </c>
       <c r="R58" t="n">
-        <v>6748357</v>
+        <v>6748499</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6778,7 +6768,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6788,7 +6778,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6808,17 +6798,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543001</v>
+        <v>129542914</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6826,21 +6816,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6850,10 +6840,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457838</v>
+        <v>457650</v>
       </c>
       <c r="R59" t="n">
-        <v>6748208</v>
+        <v>6748064</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6885,7 +6875,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6895,7 +6885,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6922,45 +6912,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543064</v>
+        <v>129542948</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458049</v>
+        <v>457777</v>
       </c>
       <c r="R60" t="n">
-        <v>6748509</v>
+        <v>6748294</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6992,7 +6987,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7002,7 +6997,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7029,45 +7024,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543042</v>
+        <v>129542950</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457922</v>
+        <v>457695</v>
       </c>
       <c r="R61" t="n">
-        <v>6748447</v>
+        <v>6748215</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7136,10 +7136,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129542914</v>
+        <v>129543001</v>
       </c>
       <c r="B62" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7147,21 +7147,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457650</v>
+        <v>457838</v>
       </c>
       <c r="R62" t="n">
-        <v>6748064</v>
+        <v>6748208</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7243,10 +7243,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543097</v>
+        <v>129543073</v>
       </c>
       <c r="B63" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457673</v>
+        <v>457917</v>
       </c>
       <c r="R63" t="n">
-        <v>6748071</v>
+        <v>6748303</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7343,17 +7343,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543060</v>
+        <v>129542962</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7361,21 +7361,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>458177</v>
+        <v>457762</v>
       </c>
       <c r="R64" t="n">
-        <v>6748587</v>
+        <v>6748208</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,7 +7457,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543053</v>
+        <v>129543047</v>
       </c>
       <c r="B65" t="n">
         <v>79044</v>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>458094</v>
+        <v>457952</v>
       </c>
       <c r="R65" t="n">
-        <v>6748667</v>
+        <v>6748501</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7564,7 +7564,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543029</v>
+        <v>129543019</v>
       </c>
       <c r="B66" t="n">
         <v>79044</v>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457780</v>
+        <v>457725</v>
       </c>
       <c r="R66" t="n">
-        <v>6748311</v>
+        <v>6748208</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7671,7 +7671,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543002</v>
+        <v>129543060</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457813</v>
+        <v>458177</v>
       </c>
       <c r="R67" t="n">
-        <v>6748191</v>
+        <v>6748587</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7778,7 +7778,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543047</v>
+        <v>129543029</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457952</v>
+        <v>457780</v>
       </c>
       <c r="R68" t="n">
-        <v>6748501</v>
+        <v>6748311</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7885,10 +7885,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543073</v>
+        <v>129542961</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7896,21 +7896,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457917</v>
+        <v>457859</v>
       </c>
       <c r="R69" t="n">
-        <v>6748303</v>
+        <v>6748231</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7992,10 +7992,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129542962</v>
+        <v>129543002</v>
       </c>
       <c r="B70" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8003,21 +8003,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457762</v>
+        <v>457813</v>
       </c>
       <c r="R70" t="n">
-        <v>6748208</v>
+        <v>6748191</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8099,7 +8099,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543019</v>
+        <v>129543053</v>
       </c>
       <c r="B71" t="n">
         <v>79044</v>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457725</v>
+        <v>458094</v>
       </c>
       <c r="R71" t="n">
-        <v>6748208</v>
+        <v>6748667</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8206,45 +8206,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129542961</v>
+        <v>129542952</v>
       </c>
       <c r="B72" t="n">
-        <v>78801</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457859</v>
+        <v>458156</v>
       </c>
       <c r="R72" t="n">
-        <v>6748231</v>
+        <v>6748545</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,7 +8281,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8286,7 +8291,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8313,50 +8318,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129542952</v>
+        <v>129543097</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458156</v>
+        <v>457673</v>
       </c>
       <c r="R73" t="n">
-        <v>6748545</v>
+        <v>6748071</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8418,17 +8418,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543000</v>
+        <v>129542933</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8436,34 +8436,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457846</v>
+        <v>457753</v>
       </c>
       <c r="R74" t="n">
-        <v>6748214</v>
+        <v>6748178</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8495,7 +8500,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8505,7 +8510,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8632,14 +8637,14 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129542999</v>
+        <v>129543000</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8674,10 +8679,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457883</v>
+        <v>457846</v>
       </c>
       <c r="R76" t="n">
-        <v>6748260</v>
+        <v>6748214</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,7 +8714,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8719,7 +8724,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8746,7 +8751,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543075</v>
+        <v>129542999</v>
       </c>
       <c r="B77" t="n">
         <v>79044</v>
@@ -8781,10 +8786,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457896</v>
+        <v>457883</v>
       </c>
       <c r="R77" t="n">
-        <v>6748336</v>
+        <v>6748260</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8816,7 +8821,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8826,7 +8831,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8846,17 +8851,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129542933</v>
+        <v>129543075</v>
       </c>
       <c r="B78" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8864,39 +8869,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457753</v>
+        <v>457896</v>
       </c>
       <c r="R78" t="n">
-        <v>6748178</v>
+        <v>6748336</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9386,14 +9386,14 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543065</v>
+        <v>129542991</v>
       </c>
       <c r="B83" t="n">
         <v>79044</v>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>458039</v>
+        <v>457762</v>
       </c>
       <c r="R83" t="n">
-        <v>6748504</v>
+        <v>6748312</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9493,17 +9493,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129542991</v>
+        <v>129542964</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9511,21 +9511,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457762</v>
+        <v>457767</v>
       </c>
       <c r="R84" t="n">
-        <v>6748312</v>
+        <v>6748250</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9607,7 +9607,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129542964</v>
+        <v>129542968</v>
       </c>
       <c r="B85" t="n">
         <v>78801</v>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>457767</v>
+        <v>458060</v>
       </c>
       <c r="R85" t="n">
-        <v>6748250</v>
+        <v>6748629</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9714,10 +9714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129542968</v>
+        <v>129543065</v>
       </c>
       <c r="B86" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9725,21 +9725,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458060</v>
+        <v>458039</v>
       </c>
       <c r="R86" t="n">
-        <v>6748629</v>
+        <v>6748504</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9814,17 +9814,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543028</v>
+        <v>129543085</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9832,21 +9832,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457753</v>
+        <v>457880</v>
       </c>
       <c r="R87" t="n">
-        <v>6748290</v>
+        <v>6748247</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9901,7 +9901,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På högstubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9921,7 +9926,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10028,17 +10033,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543085</v>
+        <v>129543049</v>
       </c>
       <c r="B89" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10046,21 +10051,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10070,10 +10075,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457880</v>
+        <v>458018</v>
       </c>
       <c r="R89" t="n">
-        <v>6748247</v>
+        <v>6748602</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10105,7 +10110,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10115,12 +10120,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På högstubbe med fem brandljud</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10147,7 +10147,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543049</v>
+        <v>129543028</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458018</v>
+        <v>457753</v>
       </c>
       <c r="R90" t="n">
-        <v>6748602</v>
+        <v>6748290</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10254,45 +10254,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129542939</v>
+        <v>129542969</v>
       </c>
       <c r="B91" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457660</v>
+        <v>457879</v>
       </c>
       <c r="R91" t="n">
-        <v>6748092</v>
+        <v>6748454</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10324,7 +10333,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10334,7 +10343,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10361,54 +10370,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129542969</v>
+        <v>129542939</v>
       </c>
       <c r="B92" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457879</v>
+        <v>457660</v>
       </c>
       <c r="R92" t="n">
-        <v>6748454</v>
+        <v>6748092</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10477,10 +10477,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543099</v>
+        <v>129542956</v>
       </c>
       <c r="B93" t="n">
-        <v>78710</v>
+        <v>81029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10488,21 +10488,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457650</v>
+        <v>457662</v>
       </c>
       <c r="R93" t="n">
-        <v>6748064</v>
+        <v>6748216</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10584,7 +10584,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543104</v>
+        <v>129543099</v>
       </c>
       <c r="B94" t="n">
         <v>78710</v>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457992</v>
+        <v>457650</v>
       </c>
       <c r="R94" t="n">
-        <v>6748556</v>
+        <v>6748064</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10684,17 +10684,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129542956</v>
+        <v>129543104</v>
       </c>
       <c r="B95" t="n">
-        <v>81029</v>
+        <v>78710</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10702,21 +10702,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457662</v>
+        <v>457992</v>
       </c>
       <c r="R95" t="n">
-        <v>6748216</v>
+        <v>6748556</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10898,14 +10898,14 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543020</v>
+        <v>129543014</v>
       </c>
       <c r="B97" t="n">
         <v>79044</v>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457738</v>
+        <v>457634</v>
       </c>
       <c r="R97" t="n">
-        <v>6748205</v>
+        <v>6748179</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,7 +11012,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543013</v>
+        <v>129543037</v>
       </c>
       <c r="B98" t="n">
         <v>79044</v>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457621</v>
+        <v>457830</v>
       </c>
       <c r="R98" t="n">
-        <v>6748147</v>
+        <v>6748350</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,7 +11119,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543062</v>
+        <v>129543013</v>
       </c>
       <c r="B99" t="n">
         <v>79044</v>
@@ -11154,10 +11154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458140</v>
+        <v>457621</v>
       </c>
       <c r="R99" t="n">
-        <v>6748536</v>
+        <v>6748147</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,7 +11226,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543014</v>
+        <v>129543039</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457634</v>
+        <v>457830</v>
       </c>
       <c r="R100" t="n">
-        <v>6748179</v>
+        <v>6748402</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,7 +11333,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543037</v>
+        <v>129543030</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -11368,10 +11368,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457830</v>
+        <v>457811</v>
       </c>
       <c r="R101" t="n">
-        <v>6748350</v>
+        <v>6748293</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11440,7 +11440,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543039</v>
+        <v>129543020</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11475,10 +11475,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457830</v>
+        <v>457738</v>
       </c>
       <c r="R102" t="n">
-        <v>6748402</v>
+        <v>6748205</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11547,7 +11547,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543030</v>
+        <v>129543016</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -11582,10 +11582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457811</v>
+        <v>457699</v>
       </c>
       <c r="R103" t="n">
-        <v>6748293</v>
+        <v>6748197</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11654,7 +11654,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543016</v>
+        <v>129543062</v>
       </c>
       <c r="B104" t="n">
         <v>79044</v>
@@ -11689,10 +11689,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457699</v>
+        <v>458140</v>
       </c>
       <c r="R104" t="n">
-        <v>6748197</v>
+        <v>6748536</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11973,39 +11973,39 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129542981</v>
+        <v>129543095</v>
       </c>
       <c r="B107" t="n">
-        <v>91726</v>
+        <v>78710</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457964</v>
+        <v>457704</v>
       </c>
       <c r="R107" t="n">
-        <v>6748415</v>
+        <v>6748074</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12080,14 +12080,14 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129543095</v>
+        <v>129543096</v>
       </c>
       <c r="B108" t="n">
         <v>78710</v>
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457704</v>
+        <v>457671</v>
       </c>
       <c r="R108" t="n">
-        <v>6748074</v>
+        <v>6748048</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12187,17 +12187,17 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543096</v>
+        <v>129543012</v>
       </c>
       <c r="B109" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12205,21 +12205,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12229,10 +12229,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457671</v>
+        <v>457625</v>
       </c>
       <c r="R109" t="n">
-        <v>6748048</v>
+        <v>6748127</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12301,45 +12301,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543012</v>
+        <v>129543111</v>
       </c>
       <c r="B110" t="n">
-        <v>79044</v>
+        <v>5177</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457625</v>
+        <v>457665</v>
       </c>
       <c r="R110" t="n">
-        <v>6748127</v>
+        <v>6748081</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12371,7 +12376,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12381,7 +12386,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12401,57 +12406,52 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543111</v>
+        <v>129542981</v>
       </c>
       <c r="B111" t="n">
-        <v>5177</v>
+        <v>91726</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100526</v>
+        <v>1503</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457665</v>
+        <v>457964</v>
       </c>
       <c r="R111" t="n">
-        <v>6748081</v>
+        <v>6748415</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12513,17 +12513,17 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129543011</v>
+        <v>129542923</v>
       </c>
       <c r="B112" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12531,21 +12531,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>457665</v>
+        <v>457773</v>
       </c>
       <c r="R112" t="n">
-        <v>6748082</v>
+        <v>6748248</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12627,10 +12627,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129543008</v>
+        <v>129542935</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12638,34 +12638,39 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457671</v>
+        <v>458060</v>
       </c>
       <c r="R113" t="n">
-        <v>6748048</v>
+        <v>6748631</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12697,7 +12702,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12707,7 +12712,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12734,10 +12739,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129542935</v>
+        <v>129543008</v>
       </c>
       <c r="B114" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12745,39 +12750,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458060</v>
+        <v>457671</v>
       </c>
       <c r="R114" t="n">
-        <v>6748631</v>
+        <v>6748048</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12846,10 +12846,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129542923</v>
+        <v>129542955</v>
       </c>
       <c r="B115" t="n">
-        <v>79139</v>
+        <v>92195</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12857,21 +12857,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>967</v>
+        <v>5454</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12881,10 +12881,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457773</v>
+        <v>458015</v>
       </c>
       <c r="R115" t="n">
-        <v>6748248</v>
+        <v>6748399</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12953,10 +12953,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129542955</v>
+        <v>129543011</v>
       </c>
       <c r="B116" t="n">
-        <v>92195</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12964,21 +12964,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5454</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>458015</v>
+        <v>457665</v>
       </c>
       <c r="R116" t="n">
-        <v>6748399</v>
+        <v>6748082</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13167,7 +13167,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129543054</v>
+        <v>129543061</v>
       </c>
       <c r="B118" t="n">
         <v>79044</v>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458097</v>
+        <v>458155</v>
       </c>
       <c r="R118" t="n">
-        <v>6748662</v>
+        <v>6748548</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13274,7 +13274,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129543061</v>
+        <v>129543054</v>
       </c>
       <c r="B119" t="n">
         <v>79044</v>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458155</v>
+        <v>458097</v>
       </c>
       <c r="R119" t="n">
-        <v>6748548</v>
+        <v>6748662</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13344,7 +13344,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13493,10 +13493,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129543102</v>
+        <v>129543046</v>
       </c>
       <c r="B121" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13504,21 +13504,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>457761</v>
+        <v>457946</v>
       </c>
       <c r="R121" t="n">
-        <v>6748256</v>
+        <v>6748493</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13600,10 +13600,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129543004</v>
+        <v>129542967</v>
       </c>
       <c r="B122" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>457802</v>
+        <v>457939</v>
       </c>
       <c r="R122" t="n">
-        <v>6748157</v>
+        <v>6748494</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13707,7 +13707,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129543046</v>
+        <v>129543048</v>
       </c>
       <c r="B123" t="n">
         <v>79044</v>
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>457946</v>
+        <v>457954</v>
       </c>
       <c r="R123" t="n">
-        <v>6748493</v>
+        <v>6748541</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13814,7 +13814,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129543025</v>
+        <v>129543004</v>
       </c>
       <c r="B124" t="n">
         <v>79044</v>
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>457761</v>
+        <v>457802</v>
       </c>
       <c r="R124" t="n">
-        <v>6748254</v>
+        <v>6748157</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13921,7 +13921,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129543027</v>
+        <v>129543025</v>
       </c>
       <c r="B125" t="n">
         <v>79044</v>
@@ -13956,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>457756</v>
+        <v>457761</v>
       </c>
       <c r="R125" t="n">
-        <v>6748271</v>
+        <v>6748254</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14028,7 +14028,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129543048</v>
+        <v>129543015</v>
       </c>
       <c r="B126" t="n">
         <v>79044</v>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457954</v>
+        <v>457689</v>
       </c>
       <c r="R126" t="n">
-        <v>6748541</v>
+        <v>6748165</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14135,7 +14135,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129543015</v>
+        <v>129542978</v>
       </c>
       <c r="B127" t="n">
         <v>79044</v>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>457689</v>
+        <v>457802</v>
       </c>
       <c r="R127" t="n">
-        <v>6748165</v>
+        <v>6748301</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14235,17 +14235,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129542967</v>
+        <v>129543027</v>
       </c>
       <c r="B128" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14253,21 +14253,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457939</v>
+        <v>457756</v>
       </c>
       <c r="R128" t="n">
-        <v>6748494</v>
+        <v>6748271</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14349,10 +14349,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129542978</v>
+        <v>129543102</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14360,21 +14360,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14384,10 +14384,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>457802</v>
+        <v>457761</v>
       </c>
       <c r="R129" t="n">
-        <v>6748301</v>
+        <v>6748256</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14675,32 +14675,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129542920</v>
+        <v>129543036</v>
       </c>
       <c r="B132" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457964</v>
+        <v>457843</v>
       </c>
       <c r="R132" t="n">
-        <v>6748415</v>
+        <v>6748341</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14782,7 +14782,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129543036</v>
+        <v>129543058</v>
       </c>
       <c r="B133" t="n">
         <v>79044</v>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457843</v>
+        <v>458143</v>
       </c>
       <c r="R133" t="n">
-        <v>6748341</v>
+        <v>6748611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14889,7 +14889,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129543058</v>
+        <v>129543077</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>458143</v>
+        <v>457938</v>
       </c>
       <c r="R134" t="n">
-        <v>6748611</v>
+        <v>6748409</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14989,14 +14989,14 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129543044</v>
+        <v>129543040</v>
       </c>
       <c r="B135" t="n">
         <v>79044</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457939</v>
+        <v>457817</v>
       </c>
       <c r="R135" t="n">
-        <v>6748453</v>
+        <v>6748400</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15103,7 +15103,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129543040</v>
+        <v>129543044</v>
       </c>
       <c r="B136" t="n">
         <v>79044</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>457817</v>
+        <v>457939</v>
       </c>
       <c r="R136" t="n">
-        <v>6748400</v>
+        <v>6748453</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15210,7 +15210,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129543077</v>
+        <v>129543050</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>457938</v>
+        <v>458067</v>
       </c>
       <c r="R137" t="n">
-        <v>6748409</v>
+        <v>6748648</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15317,32 +15317,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129542916</v>
+        <v>129542920</v>
       </c>
       <c r="B138" t="n">
-        <v>79663</v>
+        <v>91517</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>457750</v>
+        <v>457964</v>
       </c>
       <c r="R138" t="n">
-        <v>6748276</v>
+        <v>6748415</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15424,10 +15424,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129543050</v>
+        <v>129542916</v>
       </c>
       <c r="B139" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15435,21 +15435,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>458067</v>
+        <v>457750</v>
       </c>
       <c r="R139" t="n">
-        <v>6748648</v>
+        <v>6748276</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15531,10 +15531,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129543089</v>
+        <v>129542958</v>
       </c>
       <c r="B140" t="n">
-        <v>78710</v>
+        <v>81029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>457809</v>
+        <v>458029</v>
       </c>
       <c r="R140" t="n">
-        <v>6748254</v>
+        <v>6748402</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15638,10 +15638,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129542958</v>
+        <v>129543089</v>
       </c>
       <c r="B141" t="n">
-        <v>81029</v>
+        <v>78710</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>458029</v>
+        <v>457809</v>
       </c>
       <c r="R141" t="n">
-        <v>6748402</v>
+        <v>6748254</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15852,10 +15852,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129542965</v>
+        <v>129543074</v>
       </c>
       <c r="B143" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15863,21 +15863,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457760</v>
+        <v>457905</v>
       </c>
       <c r="R143" t="n">
-        <v>6748255</v>
+        <v>6748321</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15952,17 +15952,17 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129543022</v>
+        <v>129542965</v>
       </c>
       <c r="B144" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15970,21 +15970,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457761</v>
+        <v>457760</v>
       </c>
       <c r="R144" t="n">
-        <v>6748192</v>
+        <v>6748255</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16066,7 +16066,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129543074</v>
+        <v>129543022</v>
       </c>
       <c r="B145" t="n">
         <v>79044</v>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>457905</v>
+        <v>457761</v>
       </c>
       <c r="R145" t="n">
-        <v>6748321</v>
+        <v>6748192</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16280,32 +16280,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129542941</v>
+        <v>129543100</v>
       </c>
       <c r="B147" t="n">
-        <v>97598</v>
+        <v>78710</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457929</v>
+        <v>457631</v>
       </c>
       <c r="R147" t="n">
-        <v>6748448</v>
+        <v>6748174</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16594,14 +16594,14 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129543023</v>
+        <v>129543006</v>
       </c>
       <c r="B150" t="n">
         <v>79044</v>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457758</v>
+        <v>457712</v>
       </c>
       <c r="R150" t="n">
-        <v>6748213</v>
+        <v>6748081</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16708,10 +16708,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129543100</v>
+        <v>129543023</v>
       </c>
       <c r="B151" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16719,21 +16719,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16743,10 +16743,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457631</v>
+        <v>457758</v>
       </c>
       <c r="R151" t="n">
-        <v>6748174</v>
+        <v>6748213</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16815,32 +16815,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129543006</v>
+        <v>129542941</v>
       </c>
       <c r="B152" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457712</v>
+        <v>457929</v>
       </c>
       <c r="R152" t="n">
-        <v>6748081</v>
+        <v>6748448</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129542980</v>
+        <v>129542945</v>
       </c>
       <c r="B153" t="n">
-        <v>91726</v>
+        <v>97604</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>458058</v>
+        <v>457654</v>
       </c>
       <c r="R153" t="n">
-        <v>6748621</v>
+        <v>6748079</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17029,32 +17029,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129542959</v>
+        <v>129542943</v>
       </c>
       <c r="B154" t="n">
-        <v>81029</v>
+        <v>97598</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1049</v>
+        <v>221945</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457884</v>
+        <v>457999</v>
       </c>
       <c r="R154" t="n">
-        <v>6748404</v>
+        <v>6748381</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17236,7 +17236,7 @@
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -17457,32 +17457,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129542945</v>
+        <v>129542980</v>
       </c>
       <c r="B158" t="n">
-        <v>97604</v>
+        <v>91726</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221941</v>
+        <v>1503</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457654</v>
+        <v>458058</v>
       </c>
       <c r="R158" t="n">
-        <v>6748079</v>
+        <v>6748621</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17557,39 +17557,39 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129542943</v>
+        <v>129542959</v>
       </c>
       <c r="B159" t="n">
-        <v>97598</v>
+        <v>81029</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221945</v>
+        <v>1049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457999</v>
+        <v>457884</v>
       </c>
       <c r="R159" t="n">
-        <v>6748381</v>
+        <v>6748404</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129543007</v>
+        <v>129543108</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457677</v>
+        <v>458131</v>
       </c>
       <c r="R2" t="n">
-        <v>6748051</v>
+        <v>6748548</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129542925</v>
+        <v>129542951</v>
       </c>
       <c r="B8" t="n">
-        <v>56917</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,27 +1328,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457896</v>
+        <v>457817</v>
       </c>
       <c r="R8" t="n">
-        <v>6748335</v>
+        <v>6748352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543108</v>
+        <v>129543007</v>
       </c>
       <c r="B9" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458131</v>
+        <v>457677</v>
       </c>
       <c r="R9" t="n">
-        <v>6748548</v>
+        <v>6748051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129542951</v>
+        <v>129542925</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>56917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,27 +1547,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457817</v>
+        <v>457896</v>
       </c>
       <c r="R10" t="n">
-        <v>6748352</v>
+        <v>6748335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129542928</v>
+        <v>129543091</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>78710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,39 +1659,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457940</v>
+        <v>457817</v>
       </c>
       <c r="R11" t="n">
-        <v>6748387</v>
+        <v>6748202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543043</v>
+        <v>129543092</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457927</v>
+        <v>457785</v>
       </c>
       <c r="R12" t="n">
-        <v>6748447</v>
+        <v>6748160</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129542992</v>
+        <v>129542924</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457763</v>
+        <v>457899</v>
       </c>
       <c r="R13" t="n">
-        <v>6748301</v>
+        <v>6748444</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,14 +1962,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543017</v>
+        <v>129543043</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -2009,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457657</v>
+        <v>457927</v>
       </c>
       <c r="R14" t="n">
-        <v>6748226</v>
+        <v>6748447</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543070</v>
+        <v>129542928</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,34 +2087,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457936</v>
+        <v>457940</v>
       </c>
       <c r="R15" t="n">
-        <v>6748379</v>
+        <v>6748387</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129542924</v>
+        <v>129542992</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457899</v>
+        <v>457763</v>
       </c>
       <c r="R16" t="n">
-        <v>6748444</v>
+        <v>6748301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,32 +2295,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543081</v>
+        <v>129543017</v>
       </c>
       <c r="B17" t="n">
-        <v>91826</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458131</v>
+        <v>457657</v>
       </c>
       <c r="R17" t="n">
-        <v>6748547</v>
+        <v>6748226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543091</v>
+        <v>129543070</v>
       </c>
       <c r="B18" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,21 +2413,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457817</v>
+        <v>457936</v>
       </c>
       <c r="R18" t="n">
-        <v>6748202</v>
+        <v>6748379</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543092</v>
+        <v>129542995</v>
       </c>
       <c r="B19" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457785</v>
+        <v>457809</v>
       </c>
       <c r="R19" t="n">
-        <v>6748160</v>
+        <v>6748246</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,39 +2609,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129542915</v>
+        <v>129543081</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>91826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457754</v>
+        <v>458131</v>
       </c>
       <c r="R20" t="n">
-        <v>6748230</v>
+        <v>6748547</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129542995</v>
+        <v>129542915</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457809</v>
+        <v>457754</v>
       </c>
       <c r="R21" t="n">
-        <v>6748246</v>
+        <v>6748230</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543107</v>
+        <v>129543005</v>
       </c>
       <c r="B22" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458144</v>
+        <v>457775</v>
       </c>
       <c r="R22" t="n">
-        <v>6748538</v>
+        <v>6748148</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2930,17 +2930,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129542913</v>
+        <v>129543032</v>
       </c>
       <c r="B23" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457761</v>
+        <v>457821</v>
       </c>
       <c r="R23" t="n">
-        <v>6748133</v>
+        <v>6748297</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129542996</v>
+        <v>129542982</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457833</v>
+        <v>457941</v>
       </c>
       <c r="R24" t="n">
-        <v>6748233</v>
+        <v>6748477</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3124,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,17 +3149,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543038</v>
+        <v>129543107</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3162,21 +3167,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3186,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457829</v>
+        <v>458144</v>
       </c>
       <c r="R25" t="n">
-        <v>6748366</v>
+        <v>6748538</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,7 +3263,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543005</v>
+        <v>129542996</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3293,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457775</v>
+        <v>457833</v>
       </c>
       <c r="R26" t="n">
-        <v>6748148</v>
+        <v>6748233</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3343,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,7 +3370,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543051</v>
+        <v>129543038</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3400,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458077</v>
+        <v>457829</v>
       </c>
       <c r="R27" t="n">
-        <v>6748657</v>
+        <v>6748366</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,7 +3440,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3450,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,7 +3477,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543045</v>
+        <v>129543051</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3507,10 +3512,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457912</v>
+        <v>458077</v>
       </c>
       <c r="R28" t="n">
-        <v>6748485</v>
+        <v>6748657</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,7 +3584,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543032</v>
+        <v>129543045</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3614,10 +3619,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457821</v>
+        <v>457912</v>
       </c>
       <c r="R29" t="n">
-        <v>6748297</v>
+        <v>6748485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,7 +3654,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3664,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,10 +3691,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129542982</v>
+        <v>129542913</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3697,21 +3702,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3721,10 +3726,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457941</v>
+        <v>457761</v>
       </c>
       <c r="R30" t="n">
-        <v>6748477</v>
+        <v>6748133</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3756,7 +3761,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,12 +3771,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543018</v>
+        <v>129543090</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457679</v>
+        <v>457883</v>
       </c>
       <c r="R31" t="n">
-        <v>6748231</v>
+        <v>6748264</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3905,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129542966</v>
+        <v>129543018</v>
       </c>
       <c r="B32" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,21 +3916,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457938</v>
+        <v>457679</v>
       </c>
       <c r="R32" t="n">
-        <v>6748466</v>
+        <v>6748231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543063</v>
+        <v>129542966</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458116</v>
+        <v>457938</v>
       </c>
       <c r="R33" t="n">
-        <v>6748548</v>
+        <v>6748466</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,7 +4119,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543059</v>
+        <v>129543063</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458174</v>
+        <v>458116</v>
       </c>
       <c r="R34" t="n">
-        <v>6748599</v>
+        <v>6748548</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,7 +4226,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543021</v>
+        <v>129543059</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457756</v>
+        <v>458174</v>
       </c>
       <c r="R35" t="n">
-        <v>6748192</v>
+        <v>6748599</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129542993</v>
+        <v>129543021</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457763</v>
+        <v>457756</v>
       </c>
       <c r="R36" t="n">
-        <v>6748294</v>
+        <v>6748192</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4433,57 +4433,52 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129542949</v>
+        <v>129542993</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457627</v>
+        <v>457763</v>
       </c>
       <c r="R37" t="n">
-        <v>6748161</v>
+        <v>6748294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4515,7 +4510,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4525,7 +4520,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4552,45 +4547,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543090</v>
+        <v>129542949</v>
       </c>
       <c r="B38" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457883</v>
+        <v>457627</v>
       </c>
       <c r="R38" t="n">
-        <v>6748264</v>
+        <v>6748161</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4766,32 +4766,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543112</v>
+        <v>129543003</v>
       </c>
       <c r="B40" t="n">
-        <v>91610</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458029</v>
+        <v>457814</v>
       </c>
       <c r="R40" t="n">
-        <v>6748411</v>
+        <v>6748175</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4855,7 +4855,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4867,17 +4866,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129542927</v>
+        <v>129543071</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4885,39 +4884,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458027</v>
+        <v>457928</v>
       </c>
       <c r="R41" t="n">
-        <v>6748413</v>
+        <v>6748344</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4949,7 +4943,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4959,7 +4953,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4986,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129542946</v>
+        <v>129542998</v>
       </c>
       <c r="B42" t="n">
-        <v>91606</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5021,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458035</v>
+        <v>457876</v>
       </c>
       <c r="R42" t="n">
-        <v>6748395</v>
+        <v>6748240</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5056,7 +5050,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5066,7 +5060,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5093,10 +5087,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543098</v>
+        <v>129543057</v>
       </c>
       <c r="B43" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,21 +5098,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5128,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457657</v>
+        <v>458134</v>
       </c>
       <c r="R43" t="n">
-        <v>6748066</v>
+        <v>6748614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,7 +5157,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5173,7 +5167,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5193,17 +5187,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543093</v>
+        <v>129542927</v>
       </c>
       <c r="B44" t="n">
-        <v>78710</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5211,34 +5205,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457737</v>
+        <v>458027</v>
       </c>
       <c r="R44" t="n">
-        <v>6748103</v>
+        <v>6748413</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5270,7 +5269,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5280,7 +5279,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5300,17 +5299,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543071</v>
+        <v>129543098</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,21 +5317,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5342,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457928</v>
+        <v>457657</v>
       </c>
       <c r="R45" t="n">
-        <v>6748344</v>
+        <v>6748066</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5377,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5387,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5407,17 +5406,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129542998</v>
+        <v>129543093</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5425,21 +5424,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5449,10 +5448,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457876</v>
+        <v>457737</v>
       </c>
       <c r="R46" t="n">
-        <v>6748240</v>
+        <v>6748103</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5484,7 +5483,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5494,7 +5493,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5514,17 +5513,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543003</v>
+        <v>129542946</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>91606</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5532,21 +5531,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5556,10 +5555,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457814</v>
+        <v>458035</v>
       </c>
       <c r="R47" t="n">
-        <v>6748175</v>
+        <v>6748395</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5591,7 +5590,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5601,7 +5600,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,32 +5627,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543057</v>
+        <v>129543112</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91610</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>458134</v>
+        <v>458029</v>
       </c>
       <c r="R48" t="n">
-        <v>6748614</v>
+        <v>6748411</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5698,7 +5697,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5708,7 +5707,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5717,6 +5716,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543009</v>
+        <v>129543082</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457654</v>
+        <v>457792</v>
       </c>
       <c r="R49" t="n">
-        <v>6748079</v>
+        <v>6748260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5842,10 +5842,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543082</v>
+        <v>129543010</v>
       </c>
       <c r="B50" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457792</v>
+        <v>457656</v>
       </c>
       <c r="R50" t="n">
-        <v>6748260</v>
+        <v>6748084</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5942,14 +5942,14 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543078</v>
+        <v>129543009</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457875</v>
+        <v>457654</v>
       </c>
       <c r="R51" t="n">
-        <v>6748394</v>
+        <v>6748079</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6049,14 +6049,14 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543010</v>
+        <v>129543078</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457656</v>
+        <v>457875</v>
       </c>
       <c r="R52" t="n">
-        <v>6748084</v>
+        <v>6748394</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6163,7 +6163,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543034</v>
+        <v>129543001</v>
       </c>
       <c r="B53" t="n">
         <v>79044</v>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457852</v>
+        <v>457838</v>
       </c>
       <c r="R53" t="n">
-        <v>6748316</v>
+        <v>6748208</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6270,7 +6270,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543064</v>
+        <v>129543035</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>458049</v>
+        <v>457845</v>
       </c>
       <c r="R54" t="n">
-        <v>6748509</v>
+        <v>6748327</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6370,14 +6370,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543042</v>
+        <v>129543066</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457922</v>
+        <v>458042</v>
       </c>
       <c r="R55" t="n">
-        <v>6748447</v>
+        <v>6748499</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6484,10 +6484,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543072</v>
+        <v>129542914</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6495,21 +6495,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457899</v>
+        <v>457650</v>
       </c>
       <c r="R56" t="n">
-        <v>6748357</v>
+        <v>6748064</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6584,14 +6584,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543035</v>
+        <v>129543034</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457845</v>
+        <v>457852</v>
       </c>
       <c r="R57" t="n">
-        <v>6748327</v>
+        <v>6748316</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6698,7 +6698,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543066</v>
+        <v>129543064</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458042</v>
+        <v>458049</v>
       </c>
       <c r="R58" t="n">
-        <v>6748499</v>
+        <v>6748509</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6798,17 +6798,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129542914</v>
+        <v>129543042</v>
       </c>
       <c r="B59" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6816,21 +6816,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457650</v>
+        <v>457922</v>
       </c>
       <c r="R59" t="n">
-        <v>6748064</v>
+        <v>6748447</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,50 +6912,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129542948</v>
+        <v>129543072</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457777</v>
+        <v>457899</v>
       </c>
       <c r="R60" t="n">
-        <v>6748294</v>
+        <v>6748357</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6987,7 +6982,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6997,7 +6992,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7136,45 +7131,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543001</v>
+        <v>129542948</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457838</v>
+        <v>457777</v>
       </c>
       <c r="R62" t="n">
-        <v>6748208</v>
+        <v>6748294</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7243,10 +7243,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543073</v>
+        <v>129543097</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457917</v>
+        <v>457673</v>
       </c>
       <c r="R63" t="n">
-        <v>6748303</v>
+        <v>6748071</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7343,17 +7343,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129542962</v>
+        <v>129543073</v>
       </c>
       <c r="B64" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7361,21 +7361,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457762</v>
+        <v>457917</v>
       </c>
       <c r="R64" t="n">
-        <v>6748208</v>
+        <v>6748303</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7564,7 +7564,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543019</v>
+        <v>129543002</v>
       </c>
       <c r="B66" t="n">
         <v>79044</v>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457725</v>
+        <v>457813</v>
       </c>
       <c r="R66" t="n">
-        <v>6748208</v>
+        <v>6748191</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7671,7 +7671,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543060</v>
+        <v>129543029</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458177</v>
+        <v>457780</v>
       </c>
       <c r="R67" t="n">
-        <v>6748587</v>
+        <v>6748311</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7778,7 +7778,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543029</v>
+        <v>129543053</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457780</v>
+        <v>458094</v>
       </c>
       <c r="R68" t="n">
-        <v>6748311</v>
+        <v>6748667</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7885,45 +7885,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129542961</v>
+        <v>129542952</v>
       </c>
       <c r="B69" t="n">
-        <v>78801</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457859</v>
+        <v>458156</v>
       </c>
       <c r="R69" t="n">
-        <v>6748231</v>
+        <v>6748545</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7955,7 +7960,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7965,7 +7970,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7992,10 +7997,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543002</v>
+        <v>129542962</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8003,21 +8008,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8027,10 +8032,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457813</v>
+        <v>457762</v>
       </c>
       <c r="R70" t="n">
-        <v>6748191</v>
+        <v>6748208</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8062,7 +8067,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8072,7 +8077,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8099,7 +8104,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543053</v>
+        <v>129543019</v>
       </c>
       <c r="B71" t="n">
         <v>79044</v>
@@ -8134,10 +8139,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458094</v>
+        <v>457725</v>
       </c>
       <c r="R71" t="n">
-        <v>6748667</v>
+        <v>6748208</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8169,7 +8174,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8179,7 +8184,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8206,50 +8211,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129542952</v>
+        <v>129543060</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458156</v>
+        <v>458177</v>
       </c>
       <c r="R72" t="n">
-        <v>6748545</v>
+        <v>6748587</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8318,10 +8318,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543097</v>
+        <v>129542961</v>
       </c>
       <c r="B73" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8329,21 +8329,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8353,10 +8353,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457673</v>
+        <v>457859</v>
       </c>
       <c r="R73" t="n">
-        <v>6748071</v>
+        <v>6748231</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8418,17 +8418,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129542933</v>
+        <v>129543101</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>78710</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8436,39 +8436,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457753</v>
+        <v>457746</v>
       </c>
       <c r="R74" t="n">
-        <v>6748178</v>
+        <v>6748232</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8500,7 +8495,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8510,7 +8505,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8537,10 +8532,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129542997</v>
+        <v>129543105</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8548,21 +8543,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8572,10 +8567,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457863</v>
+        <v>457993</v>
       </c>
       <c r="R75" t="n">
-        <v>6748231</v>
+        <v>6748571</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8607,7 +8602,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8617,7 +8612,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8637,14 +8632,14 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543000</v>
+        <v>129542997</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8679,10 +8674,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457846</v>
+        <v>457863</v>
       </c>
       <c r="R76" t="n">
-        <v>6748214</v>
+        <v>6748231</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8714,7 +8709,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8724,7 +8719,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8851,14 +8846,14 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543075</v>
+        <v>129543000</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8893,10 +8888,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457896</v>
+        <v>457846</v>
       </c>
       <c r="R78" t="n">
-        <v>6748336</v>
+        <v>6748214</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8928,7 +8923,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8938,7 +8933,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8958,17 +8953,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543101</v>
+        <v>129543075</v>
       </c>
       <c r="B79" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8976,21 +8971,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9000,10 +8995,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457746</v>
+        <v>457896</v>
       </c>
       <c r="R79" t="n">
-        <v>6748232</v>
+        <v>6748336</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9035,7 +9030,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9045,7 +9040,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9065,17 +9060,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543105</v>
+        <v>129542933</v>
       </c>
       <c r="B80" t="n">
-        <v>78710</v>
+        <v>57724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9083,34 +9078,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457993</v>
+        <v>457753</v>
       </c>
       <c r="R80" t="n">
-        <v>6748571</v>
+        <v>6748178</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9172,17 +9172,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543103</v>
+        <v>129542968</v>
       </c>
       <c r="B81" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457842</v>
+        <v>458060</v>
       </c>
       <c r="R81" t="n">
-        <v>6748363</v>
+        <v>6748629</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9279,17 +9279,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543088</v>
+        <v>129543065</v>
       </c>
       <c r="B82" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457797</v>
+        <v>458039</v>
       </c>
       <c r="R82" t="n">
-        <v>6748261</v>
+        <v>6748504</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9386,17 +9386,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129542991</v>
+        <v>129543103</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9404,21 +9404,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457762</v>
+        <v>457842</v>
       </c>
       <c r="R83" t="n">
-        <v>6748312</v>
+        <v>6748363</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9493,17 +9493,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129542964</v>
+        <v>129543088</v>
       </c>
       <c r="B84" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9511,21 +9511,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457767</v>
+        <v>457797</v>
       </c>
       <c r="R84" t="n">
-        <v>6748250</v>
+        <v>6748261</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9607,10 +9607,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129542968</v>
+        <v>129542991</v>
       </c>
       <c r="B85" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9618,21 +9618,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458060</v>
+        <v>457762</v>
       </c>
       <c r="R85" t="n">
-        <v>6748629</v>
+        <v>6748312</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9714,10 +9714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543065</v>
+        <v>129542964</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9725,21 +9725,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458039</v>
+        <v>457767</v>
       </c>
       <c r="R86" t="n">
-        <v>6748504</v>
+        <v>6748250</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10254,54 +10254,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129542969</v>
+        <v>129542939</v>
       </c>
       <c r="B91" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457879</v>
+        <v>457660</v>
       </c>
       <c r="R91" t="n">
-        <v>6748454</v>
+        <v>6748092</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10333,7 +10324,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10343,7 +10334,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10370,45 +10361,54 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129542939</v>
+        <v>129542969</v>
       </c>
       <c r="B92" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457660</v>
+        <v>457879</v>
       </c>
       <c r="R92" t="n">
-        <v>6748092</v>
+        <v>6748454</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10477,10 +10477,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129542956</v>
+        <v>129543013</v>
       </c>
       <c r="B93" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10488,21 +10488,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457662</v>
+        <v>457621</v>
       </c>
       <c r="R93" t="n">
-        <v>6748216</v>
+        <v>6748147</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10584,10 +10584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543099</v>
+        <v>129543014</v>
       </c>
       <c r="B94" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10595,21 +10595,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457650</v>
+        <v>457634</v>
       </c>
       <c r="R94" t="n">
-        <v>6748064</v>
+        <v>6748179</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10684,17 +10684,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543104</v>
+        <v>129543037</v>
       </c>
       <c r="B95" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10702,21 +10702,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457992</v>
+        <v>457830</v>
       </c>
       <c r="R95" t="n">
-        <v>6748556</v>
+        <v>6748350</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10791,17 +10791,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543083</v>
+        <v>129543020</v>
       </c>
       <c r="B96" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457757</v>
+        <v>457738</v>
       </c>
       <c r="R96" t="n">
-        <v>6748191</v>
+        <v>6748205</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10898,14 +10898,14 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543014</v>
+        <v>129543062</v>
       </c>
       <c r="B97" t="n">
         <v>79044</v>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457634</v>
+        <v>458140</v>
       </c>
       <c r="R97" t="n">
-        <v>6748179</v>
+        <v>6748536</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,10 +11012,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543037</v>
+        <v>129543099</v>
       </c>
       <c r="B98" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11023,21 +11023,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457830</v>
+        <v>457650</v>
       </c>
       <c r="R98" t="n">
-        <v>6748350</v>
+        <v>6748064</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543013</v>
+        <v>129543104</v>
       </c>
       <c r="B99" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11130,21 +11130,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11154,10 +11154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457621</v>
+        <v>457992</v>
       </c>
       <c r="R99" t="n">
-        <v>6748147</v>
+        <v>6748556</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,10 +11226,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543039</v>
+        <v>129542956</v>
       </c>
       <c r="B100" t="n">
-        <v>79044</v>
+        <v>81029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11237,21 +11237,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457830</v>
+        <v>457662</v>
       </c>
       <c r="R100" t="n">
-        <v>6748402</v>
+        <v>6748216</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,10 +11333,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543030</v>
+        <v>129543083</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11344,21 +11344,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11368,10 +11368,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457811</v>
+        <v>457757</v>
       </c>
       <c r="R101" t="n">
-        <v>6748293</v>
+        <v>6748191</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11440,7 +11440,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543020</v>
+        <v>129543039</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11475,10 +11475,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457738</v>
+        <v>457830</v>
       </c>
       <c r="R102" t="n">
-        <v>6748205</v>
+        <v>6748402</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11547,7 +11547,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543016</v>
+        <v>129543030</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -11582,10 +11582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457699</v>
+        <v>457811</v>
       </c>
       <c r="R103" t="n">
-        <v>6748197</v>
+        <v>6748293</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11654,7 +11654,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543062</v>
+        <v>129543016</v>
       </c>
       <c r="B104" t="n">
         <v>79044</v>
@@ -11689,10 +11689,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458140</v>
+        <v>457699</v>
       </c>
       <c r="R104" t="n">
-        <v>6748536</v>
+        <v>6748197</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12080,39 +12080,39 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129543096</v>
+        <v>129542981</v>
       </c>
       <c r="B108" t="n">
-        <v>78710</v>
+        <v>91726</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457671</v>
+        <v>457964</v>
       </c>
       <c r="R108" t="n">
-        <v>6748048</v>
+        <v>6748415</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12187,52 +12187,57 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543012</v>
+        <v>129543111</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>5177</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457625</v>
+        <v>457665</v>
       </c>
       <c r="R109" t="n">
-        <v>6748127</v>
+        <v>6748081</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12264,7 +12269,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12274,7 +12279,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12301,50 +12306,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543111</v>
+        <v>129543096</v>
       </c>
       <c r="B110" t="n">
-        <v>5177</v>
+        <v>78710</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457665</v>
+        <v>457671</v>
       </c>
       <c r="R110" t="n">
-        <v>6748081</v>
+        <v>6748048</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12406,39 +12406,39 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129542981</v>
+        <v>129543012</v>
       </c>
       <c r="B111" t="n">
-        <v>91726</v>
+        <v>79044</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457964</v>
+        <v>457625</v>
       </c>
       <c r="R111" t="n">
-        <v>6748415</v>
+        <v>6748127</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12513,17 +12513,17 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129542923</v>
+        <v>129542955</v>
       </c>
       <c r="B112" t="n">
-        <v>79139</v>
+        <v>92195</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12531,21 +12531,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>967</v>
+        <v>5454</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>457773</v>
+        <v>458015</v>
       </c>
       <c r="R112" t="n">
-        <v>6748248</v>
+        <v>6748399</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12627,10 +12627,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129542935</v>
+        <v>129543011</v>
       </c>
       <c r="B113" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12638,39 +12638,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458060</v>
+        <v>457665</v>
       </c>
       <c r="R113" t="n">
-        <v>6748631</v>
+        <v>6748082</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12702,7 +12697,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12712,7 +12707,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12846,10 +12841,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129542955</v>
+        <v>129542935</v>
       </c>
       <c r="B115" t="n">
-        <v>92195</v>
+        <v>57724</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12857,34 +12852,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458015</v>
+        <v>458060</v>
       </c>
       <c r="R115" t="n">
-        <v>6748399</v>
+        <v>6748631</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12953,10 +12953,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129543011</v>
+        <v>129542923</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12964,21 +12964,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457665</v>
+        <v>457773</v>
       </c>
       <c r="R116" t="n">
-        <v>6748082</v>
+        <v>6748248</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13167,7 +13167,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129543061</v>
+        <v>129543054</v>
       </c>
       <c r="B118" t="n">
         <v>79044</v>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458155</v>
+        <v>458097</v>
       </c>
       <c r="R118" t="n">
-        <v>6748548</v>
+        <v>6748662</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13274,45 +13274,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129543054</v>
+        <v>129542947</v>
       </c>
       <c r="B119" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458097</v>
+        <v>457929</v>
       </c>
       <c r="R119" t="n">
-        <v>6748662</v>
+        <v>6748484</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13344,7 +13349,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13354,7 +13359,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13381,50 +13386,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129542947</v>
+        <v>129543061</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>457929</v>
+        <v>458155</v>
       </c>
       <c r="R120" t="n">
-        <v>6748484</v>
+        <v>6748548</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13600,10 +13600,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129542967</v>
+        <v>129543048</v>
       </c>
       <c r="B122" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>457939</v>
+        <v>457954</v>
       </c>
       <c r="R122" t="n">
-        <v>6748494</v>
+        <v>6748541</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13707,7 +13707,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129543048</v>
+        <v>129543004</v>
       </c>
       <c r="B123" t="n">
         <v>79044</v>
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>457954</v>
+        <v>457802</v>
       </c>
       <c r="R123" t="n">
-        <v>6748541</v>
+        <v>6748157</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13814,7 +13814,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129543004</v>
+        <v>129543025</v>
       </c>
       <c r="B124" t="n">
         <v>79044</v>
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>457802</v>
+        <v>457761</v>
       </c>
       <c r="R124" t="n">
-        <v>6748157</v>
+        <v>6748254</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13921,7 +13921,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129543025</v>
+        <v>129543015</v>
       </c>
       <c r="B125" t="n">
         <v>79044</v>
@@ -13956,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>457761</v>
+        <v>457689</v>
       </c>
       <c r="R125" t="n">
-        <v>6748254</v>
+        <v>6748165</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14028,7 +14028,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129543015</v>
+        <v>129543027</v>
       </c>
       <c r="B126" t="n">
         <v>79044</v>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457689</v>
+        <v>457756</v>
       </c>
       <c r="R126" t="n">
-        <v>6748165</v>
+        <v>6748271</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14135,10 +14135,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129542978</v>
+        <v>129542936</v>
       </c>
       <c r="B127" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14146,34 +14146,39 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>457802</v>
+        <v>458155</v>
       </c>
       <c r="R127" t="n">
-        <v>6748301</v>
+        <v>6748562</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14205,7 +14210,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14215,7 +14220,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14235,17 +14240,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129543027</v>
+        <v>129543102</v>
       </c>
       <c r="B128" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14253,21 +14258,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14277,10 +14282,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457756</v>
+        <v>457761</v>
       </c>
       <c r="R128" t="n">
-        <v>6748271</v>
+        <v>6748256</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14349,10 +14354,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129543102</v>
+        <v>129542978</v>
       </c>
       <c r="B129" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14360,21 +14365,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14384,10 +14389,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>457761</v>
+        <v>457802</v>
       </c>
       <c r="R129" t="n">
-        <v>6748256</v>
+        <v>6748301</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14419,7 +14424,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14429,7 +14434,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14449,17 +14454,17 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129542936</v>
+        <v>129542967</v>
       </c>
       <c r="B130" t="n">
-        <v>57724</v>
+        <v>78801</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14467,39 +14472,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>458155</v>
+        <v>457939</v>
       </c>
       <c r="R130" t="n">
-        <v>6748562</v>
+        <v>6748494</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14675,7 +14675,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129543036</v>
+        <v>129543077</v>
       </c>
       <c r="B132" t="n">
         <v>79044</v>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457843</v>
+        <v>457938</v>
       </c>
       <c r="R132" t="n">
-        <v>6748341</v>
+        <v>6748409</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14782,7 +14782,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129543058</v>
+        <v>129543040</v>
       </c>
       <c r="B133" t="n">
         <v>79044</v>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>458143</v>
+        <v>457817</v>
       </c>
       <c r="R133" t="n">
-        <v>6748611</v>
+        <v>6748400</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14889,7 +14889,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129543077</v>
+        <v>129543050</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>457938</v>
+        <v>458067</v>
       </c>
       <c r="R134" t="n">
-        <v>6748409</v>
+        <v>6748648</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14989,14 +14989,14 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129543040</v>
+        <v>129543036</v>
       </c>
       <c r="B135" t="n">
         <v>79044</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457817</v>
+        <v>457843</v>
       </c>
       <c r="R135" t="n">
-        <v>6748400</v>
+        <v>6748341</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15103,32 +15103,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129543044</v>
+        <v>129542920</v>
       </c>
       <c r="B136" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>457939</v>
+        <v>457964</v>
       </c>
       <c r="R136" t="n">
-        <v>6748453</v>
+        <v>6748415</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15210,7 +15210,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129543050</v>
+        <v>129543044</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>458067</v>
+        <v>457939</v>
       </c>
       <c r="R137" t="n">
-        <v>6748648</v>
+        <v>6748453</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15317,32 +15317,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129542920</v>
+        <v>129543058</v>
       </c>
       <c r="B138" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>457964</v>
+        <v>458143</v>
       </c>
       <c r="R138" t="n">
-        <v>6748415</v>
+        <v>6748611</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15531,10 +15531,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129542958</v>
+        <v>129543089</v>
       </c>
       <c r="B140" t="n">
-        <v>81029</v>
+        <v>78710</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>458029</v>
+        <v>457809</v>
       </c>
       <c r="R140" t="n">
-        <v>6748402</v>
+        <v>6748254</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15638,10 +15638,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129543089</v>
+        <v>129542958</v>
       </c>
       <c r="B141" t="n">
-        <v>78710</v>
+        <v>81029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457809</v>
+        <v>458029</v>
       </c>
       <c r="R141" t="n">
-        <v>6748254</v>
+        <v>6748402</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15738,17 +15738,17 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129542963</v>
+        <v>129543074</v>
       </c>
       <c r="B142" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15756,21 +15756,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457754</v>
+        <v>457905</v>
       </c>
       <c r="R142" t="n">
-        <v>6748230</v>
+        <v>6748321</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15852,10 +15852,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129543074</v>
+        <v>129542965</v>
       </c>
       <c r="B143" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15863,21 +15863,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457905</v>
+        <v>457760</v>
       </c>
       <c r="R143" t="n">
-        <v>6748321</v>
+        <v>6748255</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15952,14 +15952,14 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129542965</v>
+        <v>129542963</v>
       </c>
       <c r="B144" t="n">
         <v>78801</v>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457760</v>
+        <v>457754</v>
       </c>
       <c r="R144" t="n">
-        <v>6748255</v>
+        <v>6748230</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16380,14 +16380,14 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129543069</v>
+        <v>129542994</v>
       </c>
       <c r="B148" t="n">
         <v>79044</v>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457930</v>
+        <v>457786</v>
       </c>
       <c r="R148" t="n">
-        <v>6748385</v>
+        <v>6748280</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16487,14 +16487,14 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129542994</v>
+        <v>129543023</v>
       </c>
       <c r="B149" t="n">
         <v>79044</v>
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457786</v>
+        <v>457758</v>
       </c>
       <c r="R149" t="n">
-        <v>6748280</v>
+        <v>6748213</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16594,14 +16594,14 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129543006</v>
+        <v>129543069</v>
       </c>
       <c r="B150" t="n">
         <v>79044</v>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457712</v>
+        <v>457930</v>
       </c>
       <c r="R150" t="n">
-        <v>6748081</v>
+        <v>6748385</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16708,7 +16708,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129543023</v>
+        <v>129543006</v>
       </c>
       <c r="B151" t="n">
         <v>79044</v>
@@ -16743,10 +16743,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457758</v>
+        <v>457712</v>
       </c>
       <c r="R151" t="n">
-        <v>6748213</v>
+        <v>6748081</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129542945</v>
+        <v>129542959</v>
       </c>
       <c r="B153" t="n">
-        <v>97604</v>
+        <v>81029</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>457654</v>
+        <v>457884</v>
       </c>
       <c r="R153" t="n">
-        <v>6748079</v>
+        <v>6748404</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17029,32 +17029,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129542943</v>
+        <v>129542980</v>
       </c>
       <c r="B154" t="n">
-        <v>97598</v>
+        <v>91726</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221945</v>
+        <v>1503</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457999</v>
+        <v>458058</v>
       </c>
       <c r="R154" t="n">
-        <v>6748381</v>
+        <v>6748621</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17236,7 +17236,7 @@
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -17457,32 +17457,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129542980</v>
+        <v>129542945</v>
       </c>
       <c r="B158" t="n">
-        <v>91726</v>
+        <v>97604</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>458058</v>
+        <v>457654</v>
       </c>
       <c r="R158" t="n">
-        <v>6748621</v>
+        <v>6748079</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17557,39 +17557,39 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129542959</v>
+        <v>129542943</v>
       </c>
       <c r="B159" t="n">
-        <v>81029</v>
+        <v>97598</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1049</v>
+        <v>221945</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457884</v>
+        <v>457999</v>
       </c>
       <c r="R159" t="n">
-        <v>6748404</v>
+        <v>6748381</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129543031</v>
+        <v>129543007</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457809</v>
+        <v>457677</v>
       </c>
       <c r="R3" t="n">
-        <v>6748286</v>
+        <v>6748051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543024</v>
+        <v>129543031</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457755</v>
+        <v>457809</v>
       </c>
       <c r="R4" t="n">
-        <v>6748219</v>
+        <v>6748286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543041</v>
+        <v>129543024</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457854</v>
+        <v>457755</v>
       </c>
       <c r="R5" t="n">
-        <v>6748444</v>
+        <v>6748219</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543026</v>
+        <v>129543041</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457758</v>
+        <v>457854</v>
       </c>
       <c r="R6" t="n">
-        <v>6748263</v>
+        <v>6748444</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543056</v>
+        <v>129543026</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458120</v>
+        <v>457758</v>
       </c>
       <c r="R7" t="n">
-        <v>6748624</v>
+        <v>6748263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,50 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129542951</v>
+        <v>129543056</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457817</v>
+        <v>458120</v>
       </c>
       <c r="R8" t="n">
-        <v>6748352</v>
+        <v>6748624</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,45 +1424,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543007</v>
+        <v>129542925</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457677</v>
+        <v>457896</v>
       </c>
       <c r="R9" t="n">
-        <v>6748051</v>
+        <v>6748335</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129542925</v>
+        <v>129542951</v>
       </c>
       <c r="B10" t="n">
-        <v>56917</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,27 +1547,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457896</v>
+        <v>457817</v>
       </c>
       <c r="R10" t="n">
-        <v>6748335</v>
+        <v>6748352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543091</v>
+        <v>129543081</v>
       </c>
       <c r="B11" t="n">
-        <v>78710</v>
+        <v>91826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457817</v>
+        <v>458131</v>
       </c>
       <c r="R11" t="n">
-        <v>6748202</v>
+        <v>6748547</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543092</v>
+        <v>129543043</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457785</v>
+        <v>457927</v>
       </c>
       <c r="R12" t="n">
-        <v>6748160</v>
+        <v>6748447</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129542924</v>
+        <v>129542992</v>
       </c>
       <c r="B13" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457899</v>
+        <v>457763</v>
       </c>
       <c r="R13" t="n">
-        <v>6748444</v>
+        <v>6748301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,7 +1969,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543043</v>
+        <v>129543017</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457927</v>
+        <v>457657</v>
       </c>
       <c r="R14" t="n">
-        <v>6748447</v>
+        <v>6748226</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129542928</v>
+        <v>129543070</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,39 +2087,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457940</v>
+        <v>457936</v>
       </c>
       <c r="R15" t="n">
-        <v>6748387</v>
+        <v>6748379</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129542992</v>
+        <v>129542995</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2223,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457763</v>
+        <v>457809</v>
       </c>
       <c r="R16" t="n">
-        <v>6748301</v>
+        <v>6748246</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543017</v>
+        <v>129542924</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457657</v>
+        <v>457899</v>
       </c>
       <c r="R17" t="n">
-        <v>6748226</v>
+        <v>6748444</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2370,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543070</v>
+        <v>129543091</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457936</v>
+        <v>457817</v>
       </c>
       <c r="R18" t="n">
-        <v>6748379</v>
+        <v>6748202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129542995</v>
+        <v>129543092</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457809</v>
+        <v>457785</v>
       </c>
       <c r="R19" t="n">
-        <v>6748246</v>
+        <v>6748160</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2574,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2584,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,32 +2611,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543081</v>
+        <v>129542915</v>
       </c>
       <c r="B20" t="n">
-        <v>91826</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458131</v>
+        <v>457754</v>
       </c>
       <c r="R20" t="n">
-        <v>6748547</v>
+        <v>6748230</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129542915</v>
+        <v>129542928</v>
       </c>
       <c r="B21" t="n">
-        <v>79663</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,34 +2729,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457754</v>
+        <v>457940</v>
       </c>
       <c r="R21" t="n">
-        <v>6748230</v>
+        <v>6748387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543005</v>
+        <v>129542913</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457775</v>
+        <v>457761</v>
       </c>
       <c r="R22" t="n">
-        <v>6748148</v>
+        <v>6748133</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543032</v>
+        <v>129543107</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457821</v>
+        <v>458144</v>
       </c>
       <c r="R23" t="n">
-        <v>6748297</v>
+        <v>6748538</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129542982</v>
+        <v>129542996</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457941</v>
+        <v>457833</v>
       </c>
       <c r="R24" t="n">
-        <v>6748477</v>
+        <v>6748233</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,12 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3151,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543107</v>
+        <v>129543038</v>
       </c>
       <c r="B25" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,21 +3162,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458144</v>
+        <v>457829</v>
       </c>
       <c r="R25" t="n">
-        <v>6748538</v>
+        <v>6748366</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,7 +3258,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129542996</v>
+        <v>129543005</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3298,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457833</v>
+        <v>457775</v>
       </c>
       <c r="R26" t="n">
-        <v>6748233</v>
+        <v>6748148</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3370,7 +3365,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543038</v>
+        <v>129543051</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3405,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457829</v>
+        <v>458077</v>
       </c>
       <c r="R27" t="n">
-        <v>6748366</v>
+        <v>6748657</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3450,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3477,7 +3472,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543051</v>
+        <v>129543045</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3512,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458077</v>
+        <v>457912</v>
       </c>
       <c r="R28" t="n">
-        <v>6748657</v>
+        <v>6748485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3557,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3584,7 +3579,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543045</v>
+        <v>129543032</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3619,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457912</v>
+        <v>457821</v>
       </c>
       <c r="R29" t="n">
-        <v>6748485</v>
+        <v>6748297</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3654,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3664,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3691,10 +3686,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129542913</v>
+        <v>129542982</v>
       </c>
       <c r="B30" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3702,21 +3697,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3726,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457761</v>
+        <v>457941</v>
       </c>
       <c r="R30" t="n">
-        <v>6748133</v>
+        <v>6748477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3771,7 +3766,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4012,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129542966</v>
+        <v>129543063</v>
       </c>
       <c r="B33" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457938</v>
+        <v>458116</v>
       </c>
       <c r="R33" t="n">
-        <v>6748466</v>
+        <v>6748548</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,7 +4119,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543063</v>
+        <v>129543059</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458116</v>
+        <v>458174</v>
       </c>
       <c r="R34" t="n">
-        <v>6748548</v>
+        <v>6748599</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,7 +4226,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543059</v>
+        <v>129543021</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458174</v>
+        <v>457756</v>
       </c>
       <c r="R35" t="n">
-        <v>6748599</v>
+        <v>6748192</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543021</v>
+        <v>129542993</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457756</v>
+        <v>457763</v>
       </c>
       <c r="R36" t="n">
-        <v>6748192</v>
+        <v>6748294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,32 +4440,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129542993</v>
+        <v>129542942</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457763</v>
+        <v>457951</v>
       </c>
       <c r="R37" t="n">
-        <v>6748294</v>
+        <v>6748543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4547,50 +4547,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542949</v>
+        <v>129542966</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457627</v>
+        <v>457938</v>
       </c>
       <c r="R38" t="n">
-        <v>6748161</v>
+        <v>6748466</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4622,7 +4617,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4632,7 +4627,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4659,10 +4654,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129542942</v>
+        <v>129542949</v>
       </c>
       <c r="B39" t="n">
-        <v>97598</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4670,34 +4665,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457951</v>
+        <v>457627</v>
       </c>
       <c r="R39" t="n">
-        <v>6748543</v>
+        <v>6748161</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4766,10 +4766,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543003</v>
+        <v>129543098</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457814</v>
+        <v>457657</v>
       </c>
       <c r="R40" t="n">
-        <v>6748175</v>
+        <v>6748066</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543071</v>
+        <v>129543093</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457928</v>
+        <v>457737</v>
       </c>
       <c r="R41" t="n">
-        <v>6748344</v>
+        <v>6748103</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129542998</v>
+        <v>129543071</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457876</v>
+        <v>457928</v>
       </c>
       <c r="R42" t="n">
-        <v>6748240</v>
+        <v>6748344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543057</v>
+        <v>129542998</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>458134</v>
+        <v>457876</v>
       </c>
       <c r="R43" t="n">
-        <v>6748614</v>
+        <v>6748240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129542927</v>
+        <v>129543003</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,39 +5205,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458027</v>
+        <v>457814</v>
       </c>
       <c r="R44" t="n">
-        <v>6748413</v>
+        <v>6748175</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5269,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5279,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5306,10 +5301,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543098</v>
+        <v>129543057</v>
       </c>
       <c r="B45" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5317,21 +5312,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5341,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457657</v>
+        <v>458134</v>
       </c>
       <c r="R45" t="n">
-        <v>6748066</v>
+        <v>6748614</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,7 +5371,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5381,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,10 +5408,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543093</v>
+        <v>129542946</v>
       </c>
       <c r="B46" t="n">
-        <v>78710</v>
+        <v>91606</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5424,21 +5419,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5448,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457737</v>
+        <v>458035</v>
       </c>
       <c r="R46" t="n">
-        <v>6748103</v>
+        <v>6748395</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5483,7 +5478,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5493,7 +5488,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,32 +5515,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129542946</v>
+        <v>129543112</v>
       </c>
       <c r="B47" t="n">
-        <v>91606</v>
+        <v>91610</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>5321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5555,10 +5550,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458035</v>
+        <v>458029</v>
       </c>
       <c r="R47" t="n">
-        <v>6748395</v>
+        <v>6748411</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5590,7 +5585,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5600,7 +5595,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5609,6 +5604,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5627,45 +5623,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543112</v>
+        <v>129542927</v>
       </c>
       <c r="B48" t="n">
-        <v>91610</v>
+        <v>57887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5321</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>458029</v>
+        <v>458027</v>
       </c>
       <c r="R48" t="n">
-        <v>6748411</v>
+        <v>6748413</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5716,7 +5717,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543082</v>
+        <v>129543078</v>
       </c>
       <c r="B49" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457792</v>
+        <v>457875</v>
       </c>
       <c r="R49" t="n">
-        <v>6748260</v>
+        <v>6748394</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6056,10 +6056,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543078</v>
+        <v>129543082</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6067,21 +6067,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457875</v>
+        <v>457792</v>
       </c>
       <c r="R52" t="n">
-        <v>6748394</v>
+        <v>6748260</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6163,10 +6163,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543001</v>
+        <v>129542914</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6174,21 +6174,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457838</v>
+        <v>457650</v>
       </c>
       <c r="R53" t="n">
-        <v>6748208</v>
+        <v>6748064</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6270,7 +6270,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543035</v>
+        <v>129543034</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457845</v>
+        <v>457852</v>
       </c>
       <c r="R54" t="n">
-        <v>6748327</v>
+        <v>6748316</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6377,7 +6377,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543066</v>
+        <v>129543001</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458042</v>
+        <v>457838</v>
       </c>
       <c r="R55" t="n">
-        <v>6748499</v>
+        <v>6748208</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6484,10 +6484,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129542914</v>
+        <v>129543064</v>
       </c>
       <c r="B56" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6495,21 +6495,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457650</v>
+        <v>458049</v>
       </c>
       <c r="R56" t="n">
-        <v>6748064</v>
+        <v>6748509</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,7 +6591,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543034</v>
+        <v>129543042</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457852</v>
+        <v>457922</v>
       </c>
       <c r="R57" t="n">
-        <v>6748316</v>
+        <v>6748447</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6698,7 +6698,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543064</v>
+        <v>129543072</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458049</v>
+        <v>457899</v>
       </c>
       <c r="R58" t="n">
-        <v>6748509</v>
+        <v>6748357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6805,7 +6805,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543042</v>
+        <v>129543035</v>
       </c>
       <c r="B59" t="n">
         <v>79044</v>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457922</v>
+        <v>457845</v>
       </c>
       <c r="R59" t="n">
-        <v>6748447</v>
+        <v>6748327</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,7 +6912,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543072</v>
+        <v>129543066</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457899</v>
+        <v>458042</v>
       </c>
       <c r="R60" t="n">
-        <v>6748357</v>
+        <v>6748499</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7350,10 +7350,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543073</v>
+        <v>129542962</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7361,21 +7361,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457917</v>
+        <v>457762</v>
       </c>
       <c r="R64" t="n">
-        <v>6748303</v>
+        <v>6748208</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543047</v>
+        <v>129542961</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457952</v>
+        <v>457859</v>
       </c>
       <c r="R65" t="n">
-        <v>6748501</v>
+        <v>6748231</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7564,7 +7564,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543002</v>
+        <v>129543073</v>
       </c>
       <c r="B66" t="n">
         <v>79044</v>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457813</v>
+        <v>457917</v>
       </c>
       <c r="R66" t="n">
-        <v>6748191</v>
+        <v>6748303</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7671,7 +7671,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543029</v>
+        <v>129543047</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457780</v>
+        <v>457952</v>
       </c>
       <c r="R67" t="n">
-        <v>6748311</v>
+        <v>6748501</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7778,7 +7778,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543053</v>
+        <v>129543019</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458094</v>
+        <v>457725</v>
       </c>
       <c r="R68" t="n">
-        <v>6748667</v>
+        <v>6748208</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7885,50 +7885,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129542952</v>
+        <v>129543060</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458156</v>
+        <v>458177</v>
       </c>
       <c r="R69" t="n">
-        <v>6748545</v>
+        <v>6748587</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7960,7 +7955,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7970,7 +7965,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,10 +7992,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129542962</v>
+        <v>129543029</v>
       </c>
       <c r="B70" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8008,21 +8003,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8032,10 +8027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457762</v>
+        <v>457780</v>
       </c>
       <c r="R70" t="n">
-        <v>6748208</v>
+        <v>6748311</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8067,7 +8062,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8077,7 +8072,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8104,7 +8099,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543019</v>
+        <v>129543002</v>
       </c>
       <c r="B71" t="n">
         <v>79044</v>
@@ -8139,10 +8134,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457725</v>
+        <v>457813</v>
       </c>
       <c r="R71" t="n">
-        <v>6748208</v>
+        <v>6748191</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8174,7 +8169,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8184,7 +8179,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8211,7 +8206,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543060</v>
+        <v>129543053</v>
       </c>
       <c r="B72" t="n">
         <v>79044</v>
@@ -8246,10 +8241,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458177</v>
+        <v>458094</v>
       </c>
       <c r="R72" t="n">
-        <v>6748587</v>
+        <v>6748667</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8281,7 +8276,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8291,7 +8286,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8318,45 +8313,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129542961</v>
+        <v>129542952</v>
       </c>
       <c r="B73" t="n">
-        <v>78801</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457859</v>
+        <v>458156</v>
       </c>
       <c r="R73" t="n">
-        <v>6748231</v>
+        <v>6748545</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8746,7 +8746,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129542999</v>
+        <v>129543000</v>
       </c>
       <c r="B77" t="n">
         <v>79044</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457883</v>
+        <v>457846</v>
       </c>
       <c r="R77" t="n">
-        <v>6748260</v>
+        <v>6748214</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8853,7 +8853,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543000</v>
+        <v>129542999</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457846</v>
+        <v>457883</v>
       </c>
       <c r="R78" t="n">
-        <v>6748214</v>
+        <v>6748260</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9179,10 +9179,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129542968</v>
+        <v>129543103</v>
       </c>
       <c r="B81" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458060</v>
+        <v>457842</v>
       </c>
       <c r="R81" t="n">
-        <v>6748629</v>
+        <v>6748363</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9286,10 +9286,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543065</v>
+        <v>129543088</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458039</v>
+        <v>457797</v>
       </c>
       <c r="R82" t="n">
-        <v>6748504</v>
+        <v>6748261</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9393,10 +9393,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543103</v>
+        <v>129542964</v>
       </c>
       <c r="B83" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9404,21 +9404,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457842</v>
+        <v>457767</v>
       </c>
       <c r="R83" t="n">
-        <v>6748363</v>
+        <v>6748250</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9500,10 +9500,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543088</v>
+        <v>129542968</v>
       </c>
       <c r="B84" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9511,21 +9511,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457797</v>
+        <v>458060</v>
       </c>
       <c r="R84" t="n">
-        <v>6748261</v>
+        <v>6748629</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9714,10 +9714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129542964</v>
+        <v>129543065</v>
       </c>
       <c r="B86" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9725,21 +9725,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457767</v>
+        <v>458039</v>
       </c>
       <c r="R86" t="n">
-        <v>6748250</v>
+        <v>6748504</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10254,45 +10254,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129542939</v>
+        <v>129542969</v>
       </c>
       <c r="B91" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457660</v>
+        <v>457879</v>
       </c>
       <c r="R91" t="n">
-        <v>6748092</v>
+        <v>6748454</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10324,7 +10333,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10334,7 +10343,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10361,54 +10370,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129542969</v>
+        <v>129542939</v>
       </c>
       <c r="B92" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457879</v>
+        <v>457660</v>
       </c>
       <c r="R92" t="n">
-        <v>6748454</v>
+        <v>6748092</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10798,7 +10798,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543020</v>
+        <v>129543039</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457738</v>
+        <v>457830</v>
       </c>
       <c r="R96" t="n">
-        <v>6748205</v>
+        <v>6748402</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10905,7 +10905,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543062</v>
+        <v>129543030</v>
       </c>
       <c r="B97" t="n">
         <v>79044</v>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458140</v>
+        <v>457811</v>
       </c>
       <c r="R97" t="n">
-        <v>6748536</v>
+        <v>6748293</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,10 +11012,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543099</v>
+        <v>129543020</v>
       </c>
       <c r="B98" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11023,21 +11023,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457650</v>
+        <v>457738</v>
       </c>
       <c r="R98" t="n">
-        <v>6748064</v>
+        <v>6748205</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543104</v>
+        <v>129543016</v>
       </c>
       <c r="B99" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11130,21 +11130,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11154,10 +11154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457992</v>
+        <v>457699</v>
       </c>
       <c r="R99" t="n">
-        <v>6748556</v>
+        <v>6748197</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,10 +11226,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129542956</v>
+        <v>129543062</v>
       </c>
       <c r="B100" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11237,21 +11237,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457662</v>
+        <v>458140</v>
       </c>
       <c r="R100" t="n">
-        <v>6748216</v>
+        <v>6748536</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,32 +11333,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543083</v>
+        <v>129542960</v>
       </c>
       <c r="B101" t="n">
-        <v>78710</v>
+        <v>80109</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11368,10 +11368,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457757</v>
+        <v>458029</v>
       </c>
       <c r="R101" t="n">
-        <v>6748191</v>
+        <v>6748413</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11413,7 +11413,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt på jätteasp</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11440,10 +11445,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543039</v>
+        <v>129542956</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>81029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11451,21 +11456,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11475,10 +11480,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457830</v>
+        <v>457662</v>
       </c>
       <c r="R102" t="n">
-        <v>6748402</v>
+        <v>6748216</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,7 +11515,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11520,7 +11525,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11547,10 +11552,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543030</v>
+        <v>129543099</v>
       </c>
       <c r="B103" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11558,21 +11563,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11582,10 +11587,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457811</v>
+        <v>457650</v>
       </c>
       <c r="R103" t="n">
-        <v>6748293</v>
+        <v>6748064</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,7 +11622,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11627,7 +11632,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11654,10 +11659,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543016</v>
+        <v>129543104</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11665,21 +11670,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11689,10 +11694,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457699</v>
+        <v>457992</v>
       </c>
       <c r="R104" t="n">
-        <v>6748197</v>
+        <v>6748556</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11724,7 +11729,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11734,7 +11739,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11761,32 +11766,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129542960</v>
+        <v>129543083</v>
       </c>
       <c r="B105" t="n">
-        <v>80109</v>
+        <v>78710</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11796,10 +11801,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458029</v>
+        <v>457757</v>
       </c>
       <c r="R105" t="n">
-        <v>6748413</v>
+        <v>6748191</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11831,7 +11836,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11841,12 +11846,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Rikligt på jätteasp</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,7 +11873,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543094</v>
+        <v>129543095</v>
       </c>
       <c r="B106" t="n">
         <v>78710</v>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457728</v>
+        <v>457704</v>
       </c>
       <c r="R106" t="n">
-        <v>6748093</v>
+        <v>6748074</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11980,7 +11980,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543095</v>
+        <v>129543096</v>
       </c>
       <c r="B107" t="n">
         <v>78710</v>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457704</v>
+        <v>457671</v>
       </c>
       <c r="R107" t="n">
-        <v>6748074</v>
+        <v>6748048</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12087,32 +12087,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129542981</v>
+        <v>129543012</v>
       </c>
       <c r="B108" t="n">
-        <v>91726</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457964</v>
+        <v>457625</v>
       </c>
       <c r="R108" t="n">
-        <v>6748415</v>
+        <v>6748127</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12306,32 +12306,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543096</v>
+        <v>129542981</v>
       </c>
       <c r="B110" t="n">
-        <v>78710</v>
+        <v>91726</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12341,10 +12341,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457671</v>
+        <v>457964</v>
       </c>
       <c r="R110" t="n">
-        <v>6748048</v>
+        <v>6748415</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12413,10 +12413,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543012</v>
+        <v>129543094</v>
       </c>
       <c r="B111" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12424,21 +12424,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457625</v>
+        <v>457728</v>
       </c>
       <c r="R111" t="n">
-        <v>6748127</v>
+        <v>6748093</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12627,10 +12627,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129543011</v>
+        <v>129542935</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12638,34 +12638,39 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457665</v>
+        <v>458060</v>
       </c>
       <c r="R113" t="n">
-        <v>6748082</v>
+        <v>6748631</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12697,7 +12702,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12707,7 +12712,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12734,32 +12739,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129543008</v>
+        <v>129542944</v>
       </c>
       <c r="B114" t="n">
-        <v>79044</v>
+        <v>97604</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12769,10 +12774,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>457671</v>
+        <v>457654</v>
       </c>
       <c r="R114" t="n">
-        <v>6748048</v>
+        <v>6748070</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12804,7 +12809,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12814,7 +12819,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12841,10 +12846,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129542935</v>
+        <v>129542923</v>
       </c>
       <c r="B115" t="n">
-        <v>57724</v>
+        <v>79139</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12852,39 +12857,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458060</v>
+        <v>457773</v>
       </c>
       <c r="R115" t="n">
-        <v>6748631</v>
+        <v>6748248</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12953,10 +12953,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129542923</v>
+        <v>129543011</v>
       </c>
       <c r="B116" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12964,21 +12964,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457773</v>
+        <v>457665</v>
       </c>
       <c r="R116" t="n">
-        <v>6748248</v>
+        <v>6748082</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13060,32 +13060,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129542944</v>
+        <v>129543008</v>
       </c>
       <c r="B117" t="n">
-        <v>97604</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457654</v>
+        <v>457671</v>
       </c>
       <c r="R117" t="n">
-        <v>6748070</v>
+        <v>6748048</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13167,7 +13167,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129543054</v>
+        <v>129543061</v>
       </c>
       <c r="B118" t="n">
         <v>79044</v>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458097</v>
+        <v>458155</v>
       </c>
       <c r="R118" t="n">
-        <v>6748662</v>
+        <v>6748548</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13274,50 +13274,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129542947</v>
+        <v>129543054</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>457929</v>
+        <v>458097</v>
       </c>
       <c r="R119" t="n">
-        <v>6748484</v>
+        <v>6748662</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13349,7 +13344,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13359,7 +13354,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13386,45 +13381,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129543061</v>
+        <v>129542947</v>
       </c>
       <c r="B120" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>458155</v>
+        <v>457929</v>
       </c>
       <c r="R120" t="n">
-        <v>6748548</v>
+        <v>6748484</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13493,10 +13493,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129543046</v>
+        <v>129543102</v>
       </c>
       <c r="B121" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13504,21 +13504,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>457946</v>
+        <v>457761</v>
       </c>
       <c r="R121" t="n">
-        <v>6748493</v>
+        <v>6748256</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13600,7 +13600,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129543048</v>
+        <v>129543046</v>
       </c>
       <c r="B122" t="n">
         <v>79044</v>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>457954</v>
+        <v>457946</v>
       </c>
       <c r="R122" t="n">
-        <v>6748541</v>
+        <v>6748493</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13707,7 +13707,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129543004</v>
+        <v>129543048</v>
       </c>
       <c r="B123" t="n">
         <v>79044</v>
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>457802</v>
+        <v>457954</v>
       </c>
       <c r="R123" t="n">
-        <v>6748157</v>
+        <v>6748541</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13814,7 +13814,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129543025</v>
+        <v>129543004</v>
       </c>
       <c r="B124" t="n">
         <v>79044</v>
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>457761</v>
+        <v>457802</v>
       </c>
       <c r="R124" t="n">
-        <v>6748254</v>
+        <v>6748157</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13921,7 +13921,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129543015</v>
+        <v>129543025</v>
       </c>
       <c r="B125" t="n">
         <v>79044</v>
@@ -13956,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>457689</v>
+        <v>457761</v>
       </c>
       <c r="R125" t="n">
-        <v>6748165</v>
+        <v>6748254</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14028,7 +14028,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129543027</v>
+        <v>129543015</v>
       </c>
       <c r="B126" t="n">
         <v>79044</v>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457756</v>
+        <v>457689</v>
       </c>
       <c r="R126" t="n">
-        <v>6748271</v>
+        <v>6748165</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14135,10 +14135,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129542936</v>
+        <v>129542978</v>
       </c>
       <c r="B127" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14146,39 +14146,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458155</v>
+        <v>457802</v>
       </c>
       <c r="R127" t="n">
-        <v>6748562</v>
+        <v>6748301</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14210,7 +14205,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14220,7 +14215,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14247,10 +14242,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129543102</v>
+        <v>129543027</v>
       </c>
       <c r="B128" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14258,21 +14253,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14282,10 +14277,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457761</v>
+        <v>457756</v>
       </c>
       <c r="R128" t="n">
-        <v>6748256</v>
+        <v>6748271</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14354,10 +14349,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129542978</v>
+        <v>129542936</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14365,34 +14360,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>457802</v>
+        <v>458155</v>
       </c>
       <c r="R129" t="n">
-        <v>6748301</v>
+        <v>6748562</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14675,32 +14675,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129543077</v>
+        <v>129542920</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457938</v>
+        <v>457964</v>
       </c>
       <c r="R132" t="n">
-        <v>6748409</v>
+        <v>6748415</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14782,10 +14782,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129543040</v>
+        <v>129542916</v>
       </c>
       <c r="B133" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14793,21 +14793,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457817</v>
+        <v>457750</v>
       </c>
       <c r="R133" t="n">
-        <v>6748400</v>
+        <v>6748276</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14889,7 +14889,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129543050</v>
+        <v>129543077</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>458067</v>
+        <v>457938</v>
       </c>
       <c r="R134" t="n">
-        <v>6748648</v>
+        <v>6748409</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14996,7 +14996,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129543036</v>
+        <v>129543040</v>
       </c>
       <c r="B135" t="n">
         <v>79044</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457843</v>
+        <v>457817</v>
       </c>
       <c r="R135" t="n">
-        <v>6748341</v>
+        <v>6748400</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15103,32 +15103,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129542920</v>
+        <v>129543044</v>
       </c>
       <c r="B136" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>457964</v>
+        <v>457939</v>
       </c>
       <c r="R136" t="n">
-        <v>6748415</v>
+        <v>6748453</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15210,7 +15210,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129543044</v>
+        <v>129543050</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>457939</v>
+        <v>458067</v>
       </c>
       <c r="R137" t="n">
-        <v>6748453</v>
+        <v>6748648</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15317,7 +15317,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129543058</v>
+        <v>129543036</v>
       </c>
       <c r="B138" t="n">
         <v>79044</v>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>458143</v>
+        <v>457843</v>
       </c>
       <c r="R138" t="n">
-        <v>6748611</v>
+        <v>6748341</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15424,10 +15424,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129542916</v>
+        <v>129543058</v>
       </c>
       <c r="B139" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15435,21 +15435,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>457750</v>
+        <v>458143</v>
       </c>
       <c r="R139" t="n">
-        <v>6748276</v>
+        <v>6748611</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15531,10 +15531,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129543089</v>
+        <v>129542963</v>
       </c>
       <c r="B140" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>457809</v>
+        <v>457754</v>
       </c>
       <c r="R140" t="n">
-        <v>6748254</v>
+        <v>6748230</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15638,10 +15638,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129542958</v>
+        <v>129542965</v>
       </c>
       <c r="B141" t="n">
-        <v>81029</v>
+        <v>78801</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>458029</v>
+        <v>457760</v>
       </c>
       <c r="R141" t="n">
-        <v>6748402</v>
+        <v>6748255</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15745,10 +15745,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129543074</v>
+        <v>129542958</v>
       </c>
       <c r="B142" t="n">
-        <v>79044</v>
+        <v>81029</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15756,21 +15756,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457905</v>
+        <v>458029</v>
       </c>
       <c r="R142" t="n">
-        <v>6748321</v>
+        <v>6748402</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15852,10 +15852,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129542965</v>
+        <v>129543074</v>
       </c>
       <c r="B143" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15863,21 +15863,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457760</v>
+        <v>457905</v>
       </c>
       <c r="R143" t="n">
-        <v>6748255</v>
+        <v>6748321</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129542963</v>
+        <v>129543022</v>
       </c>
       <c r="B144" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15970,21 +15970,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457754</v>
+        <v>457761</v>
       </c>
       <c r="R144" t="n">
-        <v>6748230</v>
+        <v>6748192</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16066,7 +16066,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129543022</v>
+        <v>129543052</v>
       </c>
       <c r="B145" t="n">
         <v>79044</v>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>457761</v>
+        <v>458081</v>
       </c>
       <c r="R145" t="n">
-        <v>6748192</v>
+        <v>6748667</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16173,10 +16173,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129543052</v>
+        <v>129543089</v>
       </c>
       <c r="B146" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16184,21 +16184,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>458081</v>
+        <v>457809</v>
       </c>
       <c r="R146" t="n">
-        <v>6748667</v>
+        <v>6748254</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16280,32 +16280,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129543100</v>
+        <v>129542941</v>
       </c>
       <c r="B147" t="n">
-        <v>78710</v>
+        <v>97598</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457631</v>
+        <v>457929</v>
       </c>
       <c r="R147" t="n">
-        <v>6748174</v>
+        <v>6748448</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,10 +16387,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129542994</v>
+        <v>129543100</v>
       </c>
       <c r="B148" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16398,21 +16398,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457786</v>
+        <v>457631</v>
       </c>
       <c r="R148" t="n">
-        <v>6748280</v>
+        <v>6748174</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16494,7 +16494,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129543023</v>
+        <v>129543069</v>
       </c>
       <c r="B149" t="n">
         <v>79044</v>
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457758</v>
+        <v>457930</v>
       </c>
       <c r="R149" t="n">
-        <v>6748213</v>
+        <v>6748385</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16601,7 +16601,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129543069</v>
+        <v>129542994</v>
       </c>
       <c r="B150" t="n">
         <v>79044</v>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457930</v>
+        <v>457786</v>
       </c>
       <c r="R150" t="n">
-        <v>6748385</v>
+        <v>6748280</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16815,32 +16815,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129542941</v>
+        <v>129543023</v>
       </c>
       <c r="B152" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457929</v>
+        <v>457758</v>
       </c>
       <c r="R152" t="n">
-        <v>6748448</v>
+        <v>6748213</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129542959</v>
+        <v>129542945</v>
       </c>
       <c r="B153" t="n">
-        <v>81029</v>
+        <v>97604</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1049</v>
+        <v>221941</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>457884</v>
+        <v>457654</v>
       </c>
       <c r="R153" t="n">
-        <v>6748404</v>
+        <v>6748079</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17029,32 +17029,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129542980</v>
+        <v>129542943</v>
       </c>
       <c r="B154" t="n">
-        <v>91726</v>
+        <v>97598</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1503</v>
+        <v>221945</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>458058</v>
+        <v>457999</v>
       </c>
       <c r="R154" t="n">
-        <v>6748621</v>
+        <v>6748381</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17136,10 +17136,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129543068</v>
+        <v>129542959</v>
       </c>
       <c r="B155" t="n">
-        <v>79044</v>
+        <v>81029</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17147,21 +17147,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>457935</v>
+        <v>457884</v>
       </c>
       <c r="R155" t="n">
-        <v>6748390</v>
+        <v>6748404</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129543067</v>
+        <v>129542980</v>
       </c>
       <c r="B156" t="n">
-        <v>79044</v>
+        <v>91726</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>457946</v>
+        <v>458058</v>
       </c>
       <c r="R156" t="n">
-        <v>6748380</v>
+        <v>6748621</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17350,7 +17350,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129543033</v>
+        <v>129543068</v>
       </c>
       <c r="B157" t="n">
         <v>79044</v>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457836</v>
+        <v>457935</v>
       </c>
       <c r="R157" t="n">
-        <v>6748291</v>
+        <v>6748390</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17457,32 +17457,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129542945</v>
+        <v>129543067</v>
       </c>
       <c r="B158" t="n">
-        <v>97604</v>
+        <v>79044</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457654</v>
+        <v>457946</v>
       </c>
       <c r="R158" t="n">
-        <v>6748079</v>
+        <v>6748380</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17564,32 +17564,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129542943</v>
+        <v>129543033</v>
       </c>
       <c r="B159" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457999</v>
+        <v>457836</v>
       </c>
       <c r="R159" t="n">
-        <v>6748381</v>
+        <v>6748291</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129543108</v>
       </c>
       <c r="B2" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129543007</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129543031</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129543024</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129543041</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129543026</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129543056</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129542925</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>129543081</v>
       </c>
       <c r="B11" t="n">
-        <v>91826</v>
+        <v>91854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543043</v>
+        <v>129543091</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457927</v>
+        <v>457817</v>
       </c>
       <c r="R12" t="n">
-        <v>6748447</v>
+        <v>6748202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129542992</v>
+        <v>129543092</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457763</v>
+        <v>457785</v>
       </c>
       <c r="R13" t="n">
-        <v>6748301</v>
+        <v>6748160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543017</v>
+        <v>129542924</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457657</v>
+        <v>457899</v>
       </c>
       <c r="R14" t="n">
-        <v>6748226</v>
+        <v>6748444</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543070</v>
+        <v>129542995</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457936</v>
+        <v>457809</v>
       </c>
       <c r="R15" t="n">
-        <v>6748379</v>
+        <v>6748246</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129542995</v>
+        <v>129542915</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457809</v>
+        <v>457754</v>
       </c>
       <c r="R16" t="n">
-        <v>6748246</v>
+        <v>6748230</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129542924</v>
+        <v>129543017</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457899</v>
+        <v>457657</v>
       </c>
       <c r="R17" t="n">
-        <v>6748444</v>
+        <v>6748226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543091</v>
+        <v>129543070</v>
       </c>
       <c r="B18" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457817</v>
+        <v>457936</v>
       </c>
       <c r="R18" t="n">
-        <v>6748202</v>
+        <v>6748379</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543092</v>
+        <v>129543043</v>
       </c>
       <c r="B19" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457785</v>
+        <v>457927</v>
       </c>
       <c r="R19" t="n">
-        <v>6748160</v>
+        <v>6748447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129542915</v>
+        <v>129542992</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457754</v>
+        <v>457763</v>
       </c>
       <c r="R20" t="n">
-        <v>6748230</v>
+        <v>6748301</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,7 +2721,7 @@
         <v>129542928</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129542913</v>
+        <v>129543107</v>
       </c>
       <c r="B22" t="n">
-        <v>79663</v>
+        <v>78736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457761</v>
+        <v>458144</v>
       </c>
       <c r="R22" t="n">
-        <v>6748133</v>
+        <v>6748538</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543107</v>
+        <v>129542996</v>
       </c>
       <c r="B23" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458144</v>
+        <v>457833</v>
       </c>
       <c r="R23" t="n">
-        <v>6748538</v>
+        <v>6748233</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129542996</v>
+        <v>129542913</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,21 +3055,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457833</v>
+        <v>457761</v>
       </c>
       <c r="R24" t="n">
-        <v>6748233</v>
+        <v>6748133</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,7 +3154,7 @@
         <v>129543038</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>129543005</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>129543051</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543045</v>
+        <v>129543032</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457912</v>
+        <v>457821</v>
       </c>
       <c r="R28" t="n">
-        <v>6748485</v>
+        <v>6748297</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,10 +3579,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543032</v>
+        <v>129542982</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457821</v>
+        <v>457941</v>
       </c>
       <c r="R29" t="n">
-        <v>6748297</v>
+        <v>6748477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3659,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,10 +3691,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129542982</v>
+        <v>129543045</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3721,10 +3726,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457941</v>
+        <v>457912</v>
       </c>
       <c r="R30" t="n">
-        <v>6748477</v>
+        <v>6748485</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3756,7 +3761,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,12 +3771,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3801,7 +3801,7 @@
         <v>129543090</v>
       </c>
       <c r="B31" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543018</v>
+        <v>129542993</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457679</v>
+        <v>457763</v>
       </c>
       <c r="R32" t="n">
-        <v>6748231</v>
+        <v>6748294</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543063</v>
+        <v>129543018</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458116</v>
+        <v>457679</v>
       </c>
       <c r="R33" t="n">
-        <v>6748548</v>
+        <v>6748231</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,10 +4119,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543059</v>
+        <v>129542966</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>78827</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,21 +4130,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458174</v>
+        <v>457938</v>
       </c>
       <c r="R34" t="n">
-        <v>6748599</v>
+        <v>6748466</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,10 +4226,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543021</v>
+        <v>129543063</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457756</v>
+        <v>458116</v>
       </c>
       <c r="R35" t="n">
-        <v>6748192</v>
+        <v>6748548</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,10 +4333,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129542993</v>
+        <v>129543059</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457763</v>
+        <v>458174</v>
       </c>
       <c r="R36" t="n">
-        <v>6748294</v>
+        <v>6748599</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,32 +4440,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129542942</v>
+        <v>129543021</v>
       </c>
       <c r="B37" t="n">
-        <v>97598</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457951</v>
+        <v>457756</v>
       </c>
       <c r="R37" t="n">
-        <v>6748543</v>
+        <v>6748192</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4547,32 +4547,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542966</v>
+        <v>129542942</v>
       </c>
       <c r="B38" t="n">
-        <v>78801</v>
+        <v>97627</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457938</v>
+        <v>457951</v>
       </c>
       <c r="R38" t="n">
-        <v>6748466</v>
+        <v>6748543</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4766,10 +4766,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543098</v>
+        <v>129542946</v>
       </c>
       <c r="B40" t="n">
-        <v>78710</v>
+        <v>91634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457657</v>
+        <v>458035</v>
       </c>
       <c r="R40" t="n">
-        <v>6748066</v>
+        <v>6748395</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543093</v>
+        <v>129543098</v>
       </c>
       <c r="B41" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457737</v>
+        <v>457657</v>
       </c>
       <c r="R41" t="n">
-        <v>6748103</v>
+        <v>6748066</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4980,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543071</v>
+        <v>129543093</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457928</v>
+        <v>457737</v>
       </c>
       <c r="R42" t="n">
-        <v>6748344</v>
+        <v>6748103</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5087,32 +5087,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129542998</v>
+        <v>129543112</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>91638</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457876</v>
+        <v>458029</v>
       </c>
       <c r="R43" t="n">
-        <v>6748240</v>
+        <v>6748411</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5176,6 +5176,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5194,10 +5195,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543003</v>
+        <v>129543071</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,10 +5230,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457814</v>
+        <v>457928</v>
       </c>
       <c r="R44" t="n">
-        <v>6748175</v>
+        <v>6748344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5264,7 +5265,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5275,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,10 +5302,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543057</v>
+        <v>129543003</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,10 +5337,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>458134</v>
+        <v>457814</v>
       </c>
       <c r="R45" t="n">
-        <v>6748614</v>
+        <v>6748175</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5371,7 +5372,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5381,7 +5382,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5408,10 +5409,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129542946</v>
+        <v>129543057</v>
       </c>
       <c r="B46" t="n">
-        <v>91606</v>
+        <v>79070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5419,21 +5420,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5443,10 +5444,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458035</v>
+        <v>458134</v>
       </c>
       <c r="R46" t="n">
-        <v>6748395</v>
+        <v>6748614</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5478,7 +5479,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5488,7 +5489,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5515,32 +5516,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543112</v>
+        <v>129542998</v>
       </c>
       <c r="B47" t="n">
-        <v>91610</v>
+        <v>79070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5550,10 +5551,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458029</v>
+        <v>457876</v>
       </c>
       <c r="R47" t="n">
-        <v>6748411</v>
+        <v>6748240</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5585,7 +5586,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5595,7 +5596,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,7 +5605,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>129542927</v>
       </c>
       <c r="B48" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543078</v>
+        <v>129543082</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457875</v>
+        <v>457792</v>
       </c>
       <c r="R49" t="n">
-        <v>6748394</v>
+        <v>6748260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5842,10 +5842,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543010</v>
+        <v>129543078</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457656</v>
+        <v>457875</v>
       </c>
       <c r="R50" t="n">
-        <v>6748084</v>
+        <v>6748394</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543009</v>
+        <v>129543010</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457654</v>
+        <v>457656</v>
       </c>
       <c r="R51" t="n">
-        <v>6748079</v>
+        <v>6748084</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6056,10 +6056,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543082</v>
+        <v>129543009</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6067,21 +6067,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457792</v>
+        <v>457654</v>
       </c>
       <c r="R52" t="n">
-        <v>6748260</v>
+        <v>6748079</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6163,10 +6163,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129542914</v>
+        <v>129543034</v>
       </c>
       <c r="B53" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6174,21 +6174,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457650</v>
+        <v>457852</v>
       </c>
       <c r="R53" t="n">
-        <v>6748064</v>
+        <v>6748316</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543034</v>
+        <v>129543035</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457852</v>
+        <v>457845</v>
       </c>
       <c r="R54" t="n">
-        <v>6748316</v>
+        <v>6748327</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6377,10 +6377,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543001</v>
+        <v>129542914</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6388,21 +6388,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457838</v>
+        <v>457650</v>
       </c>
       <c r="R55" t="n">
-        <v>6748208</v>
+        <v>6748064</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6484,10 +6484,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543064</v>
+        <v>129543066</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458049</v>
+        <v>458042</v>
       </c>
       <c r="R56" t="n">
-        <v>6748509</v>
+        <v>6748499</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6591,10 +6591,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543042</v>
+        <v>129543001</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457922</v>
+        <v>457838</v>
       </c>
       <c r="R57" t="n">
-        <v>6748447</v>
+        <v>6748208</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6698,10 +6698,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543072</v>
+        <v>129543064</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457899</v>
+        <v>458049</v>
       </c>
       <c r="R58" t="n">
-        <v>6748357</v>
+        <v>6748509</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6805,10 +6805,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543035</v>
+        <v>129543042</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457845</v>
+        <v>457922</v>
       </c>
       <c r="R59" t="n">
-        <v>6748327</v>
+        <v>6748447</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,10 +6912,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543066</v>
+        <v>129543072</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458042</v>
+        <v>457899</v>
       </c>
       <c r="R60" t="n">
-        <v>6748499</v>
+        <v>6748357</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7243,45 +7243,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543097</v>
+        <v>129542952</v>
       </c>
       <c r="B63" t="n">
-        <v>78710</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457673</v>
+        <v>458156</v>
       </c>
       <c r="R63" t="n">
-        <v>6748071</v>
+        <v>6748545</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7313,7 +7318,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7323,7 +7328,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7350,10 +7355,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129542962</v>
+        <v>129543097</v>
       </c>
       <c r="B64" t="n">
-        <v>78801</v>
+        <v>78736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7361,21 +7366,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7385,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457762</v>
+        <v>457673</v>
       </c>
       <c r="R64" t="n">
-        <v>6748208</v>
+        <v>6748071</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7425,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7435,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,10 +7462,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129542961</v>
+        <v>129543073</v>
       </c>
       <c r="B65" t="n">
-        <v>78801</v>
+        <v>79070</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7473,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,10 +7497,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457859</v>
+        <v>457917</v>
       </c>
       <c r="R65" t="n">
-        <v>6748231</v>
+        <v>6748303</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7527,7 +7532,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7537,7 +7542,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7564,10 +7569,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543073</v>
+        <v>129542962</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>78827</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7575,21 +7580,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7599,10 +7604,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457917</v>
+        <v>457762</v>
       </c>
       <c r="R66" t="n">
-        <v>6748303</v>
+        <v>6748208</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7634,7 +7639,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7644,7 +7649,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7674,7 +7679,7 @@
         <v>129543047</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7781,7 +7786,7 @@
         <v>129543019</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7885,10 +7890,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543060</v>
+        <v>129543029</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7920,10 +7925,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458177</v>
+        <v>457780</v>
       </c>
       <c r="R69" t="n">
-        <v>6748587</v>
+        <v>6748311</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7955,7 +7960,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7965,7 +7970,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7992,10 +7997,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543029</v>
+        <v>129542961</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>78827</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8003,21 +8008,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8027,10 +8032,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457780</v>
+        <v>457859</v>
       </c>
       <c r="R70" t="n">
-        <v>6748311</v>
+        <v>6748231</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8062,7 +8067,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8072,7 +8077,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8102,7 +8107,7 @@
         <v>129543002</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8214,7 @@
         <v>129543053</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8313,50 +8318,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129542952</v>
+        <v>129543060</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458156</v>
+        <v>458177</v>
       </c>
       <c r="R73" t="n">
-        <v>6748545</v>
+        <v>6748587</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8428,7 +8428,7 @@
         <v>129543101</v>
       </c>
       <c r="B74" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>129543105</v>
       </c>
       <c r="B75" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>129542997</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>129543000</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>129542999</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>129543075</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>129542933</v>
       </c>
       <c r="B80" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>129543103</v>
       </c>
       <c r="B81" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>129543088</v>
       </c>
       <c r="B82" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>129542964</v>
       </c>
       <c r="B83" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>129542968</v>
       </c>
       <c r="B84" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9607,10 +9607,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129542991</v>
+        <v>129543065</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>457762</v>
+        <v>458039</v>
       </c>
       <c r="R85" t="n">
-        <v>6748312</v>
+        <v>6748504</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9714,10 +9714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543065</v>
+        <v>129542991</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458039</v>
+        <v>457762</v>
       </c>
       <c r="R86" t="n">
-        <v>6748504</v>
+        <v>6748312</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9824,7 +9824,7 @@
         <v>129543085</v>
       </c>
       <c r="B87" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>129543076</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>129543049</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>129543028</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10254,54 +10254,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129542969</v>
+        <v>129542939</v>
       </c>
       <c r="B91" t="n">
-        <v>98727</v>
+        <v>97627</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457879</v>
+        <v>457660</v>
       </c>
       <c r="R91" t="n">
-        <v>6748454</v>
+        <v>6748092</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10333,7 +10324,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10343,7 +10334,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10370,45 +10361,54 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129542939</v>
+        <v>129542969</v>
       </c>
       <c r="B92" t="n">
-        <v>97598</v>
+        <v>98756</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457660</v>
+        <v>457879</v>
       </c>
       <c r="R92" t="n">
-        <v>6748092</v>
+        <v>6748454</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10477,10 +10477,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543013</v>
+        <v>129543099</v>
       </c>
       <c r="B93" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10488,21 +10488,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457621</v>
+        <v>457650</v>
       </c>
       <c r="R93" t="n">
-        <v>6748147</v>
+        <v>6748064</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10584,10 +10584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543014</v>
+        <v>129543104</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10595,21 +10595,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457634</v>
+        <v>457992</v>
       </c>
       <c r="R94" t="n">
-        <v>6748179</v>
+        <v>6748556</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10691,10 +10691,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543037</v>
+        <v>129543083</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10702,21 +10702,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457830</v>
+        <v>457757</v>
       </c>
       <c r="R95" t="n">
-        <v>6748350</v>
+        <v>6748191</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10798,10 +10798,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543039</v>
+        <v>129542956</v>
       </c>
       <c r="B96" t="n">
-        <v>79044</v>
+        <v>81055</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457830</v>
+        <v>457662</v>
       </c>
       <c r="R96" t="n">
-        <v>6748402</v>
+        <v>6748216</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10905,10 +10905,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543030</v>
+        <v>129543013</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457811</v>
+        <v>457621</v>
       </c>
       <c r="R97" t="n">
-        <v>6748293</v>
+        <v>6748147</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,10 +11012,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543020</v>
+        <v>129543037</v>
       </c>
       <c r="B98" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457738</v>
+        <v>457830</v>
       </c>
       <c r="R98" t="n">
-        <v>6748205</v>
+        <v>6748350</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543016</v>
+        <v>129543039</v>
       </c>
       <c r="B99" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11154,10 +11154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457699</v>
+        <v>457830</v>
       </c>
       <c r="R99" t="n">
-        <v>6748197</v>
+        <v>6748402</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,10 +11226,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543062</v>
+        <v>129543030</v>
       </c>
       <c r="B100" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>458140</v>
+        <v>457811</v>
       </c>
       <c r="R100" t="n">
-        <v>6748536</v>
+        <v>6748293</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,32 +11333,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129542960</v>
+        <v>129543020</v>
       </c>
       <c r="B101" t="n">
-        <v>80109</v>
+        <v>79070</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11368,10 +11368,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>458029</v>
+        <v>457738</v>
       </c>
       <c r="R101" t="n">
-        <v>6748413</v>
+        <v>6748205</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11413,12 +11413,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt på jätteasp</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11445,10 +11440,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129542956</v>
+        <v>129543016</v>
       </c>
       <c r="B102" t="n">
-        <v>81029</v>
+        <v>79070</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11456,21 +11451,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11480,10 +11475,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457662</v>
+        <v>457699</v>
       </c>
       <c r="R102" t="n">
-        <v>6748216</v>
+        <v>6748197</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11515,7 +11510,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11525,7 +11520,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11552,10 +11547,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543099</v>
+        <v>129543062</v>
       </c>
       <c r="B103" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11563,21 +11558,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11587,10 +11582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457650</v>
+        <v>458140</v>
       </c>
       <c r="R103" t="n">
-        <v>6748064</v>
+        <v>6748536</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11622,7 +11617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11632,7 +11627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11659,10 +11654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543104</v>
+        <v>129543014</v>
       </c>
       <c r="B104" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11670,21 +11665,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11694,10 +11689,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457992</v>
+        <v>457634</v>
       </c>
       <c r="R104" t="n">
-        <v>6748556</v>
+        <v>6748179</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11729,7 +11724,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11739,7 +11734,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11766,32 +11761,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543083</v>
+        <v>129542960</v>
       </c>
       <c r="B105" t="n">
-        <v>78710</v>
+        <v>80135</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11801,10 +11796,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>457757</v>
+        <v>458029</v>
       </c>
       <c r="R105" t="n">
-        <v>6748191</v>
+        <v>6748413</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11836,7 +11831,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11846,7 +11841,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Rikligt på jätteasp</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,32 +11873,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543095</v>
+        <v>129542981</v>
       </c>
       <c r="B106" t="n">
-        <v>78710</v>
+        <v>91754</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457704</v>
+        <v>457964</v>
       </c>
       <c r="R106" t="n">
-        <v>6748074</v>
+        <v>6748415</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11980,10 +11980,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543096</v>
+        <v>129543094</v>
       </c>
       <c r="B107" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457671</v>
+        <v>457728</v>
       </c>
       <c r="R107" t="n">
-        <v>6748048</v>
+        <v>6748093</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12087,10 +12087,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129543012</v>
+        <v>129543095</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12098,21 +12098,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457625</v>
+        <v>457704</v>
       </c>
       <c r="R108" t="n">
-        <v>6748127</v>
+        <v>6748074</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12194,50 +12194,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543111</v>
+        <v>129543096</v>
       </c>
       <c r="B109" t="n">
-        <v>5177</v>
+        <v>78736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457665</v>
+        <v>457671</v>
       </c>
       <c r="R109" t="n">
-        <v>6748081</v>
+        <v>6748048</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12269,7 +12264,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12279,7 +12274,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12306,45 +12301,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129542981</v>
+        <v>129543111</v>
       </c>
       <c r="B110" t="n">
-        <v>91726</v>
+        <v>5177</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1503</v>
+        <v>100526</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457964</v>
+        <v>457665</v>
       </c>
       <c r="R110" t="n">
-        <v>6748415</v>
+        <v>6748081</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12413,10 +12413,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543094</v>
+        <v>129543012</v>
       </c>
       <c r="B111" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12424,21 +12424,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457728</v>
+        <v>457625</v>
       </c>
       <c r="R111" t="n">
-        <v>6748093</v>
+        <v>6748127</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12520,10 +12520,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129542955</v>
+        <v>129542923</v>
       </c>
       <c r="B112" t="n">
-        <v>92195</v>
+        <v>79165</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12531,21 +12531,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5454</v>
+        <v>967</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458015</v>
+        <v>457773</v>
       </c>
       <c r="R112" t="n">
-        <v>6748399</v>
+        <v>6748248</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12627,10 +12627,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129542935</v>
+        <v>129542955</v>
       </c>
       <c r="B113" t="n">
-        <v>57724</v>
+        <v>92223</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12638,39 +12638,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>5454</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458060</v>
+        <v>458015</v>
       </c>
       <c r="R113" t="n">
-        <v>6748631</v>
+        <v>6748399</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12702,7 +12697,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12712,7 +12707,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12739,32 +12734,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129542944</v>
+        <v>129543008</v>
       </c>
       <c r="B114" t="n">
-        <v>97604</v>
+        <v>79070</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12774,10 +12769,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>457654</v>
+        <v>457671</v>
       </c>
       <c r="R114" t="n">
-        <v>6748070</v>
+        <v>6748048</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12809,7 +12804,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12819,7 +12814,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12846,10 +12841,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129542923</v>
+        <v>129542935</v>
       </c>
       <c r="B115" t="n">
-        <v>79139</v>
+        <v>57727</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12857,34 +12852,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457773</v>
+        <v>458060</v>
       </c>
       <c r="R115" t="n">
-        <v>6748248</v>
+        <v>6748631</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12956,7 +12956,7 @@
         <v>129543011</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13060,32 +13060,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129543008</v>
+        <v>129542944</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>97633</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457671</v>
+        <v>457654</v>
       </c>
       <c r="R117" t="n">
-        <v>6748048</v>
+        <v>6748070</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13167,10 +13167,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129543061</v>
+        <v>129543054</v>
       </c>
       <c r="B118" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458155</v>
+        <v>458097</v>
       </c>
       <c r="R118" t="n">
-        <v>6748548</v>
+        <v>6748662</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13274,10 +13274,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129543054</v>
+        <v>129543061</v>
       </c>
       <c r="B119" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458097</v>
+        <v>458155</v>
       </c>
       <c r="R119" t="n">
-        <v>6748662</v>
+        <v>6748548</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13344,7 +13344,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13496,7 +13496,7 @@
         <v>129543102</v>
       </c>
       <c r="B121" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13600,10 +13600,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129543046</v>
+        <v>129542967</v>
       </c>
       <c r="B122" t="n">
-        <v>79044</v>
+        <v>78827</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>457946</v>
+        <v>457939</v>
       </c>
       <c r="R122" t="n">
-        <v>6748493</v>
+        <v>6748494</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13710,7 +13710,7 @@
         <v>129543048</v>
       </c>
       <c r="B123" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>129543004</v>
       </c>
       <c r="B124" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>129543025</v>
       </c>
       <c r="B125" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14028,10 +14028,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129543015</v>
+        <v>129542978</v>
       </c>
       <c r="B126" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457689</v>
+        <v>457802</v>
       </c>
       <c r="R126" t="n">
-        <v>6748165</v>
+        <v>6748301</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14135,10 +14135,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129542978</v>
+        <v>129543027</v>
       </c>
       <c r="B127" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>457802</v>
+        <v>457756</v>
       </c>
       <c r="R127" t="n">
-        <v>6748301</v>
+        <v>6748271</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14242,10 +14242,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129543027</v>
+        <v>129543015</v>
       </c>
       <c r="B128" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457756</v>
+        <v>457689</v>
       </c>
       <c r="R128" t="n">
-        <v>6748271</v>
+        <v>6748165</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14352,7 +14352,7 @@
         <v>129542936</v>
       </c>
       <c r="B129" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14461,10 +14461,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129542967</v>
+        <v>129543046</v>
       </c>
       <c r="B130" t="n">
-        <v>78801</v>
+        <v>79070</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14472,21 +14472,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14496,10 +14496,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>457939</v>
+        <v>457946</v>
       </c>
       <c r="R130" t="n">
-        <v>6748494</v>
+        <v>6748493</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14571,7 +14571,7 @@
         <v>129542940</v>
       </c>
       <c r="B131" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>129542920</v>
       </c>
       <c r="B132" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14782,10 +14782,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129542916</v>
+        <v>129543077</v>
       </c>
       <c r="B133" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14793,21 +14793,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457750</v>
+        <v>457938</v>
       </c>
       <c r="R133" t="n">
-        <v>6748276</v>
+        <v>6748409</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14889,10 +14889,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129543077</v>
+        <v>129543040</v>
       </c>
       <c r="B134" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>457938</v>
+        <v>457817</v>
       </c>
       <c r="R134" t="n">
-        <v>6748409</v>
+        <v>6748400</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129543040</v>
+        <v>129543044</v>
       </c>
       <c r="B135" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457817</v>
+        <v>457939</v>
       </c>
       <c r="R135" t="n">
-        <v>6748400</v>
+        <v>6748453</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15103,10 +15103,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129543044</v>
+        <v>129542916</v>
       </c>
       <c r="B136" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15114,21 +15114,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>457939</v>
+        <v>457750</v>
       </c>
       <c r="R136" t="n">
-        <v>6748453</v>
+        <v>6748276</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15213,7 +15213,7 @@
         <v>129543050</v>
       </c>
       <c r="B137" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>129543036</v>
       </c>
       <c r="B138" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>129543058</v>
       </c>
       <c r="B139" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15531,10 +15531,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129542963</v>
+        <v>129543089</v>
       </c>
       <c r="B140" t="n">
-        <v>78801</v>
+        <v>78736</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>457754</v>
+        <v>457809</v>
       </c>
       <c r="R140" t="n">
-        <v>6748230</v>
+        <v>6748254</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15638,10 +15638,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129542965</v>
+        <v>129542958</v>
       </c>
       <c r="B141" t="n">
-        <v>78801</v>
+        <v>81055</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457760</v>
+        <v>458029</v>
       </c>
       <c r="R141" t="n">
-        <v>6748255</v>
+        <v>6748402</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15745,10 +15745,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129542958</v>
+        <v>129542963</v>
       </c>
       <c r="B142" t="n">
-        <v>81029</v>
+        <v>78827</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15756,21 +15756,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>458029</v>
+        <v>457754</v>
       </c>
       <c r="R142" t="n">
-        <v>6748402</v>
+        <v>6748230</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15855,7 +15855,7 @@
         <v>129543074</v>
       </c>
       <c r="B143" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15959,10 +15959,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129543022</v>
+        <v>129542965</v>
       </c>
       <c r="B144" t="n">
-        <v>79044</v>
+        <v>78827</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15970,21 +15970,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457761</v>
+        <v>457760</v>
       </c>
       <c r="R144" t="n">
-        <v>6748192</v>
+        <v>6748255</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16066,10 +16066,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129543052</v>
+        <v>129543022</v>
       </c>
       <c r="B145" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>458081</v>
+        <v>457761</v>
       </c>
       <c r="R145" t="n">
-        <v>6748667</v>
+        <v>6748192</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16173,10 +16173,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129543089</v>
+        <v>129543052</v>
       </c>
       <c r="B146" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16184,21 +16184,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>457809</v>
+        <v>458081</v>
       </c>
       <c r="R146" t="n">
-        <v>6748254</v>
+        <v>6748667</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16280,32 +16280,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129542941</v>
+        <v>129543100</v>
       </c>
       <c r="B147" t="n">
-        <v>97598</v>
+        <v>78736</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457929</v>
+        <v>457631</v>
       </c>
       <c r="R147" t="n">
-        <v>6748448</v>
+        <v>6748174</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,10 +16387,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129543100</v>
+        <v>129543069</v>
       </c>
       <c r="B148" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16398,21 +16398,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457631</v>
+        <v>457930</v>
       </c>
       <c r="R148" t="n">
-        <v>6748174</v>
+        <v>6748385</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16494,10 +16494,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129543069</v>
+        <v>129542994</v>
       </c>
       <c r="B149" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457930</v>
+        <v>457786</v>
       </c>
       <c r="R149" t="n">
-        <v>6748385</v>
+        <v>6748280</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16601,10 +16601,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129542994</v>
+        <v>129543023</v>
       </c>
       <c r="B150" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457786</v>
+        <v>457758</v>
       </c>
       <c r="R150" t="n">
-        <v>6748280</v>
+        <v>6748213</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16711,7 +16711,7 @@
         <v>129543006</v>
       </c>
       <c r="B151" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16815,32 +16815,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129543023</v>
+        <v>129542941</v>
       </c>
       <c r="B152" t="n">
-        <v>79044</v>
+        <v>97627</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457758</v>
+        <v>457929</v>
       </c>
       <c r="R152" t="n">
-        <v>6748213</v>
+        <v>6748448</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129542945</v>
+        <v>129543068</v>
       </c>
       <c r="B153" t="n">
-        <v>97604</v>
+        <v>79070</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>457654</v>
+        <v>457935</v>
       </c>
       <c r="R153" t="n">
-        <v>6748079</v>
+        <v>6748390</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17029,32 +17029,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129542943</v>
+        <v>129542959</v>
       </c>
       <c r="B154" t="n">
-        <v>97598</v>
+        <v>81055</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221945</v>
+        <v>1049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457999</v>
+        <v>457884</v>
       </c>
       <c r="R154" t="n">
-        <v>6748381</v>
+        <v>6748404</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17136,32 +17136,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129542959</v>
+        <v>129542980</v>
       </c>
       <c r="B155" t="n">
-        <v>81029</v>
+        <v>91754</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>457884</v>
+        <v>458058</v>
       </c>
       <c r="R155" t="n">
-        <v>6748404</v>
+        <v>6748621</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542980</v>
+        <v>129543067</v>
       </c>
       <c r="B156" t="n">
-        <v>91726</v>
+        <v>79070</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>458058</v>
+        <v>457946</v>
       </c>
       <c r="R156" t="n">
-        <v>6748621</v>
+        <v>6748380</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17350,10 +17350,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129543068</v>
+        <v>129543033</v>
       </c>
       <c r="B157" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457935</v>
+        <v>457836</v>
       </c>
       <c r="R157" t="n">
-        <v>6748390</v>
+        <v>6748291</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17457,32 +17457,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129543067</v>
+        <v>129542945</v>
       </c>
       <c r="B158" t="n">
-        <v>79044</v>
+        <v>97633</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457946</v>
+        <v>457654</v>
       </c>
       <c r="R158" t="n">
-        <v>6748380</v>
+        <v>6748079</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17564,32 +17564,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129543033</v>
+        <v>129542943</v>
       </c>
       <c r="B159" t="n">
-        <v>79044</v>
+        <v>97627</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457836</v>
+        <v>457999</v>
       </c>
       <c r="R159" t="n">
-        <v>6748291</v>
+        <v>6748381</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -3905,45 +3905,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129542993</v>
+        <v>129542949</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457763</v>
+        <v>457627</v>
       </c>
       <c r="R32" t="n">
-        <v>6748294</v>
+        <v>6748161</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,7 +4017,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543018</v>
+        <v>129542993</v>
       </c>
       <c r="B33" t="n">
         <v>79070</v>
@@ -4047,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457679</v>
+        <v>457763</v>
       </c>
       <c r="R33" t="n">
-        <v>6748231</v>
+        <v>6748294</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,32 +4124,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129542966</v>
+        <v>129542942</v>
       </c>
       <c r="B34" t="n">
-        <v>78827</v>
+        <v>97627</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,10 +4159,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457938</v>
+        <v>457951</v>
       </c>
       <c r="R34" t="n">
-        <v>6748466</v>
+        <v>6748543</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,7 +4231,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543063</v>
+        <v>129543018</v>
       </c>
       <c r="B35" t="n">
         <v>79070</v>
@@ -4261,10 +4266,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458116</v>
+        <v>457679</v>
       </c>
       <c r="R35" t="n">
-        <v>6748548</v>
+        <v>6748231</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,10 +4338,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543059</v>
+        <v>129542966</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>78827</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,21 +4349,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4368,10 +4373,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458174</v>
+        <v>457938</v>
       </c>
       <c r="R36" t="n">
-        <v>6748599</v>
+        <v>6748466</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4408,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4418,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,7 +4445,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129543021</v>
+        <v>129543063</v>
       </c>
       <c r="B37" t="n">
         <v>79070</v>
@@ -4475,10 +4480,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457756</v>
+        <v>458116</v>
       </c>
       <c r="R37" t="n">
-        <v>6748192</v>
+        <v>6748548</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4510,7 +4515,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4520,7 +4525,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4547,32 +4552,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542942</v>
+        <v>129543059</v>
       </c>
       <c r="B38" t="n">
-        <v>97627</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4582,10 +4587,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457951</v>
+        <v>458174</v>
       </c>
       <c r="R38" t="n">
-        <v>6748543</v>
+        <v>6748599</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4617,7 +4622,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4627,7 +4632,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4654,50 +4659,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129542949</v>
+        <v>129543021</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457627</v>
+        <v>457756</v>
       </c>
       <c r="R39" t="n">
-        <v>6748161</v>
+        <v>6748192</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -9821,45 +9821,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543085</v>
+        <v>129542969</v>
       </c>
       <c r="B87" t="n">
-        <v>78736</v>
+        <v>98756</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457880</v>
+        <v>457879</v>
       </c>
       <c r="R87" t="n">
-        <v>6748247</v>
+        <v>6748454</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9891,7 +9900,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9901,12 +9910,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På högstubbe med fem brandljud</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9933,32 +9937,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543076</v>
+        <v>129542939</v>
       </c>
       <c r="B88" t="n">
-        <v>79070</v>
+        <v>97627</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9968,10 +9972,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457917</v>
+        <v>457660</v>
       </c>
       <c r="R88" t="n">
-        <v>6748390</v>
+        <v>6748092</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10003,7 +10007,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10013,7 +10017,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10040,10 +10044,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543049</v>
+        <v>129543085</v>
       </c>
       <c r="B89" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10051,21 +10055,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10075,10 +10079,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458018</v>
+        <v>457880</v>
       </c>
       <c r="R89" t="n">
-        <v>6748602</v>
+        <v>6748247</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10110,7 +10114,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10120,7 +10124,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På högstubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10147,7 +10156,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543028</v>
+        <v>129543076</v>
       </c>
       <c r="B90" t="n">
         <v>79070</v>
@@ -10182,10 +10191,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457753</v>
+        <v>457917</v>
       </c>
       <c r="R90" t="n">
-        <v>6748290</v>
+        <v>6748390</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10217,7 +10226,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10227,7 +10236,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10254,32 +10263,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129542939</v>
+        <v>129543049</v>
       </c>
       <c r="B91" t="n">
-        <v>97627</v>
+        <v>79070</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10289,10 +10298,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457660</v>
+        <v>458018</v>
       </c>
       <c r="R91" t="n">
-        <v>6748092</v>
+        <v>6748602</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10324,7 +10333,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10334,7 +10343,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10361,54 +10370,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129542969</v>
+        <v>129543028</v>
       </c>
       <c r="B92" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457879</v>
+        <v>457753</v>
       </c>
       <c r="R92" t="n">
-        <v>6748454</v>
+        <v>6748290</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10477,32 +10477,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543099</v>
+        <v>129542960</v>
       </c>
       <c r="B93" t="n">
-        <v>78736</v>
+        <v>80135</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457650</v>
+        <v>458029</v>
       </c>
       <c r="R93" t="n">
-        <v>6748064</v>
+        <v>6748413</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,7 +10557,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Rikligt på jätteasp</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10584,10 +10589,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543104</v>
+        <v>129543014</v>
       </c>
       <c r="B94" t="n">
-        <v>78736</v>
+        <v>79070</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10595,21 +10600,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10619,10 +10624,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457992</v>
+        <v>457634</v>
       </c>
       <c r="R94" t="n">
-        <v>6748556</v>
+        <v>6748179</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10654,7 +10659,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10664,7 +10669,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10691,7 +10696,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543083</v>
+        <v>129543099</v>
       </c>
       <c r="B95" t="n">
         <v>78736</v>
@@ -10726,10 +10731,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457757</v>
+        <v>457650</v>
       </c>
       <c r="R95" t="n">
-        <v>6748191</v>
+        <v>6748064</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10761,7 +10766,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10771,7 +10776,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10798,10 +10803,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129542956</v>
+        <v>129543104</v>
       </c>
       <c r="B96" t="n">
-        <v>81055</v>
+        <v>78736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10809,21 +10814,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10833,10 +10838,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457662</v>
+        <v>457992</v>
       </c>
       <c r="R96" t="n">
-        <v>6748216</v>
+        <v>6748556</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10868,7 +10873,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10878,7 +10883,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10905,10 +10910,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543013</v>
+        <v>129543083</v>
       </c>
       <c r="B97" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10916,21 +10921,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10940,10 +10945,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457621</v>
+        <v>457757</v>
       </c>
       <c r="R97" t="n">
-        <v>6748147</v>
+        <v>6748191</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10975,7 +10980,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10990,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,10 +11017,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543037</v>
+        <v>129542956</v>
       </c>
       <c r="B98" t="n">
-        <v>79070</v>
+        <v>81055</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11023,21 +11028,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11047,10 +11052,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457830</v>
+        <v>457662</v>
       </c>
       <c r="R98" t="n">
-        <v>6748350</v>
+        <v>6748216</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,7 +11087,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11097,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,7 +11124,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543039</v>
+        <v>129543013</v>
       </c>
       <c r="B99" t="n">
         <v>79070</v>
@@ -11154,10 +11159,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457830</v>
+        <v>457621</v>
       </c>
       <c r="R99" t="n">
-        <v>6748402</v>
+        <v>6748147</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,7 +11194,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11199,7 +11204,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,7 +11231,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543030</v>
+        <v>129543037</v>
       </c>
       <c r="B100" t="n">
         <v>79070</v>
@@ -11261,10 +11266,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457811</v>
+        <v>457830</v>
       </c>
       <c r="R100" t="n">
-        <v>6748293</v>
+        <v>6748350</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11296,7 +11301,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11306,7 +11311,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,7 +11338,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543020</v>
+        <v>129543039</v>
       </c>
       <c r="B101" t="n">
         <v>79070</v>
@@ -11368,10 +11373,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457738</v>
+        <v>457830</v>
       </c>
       <c r="R101" t="n">
-        <v>6748205</v>
+        <v>6748402</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,7 +11408,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11413,7 +11418,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11440,7 +11445,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543016</v>
+        <v>129543030</v>
       </c>
       <c r="B102" t="n">
         <v>79070</v>
@@ -11475,10 +11480,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457699</v>
+        <v>457811</v>
       </c>
       <c r="R102" t="n">
-        <v>6748197</v>
+        <v>6748293</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,7 +11515,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11520,7 +11525,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11547,7 +11552,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543062</v>
+        <v>129543020</v>
       </c>
       <c r="B103" t="n">
         <v>79070</v>
@@ -11582,10 +11587,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458140</v>
+        <v>457738</v>
       </c>
       <c r="R103" t="n">
-        <v>6748536</v>
+        <v>6748205</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,7 +11622,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11627,7 +11632,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11654,7 +11659,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543014</v>
+        <v>129543016</v>
       </c>
       <c r="B104" t="n">
         <v>79070</v>
@@ -11689,10 +11694,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457634</v>
+        <v>457699</v>
       </c>
       <c r="R104" t="n">
-        <v>6748179</v>
+        <v>6748197</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11724,7 +11729,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11734,7 +11739,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11761,32 +11766,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129542960</v>
+        <v>129543062</v>
       </c>
       <c r="B105" t="n">
-        <v>80135</v>
+        <v>79070</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11796,10 +11801,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458029</v>
+        <v>458140</v>
       </c>
       <c r="R105" t="n">
-        <v>6748413</v>
+        <v>6748536</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11831,7 +11836,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11841,12 +11846,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Rikligt på jätteasp</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,45 +11873,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129542981</v>
+        <v>129543111</v>
       </c>
       <c r="B106" t="n">
-        <v>91754</v>
+        <v>5177</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1503</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457964</v>
+        <v>457665</v>
       </c>
       <c r="R106" t="n">
-        <v>6748415</v>
+        <v>6748081</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11943,7 +11948,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11953,7 +11958,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11980,10 +11985,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543094</v>
+        <v>129543012</v>
       </c>
       <c r="B107" t="n">
-        <v>78736</v>
+        <v>79070</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11991,21 +11996,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12015,10 +12020,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457728</v>
+        <v>457625</v>
       </c>
       <c r="R107" t="n">
-        <v>6748093</v>
+        <v>6748127</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12050,7 +12055,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12060,7 +12065,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12087,32 +12092,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129543095</v>
+        <v>129542981</v>
       </c>
       <c r="B108" t="n">
-        <v>78736</v>
+        <v>91754</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12122,10 +12127,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457704</v>
+        <v>457964</v>
       </c>
       <c r="R108" t="n">
-        <v>6748074</v>
+        <v>6748415</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,7 +12162,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12167,7 +12172,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12194,7 +12199,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543096</v>
+        <v>129543094</v>
       </c>
       <c r="B109" t="n">
         <v>78736</v>
@@ -12229,10 +12234,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457671</v>
+        <v>457728</v>
       </c>
       <c r="R109" t="n">
-        <v>6748048</v>
+        <v>6748093</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12264,7 +12269,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12274,7 +12279,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12301,50 +12306,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543111</v>
+        <v>129543095</v>
       </c>
       <c r="B110" t="n">
-        <v>5177</v>
+        <v>78736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457665</v>
+        <v>457704</v>
       </c>
       <c r="R110" t="n">
-        <v>6748081</v>
+        <v>6748074</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12413,10 +12413,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543012</v>
+        <v>129543096</v>
       </c>
       <c r="B111" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12424,21 +12424,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457625</v>
+        <v>457671</v>
       </c>
       <c r="R111" t="n">
-        <v>6748127</v>
+        <v>6748048</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12520,10 +12520,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129542923</v>
+        <v>129543011</v>
       </c>
       <c r="B112" t="n">
-        <v>79165</v>
+        <v>79070</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12531,21 +12531,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>457773</v>
+        <v>457665</v>
       </c>
       <c r="R112" t="n">
-        <v>6748248</v>
+        <v>6748082</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12627,10 +12627,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129542955</v>
+        <v>129542923</v>
       </c>
       <c r="B113" t="n">
-        <v>92223</v>
+        <v>79165</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12638,21 +12638,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5454</v>
+        <v>967</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12662,10 +12662,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458015</v>
+        <v>457773</v>
       </c>
       <c r="R113" t="n">
-        <v>6748399</v>
+        <v>6748248</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12734,10 +12734,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129543008</v>
+        <v>129542955</v>
       </c>
       <c r="B114" t="n">
-        <v>79070</v>
+        <v>92223</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12745,21 +12745,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12769,10 +12769,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>457671</v>
+        <v>458015</v>
       </c>
       <c r="R114" t="n">
-        <v>6748048</v>
+        <v>6748399</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12841,10 +12841,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129542935</v>
+        <v>129543008</v>
       </c>
       <c r="B115" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12852,39 +12852,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458060</v>
+        <v>457671</v>
       </c>
       <c r="R115" t="n">
-        <v>6748631</v>
+        <v>6748048</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12911,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12926,7 +12921,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12953,10 +12948,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129543011</v>
+        <v>129542935</v>
       </c>
       <c r="B116" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12964,34 +12959,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457665</v>
+        <v>458060</v>
       </c>
       <c r="R116" t="n">
-        <v>6748082</v>
+        <v>6748631</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13167,45 +13167,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129543054</v>
+        <v>129542947</v>
       </c>
       <c r="B118" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458097</v>
+        <v>457929</v>
       </c>
       <c r="R118" t="n">
-        <v>6748662</v>
+        <v>6748484</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13237,7 +13242,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13247,7 +13252,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13381,50 +13386,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129542947</v>
+        <v>129543054</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>457929</v>
+        <v>458097</v>
       </c>
       <c r="R120" t="n">
-        <v>6748484</v>
+        <v>6748662</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15531,10 +15531,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129543089</v>
+        <v>129542958</v>
       </c>
       <c r="B140" t="n">
-        <v>78736</v>
+        <v>81055</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>457809</v>
+        <v>458029</v>
       </c>
       <c r="R140" t="n">
-        <v>6748254</v>
+        <v>6748402</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15638,10 +15638,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129542958</v>
+        <v>129542963</v>
       </c>
       <c r="B141" t="n">
-        <v>81055</v>
+        <v>78827</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>458029</v>
+        <v>457754</v>
       </c>
       <c r="R141" t="n">
-        <v>6748402</v>
+        <v>6748230</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15745,10 +15745,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129542963</v>
+        <v>129543074</v>
       </c>
       <c r="B142" t="n">
-        <v>78827</v>
+        <v>79070</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15756,21 +15756,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457754</v>
+        <v>457905</v>
       </c>
       <c r="R142" t="n">
-        <v>6748230</v>
+        <v>6748321</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15852,10 +15852,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129543074</v>
+        <v>129542965</v>
       </c>
       <c r="B143" t="n">
-        <v>79070</v>
+        <v>78827</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15863,21 +15863,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457905</v>
+        <v>457760</v>
       </c>
       <c r="R143" t="n">
-        <v>6748321</v>
+        <v>6748255</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129542965</v>
+        <v>129543022</v>
       </c>
       <c r="B144" t="n">
-        <v>78827</v>
+        <v>79070</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15970,21 +15970,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457760</v>
+        <v>457761</v>
       </c>
       <c r="R144" t="n">
-        <v>6748255</v>
+        <v>6748192</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16066,7 +16066,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129543022</v>
+        <v>129543052</v>
       </c>
       <c r="B145" t="n">
         <v>79070</v>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>457761</v>
+        <v>458081</v>
       </c>
       <c r="R145" t="n">
-        <v>6748192</v>
+        <v>6748667</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16173,10 +16173,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129543052</v>
+        <v>129543089</v>
       </c>
       <c r="B146" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16184,21 +16184,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>458081</v>
+        <v>457809</v>
       </c>
       <c r="R146" t="n">
-        <v>6748667</v>
+        <v>6748254</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16280,10 +16280,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129543100</v>
+        <v>129543069</v>
       </c>
       <c r="B147" t="n">
-        <v>78736</v>
+        <v>79070</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16291,21 +16291,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457631</v>
+        <v>457930</v>
       </c>
       <c r="R147" t="n">
-        <v>6748174</v>
+        <v>6748385</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,7 +16387,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129543069</v>
+        <v>129542994</v>
       </c>
       <c r="B148" t="n">
         <v>79070</v>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457930</v>
+        <v>457786</v>
       </c>
       <c r="R148" t="n">
-        <v>6748385</v>
+        <v>6748280</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16494,7 +16494,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129542994</v>
+        <v>129543023</v>
       </c>
       <c r="B149" t="n">
         <v>79070</v>
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457786</v>
+        <v>457758</v>
       </c>
       <c r="R149" t="n">
-        <v>6748280</v>
+        <v>6748213</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16601,32 +16601,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129543023</v>
+        <v>129542941</v>
       </c>
       <c r="B150" t="n">
-        <v>79070</v>
+        <v>97627</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457758</v>
+        <v>457929</v>
       </c>
       <c r="R150" t="n">
-        <v>6748213</v>
+        <v>6748448</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16708,10 +16708,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129543006</v>
+        <v>129543100</v>
       </c>
       <c r="B151" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16719,21 +16719,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16743,10 +16743,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457712</v>
+        <v>457631</v>
       </c>
       <c r="R151" t="n">
-        <v>6748081</v>
+        <v>6748174</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16815,32 +16815,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129542941</v>
+        <v>129543006</v>
       </c>
       <c r="B152" t="n">
-        <v>97627</v>
+        <v>79070</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457929</v>
+        <v>457712</v>
       </c>
       <c r="R152" t="n">
-        <v>6748448</v>
+        <v>6748081</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17029,10 +17029,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129542959</v>
+        <v>129543067</v>
       </c>
       <c r="B154" t="n">
-        <v>81055</v>
+        <v>79070</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17040,21 +17040,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457884</v>
+        <v>457946</v>
       </c>
       <c r="R154" t="n">
-        <v>6748404</v>
+        <v>6748380</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17136,32 +17136,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129542980</v>
+        <v>129543033</v>
       </c>
       <c r="B155" t="n">
-        <v>91754</v>
+        <v>79070</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>458058</v>
+        <v>457836</v>
       </c>
       <c r="R155" t="n">
-        <v>6748621</v>
+        <v>6748291</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17243,10 +17243,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129543067</v>
+        <v>129542959</v>
       </c>
       <c r="B156" t="n">
-        <v>79070</v>
+        <v>81055</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17254,21 +17254,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>457946</v>
+        <v>457884</v>
       </c>
       <c r="R156" t="n">
-        <v>6748380</v>
+        <v>6748404</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17350,32 +17350,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129543033</v>
+        <v>129542980</v>
       </c>
       <c r="B157" t="n">
-        <v>79070</v>
+        <v>91754</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457836</v>
+        <v>458058</v>
       </c>
       <c r="R157" t="n">
-        <v>6748291</v>
+        <v>6748621</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD157" t="b">

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129543108</v>
+        <v>129543056</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458131</v>
+        <v>458120</v>
       </c>
       <c r="R2" t="n">
-        <v>6748548</v>
+        <v>6748624</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129543007</v>
+        <v>129542925</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457677</v>
+        <v>457896</v>
       </c>
       <c r="R3" t="n">
-        <v>6748051</v>
+        <v>6748335</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543031</v>
+        <v>129543108</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457809</v>
+        <v>458131</v>
       </c>
       <c r="R4" t="n">
-        <v>6748286</v>
+        <v>6748548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543024</v>
+        <v>129543007</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457755</v>
+        <v>457677</v>
       </c>
       <c r="R5" t="n">
-        <v>6748219</v>
+        <v>6748051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543041</v>
+        <v>129543031</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457854</v>
+        <v>457809</v>
       </c>
       <c r="R6" t="n">
-        <v>6748444</v>
+        <v>6748286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543026</v>
+        <v>129543024</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457758</v>
+        <v>457755</v>
       </c>
       <c r="R7" t="n">
-        <v>6748263</v>
+        <v>6748219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543056</v>
+        <v>129543041</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458120</v>
+        <v>457854</v>
       </c>
       <c r="R8" t="n">
-        <v>6748624</v>
+        <v>6748444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,50 +1429,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129542925</v>
+        <v>129543026</v>
       </c>
       <c r="B9" t="n">
-        <v>56920</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457896</v>
+        <v>457758</v>
       </c>
       <c r="R9" t="n">
-        <v>6748335</v>
+        <v>6748263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,32 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543081</v>
+        <v>129542924</v>
       </c>
       <c r="B11" t="n">
-        <v>91854</v>
+        <v>91587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458131</v>
+        <v>457899</v>
       </c>
       <c r="R11" t="n">
-        <v>6748547</v>
+        <v>6748444</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543091</v>
+        <v>129543081</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>91860</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457817</v>
+        <v>458131</v>
       </c>
       <c r="R12" t="n">
-        <v>6748202</v>
+        <v>6748547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543092</v>
+        <v>129543091</v>
       </c>
       <c r="B13" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457785</v>
+        <v>457817</v>
       </c>
       <c r="R13" t="n">
-        <v>6748160</v>
+        <v>6748202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129542924</v>
+        <v>129543092</v>
       </c>
       <c r="B14" t="n">
-        <v>91581</v>
+        <v>78741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457899</v>
+        <v>457785</v>
       </c>
       <c r="R14" t="n">
-        <v>6748444</v>
+        <v>6748160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129542995</v>
+        <v>129543043</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457809</v>
+        <v>457927</v>
       </c>
       <c r="R15" t="n">
-        <v>6748246</v>
+        <v>6748447</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129542915</v>
+        <v>129542992</v>
       </c>
       <c r="B16" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457754</v>
+        <v>457763</v>
       </c>
       <c r="R16" t="n">
-        <v>6748230</v>
+        <v>6748301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,7 +2293,7 @@
         <v>129543017</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129543070</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543043</v>
+        <v>129542995</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457927</v>
+        <v>457809</v>
       </c>
       <c r="R19" t="n">
-        <v>6748447</v>
+        <v>6748246</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129542992</v>
+        <v>129542915</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457763</v>
+        <v>457754</v>
       </c>
       <c r="R20" t="n">
-        <v>6748301</v>
+        <v>6748230</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,7 +2721,7 @@
         <v>129542928</v>
       </c>
       <c r="B21" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129543107</v>
       </c>
       <c r="B22" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129542996</v>
+        <v>129542913</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457833</v>
+        <v>457761</v>
       </c>
       <c r="R23" t="n">
-        <v>6748233</v>
+        <v>6748133</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129542913</v>
+        <v>129543038</v>
       </c>
       <c r="B24" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,21 +3055,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457761</v>
+        <v>457829</v>
       </c>
       <c r="R24" t="n">
-        <v>6748133</v>
+        <v>6748366</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,10 +3151,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543038</v>
+        <v>129543045</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457829</v>
+        <v>457912</v>
       </c>
       <c r="R25" t="n">
-        <v>6748366</v>
+        <v>6748485</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543005</v>
+        <v>129542996</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457775</v>
+        <v>457833</v>
       </c>
       <c r="R26" t="n">
-        <v>6748148</v>
+        <v>6748233</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,10 +3365,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543051</v>
+        <v>129543005</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458077</v>
+        <v>457775</v>
       </c>
       <c r="R27" t="n">
-        <v>6748657</v>
+        <v>6748148</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,10 +3472,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543032</v>
+        <v>129543051</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457821</v>
+        <v>458077</v>
       </c>
       <c r="R28" t="n">
-        <v>6748297</v>
+        <v>6748657</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,10 +3579,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129542982</v>
+        <v>129543032</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457941</v>
+        <v>457821</v>
       </c>
       <c r="R29" t="n">
-        <v>6748477</v>
+        <v>6748297</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,12 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3691,10 +3686,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543045</v>
+        <v>129542982</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457912</v>
+        <v>457941</v>
       </c>
       <c r="R30" t="n">
-        <v>6748485</v>
+        <v>6748477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3771,7 +3766,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543090</v>
+        <v>129543063</v>
       </c>
       <c r="B31" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457883</v>
+        <v>458116</v>
       </c>
       <c r="R31" t="n">
-        <v>6748264</v>
+        <v>6748548</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3905,50 +3905,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129542949</v>
+        <v>129543059</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457627</v>
+        <v>458174</v>
       </c>
       <c r="R32" t="n">
-        <v>6748161</v>
+        <v>6748599</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3980,7 +3975,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3985,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129542993</v>
+        <v>129543021</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457763</v>
+        <v>457756</v>
       </c>
       <c r="R33" t="n">
-        <v>6748294</v>
+        <v>6748192</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4087,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4124,32 +4119,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129542942</v>
+        <v>129543090</v>
       </c>
       <c r="B34" t="n">
-        <v>97627</v>
+        <v>78741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4159,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457951</v>
+        <v>457883</v>
       </c>
       <c r="R34" t="n">
-        <v>6748543</v>
+        <v>6748264</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4194,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4234,7 +4229,7 @@
         <v>129543018</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,7 +4336,7 @@
         <v>129542966</v>
       </c>
       <c r="B36" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4445,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129543063</v>
+        <v>129542993</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4480,10 +4475,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458116</v>
+        <v>457763</v>
       </c>
       <c r="R37" t="n">
-        <v>6748548</v>
+        <v>6748294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4515,7 +4510,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4525,7 +4520,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4552,32 +4547,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543059</v>
+        <v>129542942</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>97639</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4587,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>458174</v>
+        <v>457951</v>
       </c>
       <c r="R38" t="n">
-        <v>6748599</v>
+        <v>6748543</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4622,7 +4617,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4632,7 +4627,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4659,45 +4654,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543021</v>
+        <v>129542949</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457756</v>
+        <v>457627</v>
       </c>
       <c r="R39" t="n">
-        <v>6748192</v>
+        <v>6748161</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129542946</v>
+        <v>129543112</v>
       </c>
       <c r="B40" t="n">
-        <v>91634</v>
+        <v>91644</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2079</v>
+        <v>5321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458035</v>
+        <v>458029</v>
       </c>
       <c r="R40" t="n">
-        <v>6748395</v>
+        <v>6748411</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4855,6 +4855,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4873,10 +4874,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543098</v>
+        <v>129542927</v>
       </c>
       <c r="B41" t="n">
-        <v>78736</v>
+        <v>57895</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,34 +4885,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457657</v>
+        <v>458027</v>
       </c>
       <c r="R41" t="n">
-        <v>6748066</v>
+        <v>6748413</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,7 +4949,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4953,7 +4959,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4980,10 +4986,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543093</v>
+        <v>129542946</v>
       </c>
       <c r="B42" t="n">
-        <v>78736</v>
+        <v>91640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,21 +4997,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5021,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457737</v>
+        <v>458035</v>
       </c>
       <c r="R42" t="n">
-        <v>6748103</v>
+        <v>6748395</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5050,7 +5056,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5060,7 +5066,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5087,32 +5093,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543112</v>
+        <v>129543098</v>
       </c>
       <c r="B43" t="n">
-        <v>91638</v>
+        <v>78741</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5321</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5122,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>458029</v>
+        <v>457657</v>
       </c>
       <c r="R43" t="n">
-        <v>6748411</v>
+        <v>6748066</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5157,7 +5163,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5167,7 +5173,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5176,7 +5182,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5195,10 +5200,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543071</v>
+        <v>129543093</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,21 +5211,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5230,10 +5235,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457928</v>
+        <v>457737</v>
       </c>
       <c r="R44" t="n">
-        <v>6748344</v>
+        <v>6748103</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5265,7 +5270,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5275,7 +5280,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543003</v>
+        <v>129543071</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5337,10 +5342,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457814</v>
+        <v>457928</v>
       </c>
       <c r="R45" t="n">
-        <v>6748175</v>
+        <v>6748344</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5372,7 +5377,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5382,7 +5387,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5409,10 +5414,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543057</v>
+        <v>129542998</v>
       </c>
       <c r="B46" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5444,10 +5449,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458134</v>
+        <v>457876</v>
       </c>
       <c r="R46" t="n">
-        <v>6748614</v>
+        <v>6748240</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5479,7 +5484,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5489,7 +5494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5516,10 +5521,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129542998</v>
+        <v>129543057</v>
       </c>
       <c r="B47" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,10 +5556,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457876</v>
+        <v>458134</v>
       </c>
       <c r="R47" t="n">
-        <v>6748240</v>
+        <v>6748614</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5586,7 +5591,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5596,7 +5601,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5623,10 +5628,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129542927</v>
+        <v>129543003</v>
       </c>
       <c r="B48" t="n">
-        <v>57890</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5634,39 +5639,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>458027</v>
+        <v>457814</v>
       </c>
       <c r="R48" t="n">
-        <v>6748413</v>
+        <v>6748175</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5738,7 +5738,7 @@
         <v>129543082</v>
       </c>
       <c r="B49" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543078</v>
+        <v>129543010</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457875</v>
+        <v>457656</v>
       </c>
       <c r="R50" t="n">
-        <v>6748394</v>
+        <v>6748084</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543010</v>
+        <v>129543078</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457656</v>
+        <v>457875</v>
       </c>
       <c r="R51" t="n">
-        <v>6748084</v>
+        <v>6748394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6059,7 +6059,7 @@
         <v>129543009</v>
       </c>
       <c r="B52" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>129543034</v>
       </c>
       <c r="B53" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543035</v>
+        <v>129543072</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457845</v>
+        <v>457899</v>
       </c>
       <c r="R54" t="n">
-        <v>6748327</v>
+        <v>6748357</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6377,10 +6377,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129542914</v>
+        <v>129543035</v>
       </c>
       <c r="B55" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6388,21 +6388,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457650</v>
+        <v>457845</v>
       </c>
       <c r="R55" t="n">
-        <v>6748064</v>
+        <v>6748327</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6484,45 +6484,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543066</v>
+        <v>129542950</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458042</v>
+        <v>457695</v>
       </c>
       <c r="R56" t="n">
-        <v>6748499</v>
+        <v>6748215</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6554,7 +6559,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6564,7 +6569,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,45 +6596,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543001</v>
+        <v>129542948</v>
       </c>
       <c r="B57" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457838</v>
+        <v>457777</v>
       </c>
       <c r="R57" t="n">
-        <v>6748208</v>
+        <v>6748294</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6671,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6671,7 +6681,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6698,10 +6708,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543064</v>
+        <v>129543001</v>
       </c>
       <c r="B58" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6733,10 +6743,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458049</v>
+        <v>457838</v>
       </c>
       <c r="R58" t="n">
-        <v>6748509</v>
+        <v>6748208</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6768,7 +6778,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6778,7 +6788,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6805,10 +6815,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543042</v>
+        <v>129543064</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6840,10 +6850,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457922</v>
+        <v>458049</v>
       </c>
       <c r="R59" t="n">
-        <v>6748447</v>
+        <v>6748509</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6875,7 +6885,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6885,7 +6895,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,10 +6922,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543072</v>
+        <v>129543042</v>
       </c>
       <c r="B60" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6947,10 +6957,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457899</v>
+        <v>457922</v>
       </c>
       <c r="R60" t="n">
-        <v>6748357</v>
+        <v>6748447</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6982,7 +6992,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6992,7 +7002,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7019,50 +7029,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129542950</v>
+        <v>129543066</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457695</v>
+        <v>458042</v>
       </c>
       <c r="R61" t="n">
-        <v>6748215</v>
+        <v>6748499</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7094,7 +7099,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7104,7 +7109,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7131,50 +7136,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129542948</v>
+        <v>129542914</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79694</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457777</v>
+        <v>457650</v>
       </c>
       <c r="R62" t="n">
-        <v>6748294</v>
+        <v>6748064</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7243,50 +7243,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129542952</v>
+        <v>129543097</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>78741</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>458156</v>
+        <v>457673</v>
       </c>
       <c r="R63" t="n">
-        <v>6748545</v>
+        <v>6748071</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7318,7 +7313,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7328,7 +7323,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7355,10 +7350,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543097</v>
+        <v>129543073</v>
       </c>
       <c r="B64" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7366,21 +7361,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7390,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457673</v>
+        <v>457917</v>
       </c>
       <c r="R64" t="n">
-        <v>6748071</v>
+        <v>6748303</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7425,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7435,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543073</v>
+        <v>129543019</v>
       </c>
       <c r="B65" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7497,10 +7492,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457917</v>
+        <v>457725</v>
       </c>
       <c r="R65" t="n">
-        <v>6748303</v>
+        <v>6748208</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7532,7 +7527,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7542,7 +7537,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7569,10 +7564,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129542962</v>
+        <v>129543060</v>
       </c>
       <c r="B66" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7580,21 +7575,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7604,10 +7599,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457762</v>
+        <v>458177</v>
       </c>
       <c r="R66" t="n">
-        <v>6748208</v>
+        <v>6748587</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7639,7 +7634,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7649,7 +7644,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7676,10 +7671,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543047</v>
+        <v>129543029</v>
       </c>
       <c r="B67" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7711,10 +7706,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457952</v>
+        <v>457780</v>
       </c>
       <c r="R67" t="n">
-        <v>6748501</v>
+        <v>6748311</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7746,7 +7741,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7756,7 +7751,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7783,10 +7778,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543019</v>
+        <v>129543002</v>
       </c>
       <c r="B68" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7818,10 +7813,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457725</v>
+        <v>457813</v>
       </c>
       <c r="R68" t="n">
-        <v>6748208</v>
+        <v>6748191</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7853,7 +7848,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7863,7 +7858,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7890,10 +7885,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543029</v>
+        <v>129543053</v>
       </c>
       <c r="B69" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7925,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457780</v>
+        <v>458094</v>
       </c>
       <c r="R69" t="n">
-        <v>6748311</v>
+        <v>6748667</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7960,7 +7955,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7970,7 +7965,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,10 +7992,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129542961</v>
+        <v>129542962</v>
       </c>
       <c r="B70" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8032,10 +8027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457859</v>
+        <v>457762</v>
       </c>
       <c r="R70" t="n">
-        <v>6748231</v>
+        <v>6748208</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8067,7 +8062,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8077,7 +8072,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8104,10 +8099,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543002</v>
+        <v>129543047</v>
       </c>
       <c r="B71" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8139,10 +8134,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457813</v>
+        <v>457952</v>
       </c>
       <c r="R71" t="n">
-        <v>6748191</v>
+        <v>6748501</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8174,7 +8169,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8184,7 +8179,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8211,10 +8206,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543053</v>
+        <v>129542961</v>
       </c>
       <c r="B72" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8222,21 +8217,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8246,10 +8241,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458094</v>
+        <v>457859</v>
       </c>
       <c r="R72" t="n">
-        <v>6748667</v>
+        <v>6748231</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8281,7 +8276,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8291,7 +8286,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8318,45 +8313,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543060</v>
+        <v>129542952</v>
       </c>
       <c r="B73" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458177</v>
+        <v>458156</v>
       </c>
       <c r="R73" t="n">
-        <v>6748587</v>
+        <v>6748545</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8425,10 +8425,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543101</v>
+        <v>129542933</v>
       </c>
       <c r="B74" t="n">
-        <v>78736</v>
+        <v>57732</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8436,34 +8436,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457746</v>
+        <v>457753</v>
       </c>
       <c r="R74" t="n">
-        <v>6748232</v>
+        <v>6748178</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8495,7 +8500,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8505,7 +8510,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8532,10 +8537,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543105</v>
+        <v>129543101</v>
       </c>
       <c r="B75" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8567,10 +8572,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457993</v>
+        <v>457746</v>
       </c>
       <c r="R75" t="n">
-        <v>6748571</v>
+        <v>6748232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8602,7 +8607,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8612,7 +8617,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8639,10 +8644,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129542997</v>
+        <v>129543105</v>
       </c>
       <c r="B76" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8650,21 +8655,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8674,10 +8679,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457863</v>
+        <v>457993</v>
       </c>
       <c r="R76" t="n">
-        <v>6748231</v>
+        <v>6748571</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,7 +8714,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8719,7 +8724,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8746,10 +8751,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543000</v>
+        <v>129542997</v>
       </c>
       <c r="B77" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8781,10 +8786,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457846</v>
+        <v>457863</v>
       </c>
       <c r="R77" t="n">
-        <v>6748214</v>
+        <v>6748231</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8816,7 +8821,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8826,7 +8831,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8853,10 +8858,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129542999</v>
+        <v>129543000</v>
       </c>
       <c r="B78" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8888,10 +8893,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457883</v>
+        <v>457846</v>
       </c>
       <c r="R78" t="n">
-        <v>6748260</v>
+        <v>6748214</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,7 +8928,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8933,7 +8938,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8960,10 +8965,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543075</v>
+        <v>129542999</v>
       </c>
       <c r="B79" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8995,10 +9000,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457896</v>
+        <v>457883</v>
       </c>
       <c r="R79" t="n">
-        <v>6748336</v>
+        <v>6748260</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,7 +9035,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9040,7 +9045,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9067,10 +9072,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129542933</v>
+        <v>129543075</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9078,39 +9083,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457753</v>
+        <v>457896</v>
       </c>
       <c r="R80" t="n">
-        <v>6748178</v>
+        <v>6748336</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9182,7 +9182,7 @@
         <v>129543103</v>
       </c>
       <c r="B81" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>129543088</v>
       </c>
       <c r="B82" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9393,10 +9393,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129542964</v>
+        <v>129542991</v>
       </c>
       <c r="B83" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9404,21 +9404,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457767</v>
+        <v>457762</v>
       </c>
       <c r="R83" t="n">
-        <v>6748250</v>
+        <v>6748312</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9500,10 +9500,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129542968</v>
+        <v>129543065</v>
       </c>
       <c r="B84" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9511,21 +9511,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>458060</v>
+        <v>458039</v>
       </c>
       <c r="R84" t="n">
-        <v>6748629</v>
+        <v>6748504</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9607,10 +9607,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543065</v>
+        <v>129542964</v>
       </c>
       <c r="B85" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9618,21 +9618,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458039</v>
+        <v>457767</v>
       </c>
       <c r="R85" t="n">
-        <v>6748504</v>
+        <v>6748250</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9714,10 +9714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129542991</v>
+        <v>129542968</v>
       </c>
       <c r="B86" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9725,21 +9725,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457762</v>
+        <v>458060</v>
       </c>
       <c r="R86" t="n">
-        <v>6748312</v>
+        <v>6748629</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9821,54 +9821,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129542969</v>
+        <v>129543085</v>
       </c>
       <c r="B87" t="n">
-        <v>98756</v>
+        <v>78741</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457879</v>
+        <v>457880</v>
       </c>
       <c r="R87" t="n">
-        <v>6748454</v>
+        <v>6748247</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9900,7 +9891,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9910,7 +9901,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På högstubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9937,32 +9933,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129542939</v>
+        <v>129543076</v>
       </c>
       <c r="B88" t="n">
-        <v>97627</v>
+        <v>79075</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9972,10 +9968,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457660</v>
+        <v>457917</v>
       </c>
       <c r="R88" t="n">
-        <v>6748092</v>
+        <v>6748390</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10007,7 +10003,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10017,7 +10013,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10044,10 +10040,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543085</v>
+        <v>129543049</v>
       </c>
       <c r="B89" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10055,21 +10051,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10079,10 +10075,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457880</v>
+        <v>458018</v>
       </c>
       <c r="R89" t="n">
-        <v>6748247</v>
+        <v>6748602</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10114,7 +10110,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10124,12 +10120,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På högstubbe med fem brandljud</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10156,10 +10147,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543076</v>
+        <v>129543028</v>
       </c>
       <c r="B90" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10191,10 +10182,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457917</v>
+        <v>457753</v>
       </c>
       <c r="R90" t="n">
-        <v>6748390</v>
+        <v>6748290</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10226,7 +10217,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10236,7 +10227,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10263,32 +10254,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129543049</v>
+        <v>129542939</v>
       </c>
       <c r="B91" t="n">
-        <v>79070</v>
+        <v>97639</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10298,10 +10289,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458018</v>
+        <v>457660</v>
       </c>
       <c r="R91" t="n">
-        <v>6748602</v>
+        <v>6748092</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10333,7 +10324,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10343,7 +10334,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10370,45 +10361,54 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543028</v>
+        <v>129542969</v>
       </c>
       <c r="B92" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457753</v>
+        <v>457879</v>
       </c>
       <c r="R92" t="n">
-        <v>6748290</v>
+        <v>6748454</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10477,32 +10477,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129542960</v>
+        <v>129542956</v>
       </c>
       <c r="B93" t="n">
-        <v>80135</v>
+        <v>81060</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229497</v>
+        <v>1049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>458029</v>
+        <v>457662</v>
       </c>
       <c r="R93" t="n">
-        <v>6748413</v>
+        <v>6748216</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,12 +10557,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Rikligt på jätteasp</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10589,10 +10584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543014</v>
+        <v>129543099</v>
       </c>
       <c r="B94" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10600,21 +10595,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10624,10 +10619,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457634</v>
+        <v>457650</v>
       </c>
       <c r="R94" t="n">
-        <v>6748179</v>
+        <v>6748064</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10659,7 +10654,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10669,7 +10664,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10696,10 +10691,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543099</v>
+        <v>129543104</v>
       </c>
       <c r="B95" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10731,10 +10726,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457650</v>
+        <v>457992</v>
       </c>
       <c r="R95" t="n">
-        <v>6748064</v>
+        <v>6748556</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10766,7 +10761,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10776,7 +10771,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10803,10 +10798,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543104</v>
+        <v>129543083</v>
       </c>
       <c r="B96" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10838,10 +10833,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457992</v>
+        <v>457757</v>
       </c>
       <c r="R96" t="n">
-        <v>6748556</v>
+        <v>6748191</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10873,7 +10868,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10883,7 +10878,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10910,10 +10905,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543083</v>
+        <v>129543014</v>
       </c>
       <c r="B97" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10921,21 +10916,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10945,10 +10940,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457757</v>
+        <v>457634</v>
       </c>
       <c r="R97" t="n">
-        <v>6748191</v>
+        <v>6748179</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10980,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10990,7 +10985,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11017,10 +11012,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129542956</v>
+        <v>129543039</v>
       </c>
       <c r="B98" t="n">
-        <v>81055</v>
+        <v>79075</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11028,21 +11023,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11052,10 +11047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457662</v>
+        <v>457830</v>
       </c>
       <c r="R98" t="n">
-        <v>6748216</v>
+        <v>6748402</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11087,7 +11082,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11097,7 +11092,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11124,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543013</v>
+        <v>129543030</v>
       </c>
       <c r="B99" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11159,10 +11154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457621</v>
+        <v>457811</v>
       </c>
       <c r="R99" t="n">
-        <v>6748147</v>
+        <v>6748293</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11194,7 +11189,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11204,7 +11199,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11231,10 +11226,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543037</v>
+        <v>129543016</v>
       </c>
       <c r="B100" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11266,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457830</v>
+        <v>457699</v>
       </c>
       <c r="R100" t="n">
-        <v>6748350</v>
+        <v>6748197</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11301,7 +11296,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11311,7 +11306,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11338,10 +11333,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543039</v>
+        <v>129543013</v>
       </c>
       <c r="B101" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11373,10 +11368,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457830</v>
+        <v>457621</v>
       </c>
       <c r="R101" t="n">
-        <v>6748402</v>
+        <v>6748147</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11408,7 +11403,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11418,7 +11413,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11445,10 +11440,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543030</v>
+        <v>129543037</v>
       </c>
       <c r="B102" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11480,10 +11475,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457811</v>
+        <v>457830</v>
       </c>
       <c r="R102" t="n">
-        <v>6748293</v>
+        <v>6748350</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11515,7 +11510,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11525,7 +11520,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11555,7 +11550,7 @@
         <v>129543020</v>
       </c>
       <c r="B103" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11659,10 +11654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543016</v>
+        <v>129543062</v>
       </c>
       <c r="B104" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11694,10 +11689,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457699</v>
+        <v>458140</v>
       </c>
       <c r="R104" t="n">
-        <v>6748197</v>
+        <v>6748536</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11729,7 +11724,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11739,7 +11734,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11766,32 +11761,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543062</v>
+        <v>129542960</v>
       </c>
       <c r="B105" t="n">
-        <v>79070</v>
+        <v>80140</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11801,10 +11796,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458140</v>
+        <v>458029</v>
       </c>
       <c r="R105" t="n">
-        <v>6748536</v>
+        <v>6748413</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11836,7 +11831,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11846,7 +11841,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Rikligt på jätteasp</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,50 +11873,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543111</v>
+        <v>129542981</v>
       </c>
       <c r="B106" t="n">
-        <v>5177</v>
+        <v>91760</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100526</v>
+        <v>1503</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457665</v>
+        <v>457964</v>
       </c>
       <c r="R106" t="n">
-        <v>6748081</v>
+        <v>6748415</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11948,7 +11943,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11958,7 +11953,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11985,10 +11980,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543012</v>
+        <v>129543094</v>
       </c>
       <c r="B107" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11996,21 +11991,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12020,10 +12015,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457625</v>
+        <v>457728</v>
       </c>
       <c r="R107" t="n">
-        <v>6748127</v>
+        <v>6748093</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12055,7 +12050,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12065,7 +12060,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12092,32 +12087,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129542981</v>
+        <v>129543095</v>
       </c>
       <c r="B108" t="n">
-        <v>91754</v>
+        <v>78741</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12127,10 +12122,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457964</v>
+        <v>457704</v>
       </c>
       <c r="R108" t="n">
-        <v>6748415</v>
+        <v>6748074</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12162,7 +12157,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12172,7 +12167,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12199,10 +12194,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543094</v>
+        <v>129543096</v>
       </c>
       <c r="B109" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12234,10 +12229,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457728</v>
+        <v>457671</v>
       </c>
       <c r="R109" t="n">
-        <v>6748093</v>
+        <v>6748048</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12269,7 +12264,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12279,7 +12274,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12306,10 +12301,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543095</v>
+        <v>129543012</v>
       </c>
       <c r="B110" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12317,21 +12312,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12341,10 +12336,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457704</v>
+        <v>457625</v>
       </c>
       <c r="R110" t="n">
-        <v>6748074</v>
+        <v>6748127</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12371,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12381,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12413,45 +12408,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543096</v>
+        <v>129543111</v>
       </c>
       <c r="B111" t="n">
-        <v>78736</v>
+        <v>5177</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457671</v>
+        <v>457665</v>
       </c>
       <c r="R111" t="n">
-        <v>6748048</v>
+        <v>6748081</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12523,7 +12523,7 @@
         <v>129543011</v>
       </c>
       <c r="B112" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12627,10 +12627,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129542923</v>
+        <v>129543008</v>
       </c>
       <c r="B113" t="n">
-        <v>79165</v>
+        <v>79075</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12638,21 +12638,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12662,10 +12662,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457773</v>
+        <v>457671</v>
       </c>
       <c r="R113" t="n">
-        <v>6748248</v>
+        <v>6748048</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12734,10 +12734,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129542955</v>
+        <v>129542935</v>
       </c>
       <c r="B114" t="n">
-        <v>92223</v>
+        <v>57732</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12745,34 +12745,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458015</v>
+        <v>458060</v>
       </c>
       <c r="R114" t="n">
-        <v>6748399</v>
+        <v>6748631</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12804,7 +12809,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12814,7 +12819,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12841,32 +12846,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129543008</v>
+        <v>129542944</v>
       </c>
       <c r="B115" t="n">
-        <v>79070</v>
+        <v>97645</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12876,10 +12881,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457671</v>
+        <v>457654</v>
       </c>
       <c r="R115" t="n">
-        <v>6748048</v>
+        <v>6748070</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12911,7 +12916,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12921,7 +12926,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12948,10 +12953,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129542935</v>
+        <v>129542923</v>
       </c>
       <c r="B116" t="n">
-        <v>57727</v>
+        <v>79170</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12959,39 +12964,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>458060</v>
+        <v>457773</v>
       </c>
       <c r="R116" t="n">
-        <v>6748631</v>
+        <v>6748248</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13060,32 +13060,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129542944</v>
+        <v>129542955</v>
       </c>
       <c r="B117" t="n">
-        <v>97633</v>
+        <v>92229</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221941</v>
+        <v>5454</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457654</v>
+        <v>458015</v>
       </c>
       <c r="R117" t="n">
-        <v>6748070</v>
+        <v>6748399</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13167,50 +13167,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129542947</v>
+        <v>129543054</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>457929</v>
+        <v>458097</v>
       </c>
       <c r="R118" t="n">
-        <v>6748484</v>
+        <v>6748662</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13242,7 +13237,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13252,7 +13247,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13282,7 +13277,7 @@
         <v>129543061</v>
       </c>
       <c r="B119" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13386,45 +13381,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129543054</v>
+        <v>129542947</v>
       </c>
       <c r="B120" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>458097</v>
+        <v>457929</v>
       </c>
       <c r="R120" t="n">
-        <v>6748662</v>
+        <v>6748484</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13493,10 +13493,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129543102</v>
+        <v>129543048</v>
       </c>
       <c r="B121" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13504,21 +13504,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>457761</v>
+        <v>457954</v>
       </c>
       <c r="R121" t="n">
-        <v>6748256</v>
+        <v>6748541</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13600,10 +13600,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129542967</v>
+        <v>129543025</v>
       </c>
       <c r="B122" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>457939</v>
+        <v>457761</v>
       </c>
       <c r="R122" t="n">
-        <v>6748494</v>
+        <v>6748254</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13707,10 +13707,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129543048</v>
+        <v>129542978</v>
       </c>
       <c r="B123" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>457954</v>
+        <v>457802</v>
       </c>
       <c r="R123" t="n">
-        <v>6748541</v>
+        <v>6748301</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13814,10 +13814,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129543004</v>
+        <v>129543027</v>
       </c>
       <c r="B124" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>457802</v>
+        <v>457756</v>
       </c>
       <c r="R124" t="n">
-        <v>6748157</v>
+        <v>6748271</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13921,10 +13921,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129543025</v>
+        <v>129543046</v>
       </c>
       <c r="B125" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13956,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>457761</v>
+        <v>457946</v>
       </c>
       <c r="R125" t="n">
-        <v>6748254</v>
+        <v>6748493</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14028,10 +14028,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129542978</v>
+        <v>129542967</v>
       </c>
       <c r="B126" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14039,21 +14039,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457802</v>
+        <v>457939</v>
       </c>
       <c r="R126" t="n">
-        <v>6748301</v>
+        <v>6748494</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14135,10 +14135,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129543027</v>
+        <v>129543004</v>
       </c>
       <c r="B127" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>457756</v>
+        <v>457802</v>
       </c>
       <c r="R127" t="n">
-        <v>6748271</v>
+        <v>6748157</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14245,7 +14245,7 @@
         <v>129543015</v>
       </c>
       <c r="B128" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>129542936</v>
       </c>
       <c r="B129" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14461,32 +14461,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129543046</v>
+        <v>129542940</v>
       </c>
       <c r="B130" t="n">
-        <v>79070</v>
+        <v>97639</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14496,10 +14496,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>457946</v>
+        <v>457879</v>
       </c>
       <c r="R130" t="n">
-        <v>6748493</v>
+        <v>6748455</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14568,32 +14568,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129542940</v>
+        <v>129543102</v>
       </c>
       <c r="B131" t="n">
-        <v>97627</v>
+        <v>78741</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14603,10 +14603,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>457879</v>
+        <v>457761</v>
       </c>
       <c r="R131" t="n">
-        <v>6748455</v>
+        <v>6748256</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14678,7 +14678,7 @@
         <v>129542920</v>
       </c>
       <c r="B132" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>129543077</v>
       </c>
       <c r="B133" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>129543040</v>
       </c>
       <c r="B134" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14996,10 +14996,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129543044</v>
+        <v>129543050</v>
       </c>
       <c r="B135" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457939</v>
+        <v>458067</v>
       </c>
       <c r="R135" t="n">
-        <v>6748453</v>
+        <v>6748648</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15103,10 +15103,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129542916</v>
+        <v>129543044</v>
       </c>
       <c r="B136" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15114,21 +15114,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>457750</v>
+        <v>457939</v>
       </c>
       <c r="R136" t="n">
-        <v>6748276</v>
+        <v>6748453</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15210,10 +15210,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129543050</v>
+        <v>129542916</v>
       </c>
       <c r="B137" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15221,21 +15221,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>458067</v>
+        <v>457750</v>
       </c>
       <c r="R137" t="n">
-        <v>6748648</v>
+        <v>6748276</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15320,7 +15320,7 @@
         <v>129543036</v>
       </c>
       <c r="B138" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>129543058</v>
       </c>
       <c r="B139" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>129542958</v>
       </c>
       <c r="B140" t="n">
-        <v>81055</v>
+        <v>81060</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15638,10 +15638,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129542963</v>
+        <v>129543089</v>
       </c>
       <c r="B141" t="n">
-        <v>78827</v>
+        <v>78741</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457754</v>
+        <v>457809</v>
       </c>
       <c r="R141" t="n">
-        <v>6748230</v>
+        <v>6748254</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15745,10 +15745,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129543074</v>
+        <v>129542963</v>
       </c>
       <c r="B142" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15756,21 +15756,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457905</v>
+        <v>457754</v>
       </c>
       <c r="R142" t="n">
-        <v>6748321</v>
+        <v>6748230</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15852,10 +15852,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129542965</v>
+        <v>129543074</v>
       </c>
       <c r="B143" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15863,21 +15863,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457760</v>
+        <v>457905</v>
       </c>
       <c r="R143" t="n">
-        <v>6748255</v>
+        <v>6748321</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129543022</v>
+        <v>129542965</v>
       </c>
       <c r="B144" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15970,21 +15970,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457761</v>
+        <v>457760</v>
       </c>
       <c r="R144" t="n">
-        <v>6748192</v>
+        <v>6748255</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16066,10 +16066,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129543052</v>
+        <v>129543022</v>
       </c>
       <c r="B145" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>458081</v>
+        <v>457761</v>
       </c>
       <c r="R145" t="n">
-        <v>6748667</v>
+        <v>6748192</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16173,10 +16173,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129543089</v>
+        <v>129543052</v>
       </c>
       <c r="B146" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16184,21 +16184,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>457809</v>
+        <v>458081</v>
       </c>
       <c r="R146" t="n">
-        <v>6748254</v>
+        <v>6748667</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16280,10 +16280,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129543069</v>
+        <v>129542994</v>
       </c>
       <c r="B147" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457930</v>
+        <v>457786</v>
       </c>
       <c r="R147" t="n">
-        <v>6748385</v>
+        <v>6748280</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,10 +16387,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129542994</v>
+        <v>129543006</v>
       </c>
       <c r="B148" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457786</v>
+        <v>457712</v>
       </c>
       <c r="R148" t="n">
-        <v>6748280</v>
+        <v>6748081</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16494,10 +16494,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129543023</v>
+        <v>129543069</v>
       </c>
       <c r="B149" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457758</v>
+        <v>457930</v>
       </c>
       <c r="R149" t="n">
-        <v>6748213</v>
+        <v>6748385</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16601,32 +16601,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129542941</v>
+        <v>129543023</v>
       </c>
       <c r="B150" t="n">
-        <v>97627</v>
+        <v>79075</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457929</v>
+        <v>457758</v>
       </c>
       <c r="R150" t="n">
-        <v>6748448</v>
+        <v>6748213</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16708,32 +16708,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129543100</v>
+        <v>129542941</v>
       </c>
       <c r="B151" t="n">
-        <v>78736</v>
+        <v>97639</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16743,10 +16743,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457631</v>
+        <v>457929</v>
       </c>
       <c r="R151" t="n">
-        <v>6748174</v>
+        <v>6748448</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16815,10 +16815,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129543006</v>
+        <v>129543100</v>
       </c>
       <c r="B152" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16826,21 +16826,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457712</v>
+        <v>457631</v>
       </c>
       <c r="R152" t="n">
-        <v>6748081</v>
+        <v>6748174</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16922,10 +16922,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129543068</v>
+        <v>129543067</v>
       </c>
       <c r="B153" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>457935</v>
+        <v>457946</v>
       </c>
       <c r="R153" t="n">
-        <v>6748390</v>
+        <v>6748380</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17029,10 +17029,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129543067</v>
+        <v>129543068</v>
       </c>
       <c r="B154" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457946</v>
+        <v>457935</v>
       </c>
       <c r="R154" t="n">
-        <v>6748380</v>
+        <v>6748390</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17139,7 +17139,7 @@
         <v>129543033</v>
       </c>
       <c r="B155" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17243,32 +17243,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542959</v>
+        <v>129542980</v>
       </c>
       <c r="B156" t="n">
-        <v>81055</v>
+        <v>91760</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>457884</v>
+        <v>458058</v>
       </c>
       <c r="R156" t="n">
-        <v>6748404</v>
+        <v>6748621</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17350,32 +17350,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129542980</v>
+        <v>129542959</v>
       </c>
       <c r="B157" t="n">
-        <v>91754</v>
+        <v>81060</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>458058</v>
+        <v>457884</v>
       </c>
       <c r="R157" t="n">
-        <v>6748621</v>
+        <v>6748404</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17460,7 +17460,7 @@
         <v>129542945</v>
       </c>
       <c r="B158" t="n">
-        <v>97633</v>
+        <v>97645</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>129542943</v>
       </c>
       <c r="B159" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129543056</v>
+        <v>129542925</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458120</v>
+        <v>457896</v>
       </c>
       <c r="R2" t="n">
-        <v>6748624</v>
+        <v>6748335</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129542925</v>
+        <v>129543108</v>
       </c>
       <c r="B3" t="n">
-        <v>56925</v>
+        <v>78742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457896</v>
+        <v>458131</v>
       </c>
       <c r="R3" t="n">
-        <v>6748335</v>
+        <v>6748548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543108</v>
+        <v>129543007</v>
       </c>
       <c r="B4" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458131</v>
+        <v>457677</v>
       </c>
       <c r="R4" t="n">
-        <v>6748548</v>
+        <v>6748051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543007</v>
+        <v>129543031</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457677</v>
+        <v>457809</v>
       </c>
       <c r="R5" t="n">
-        <v>6748051</v>
+        <v>6748286</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543031</v>
+        <v>129543024</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457809</v>
+        <v>457755</v>
       </c>
       <c r="R6" t="n">
-        <v>6748286</v>
+        <v>6748219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543024</v>
+        <v>129543041</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457755</v>
+        <v>457854</v>
       </c>
       <c r="R7" t="n">
-        <v>6748219</v>
+        <v>6748444</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543041</v>
+        <v>129543026</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457854</v>
+        <v>457758</v>
       </c>
       <c r="R8" t="n">
-        <v>6748444</v>
+        <v>6748263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543026</v>
+        <v>129543056</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457758</v>
+        <v>458120</v>
       </c>
       <c r="R9" t="n">
-        <v>6748263</v>
+        <v>6748624</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,32 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129542924</v>
+        <v>129543081</v>
       </c>
       <c r="B11" t="n">
-        <v>91587</v>
+        <v>91861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457899</v>
+        <v>458131</v>
       </c>
       <c r="R11" t="n">
-        <v>6748444</v>
+        <v>6748547</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543081</v>
+        <v>129543091</v>
       </c>
       <c r="B12" t="n">
-        <v>91860</v>
+        <v>78742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458131</v>
+        <v>457817</v>
       </c>
       <c r="R12" t="n">
-        <v>6748547</v>
+        <v>6748202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543091</v>
+        <v>129543092</v>
       </c>
       <c r="B13" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457817</v>
+        <v>457785</v>
       </c>
       <c r="R13" t="n">
-        <v>6748202</v>
+        <v>6748160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543092</v>
+        <v>129543043</v>
       </c>
       <c r="B14" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457785</v>
+        <v>457927</v>
       </c>
       <c r="R14" t="n">
-        <v>6748160</v>
+        <v>6748447</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129543043</v>
+        <v>129542992</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457927</v>
+        <v>457763</v>
       </c>
       <c r="R15" t="n">
-        <v>6748447</v>
+        <v>6748301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129542992</v>
+        <v>129543017</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457763</v>
+        <v>457657</v>
       </c>
       <c r="R16" t="n">
-        <v>6748301</v>
+        <v>6748226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543017</v>
+        <v>129543070</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457657</v>
+        <v>457936</v>
       </c>
       <c r="R17" t="n">
-        <v>6748226</v>
+        <v>6748379</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543070</v>
+        <v>129542915</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457936</v>
+        <v>457754</v>
       </c>
       <c r="R18" t="n">
-        <v>6748379</v>
+        <v>6748230</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129542995</v>
+        <v>129542924</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457809</v>
+        <v>457899</v>
       </c>
       <c r="R19" t="n">
-        <v>6748246</v>
+        <v>6748444</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129542915</v>
+        <v>129542928</v>
       </c>
       <c r="B20" t="n">
-        <v>79694</v>
+        <v>57896</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,34 +2622,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457754</v>
+        <v>457940</v>
       </c>
       <c r="R20" t="n">
-        <v>6748230</v>
+        <v>6748387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129542928</v>
+        <v>129542995</v>
       </c>
       <c r="B21" t="n">
-        <v>57895</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,39 +2734,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457940</v>
+        <v>457809</v>
       </c>
       <c r="R21" t="n">
-        <v>6748387</v>
+        <v>6748246</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,7 +2833,7 @@
         <v>129543107</v>
       </c>
       <c r="B22" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129542913</v>
+        <v>129542996</v>
       </c>
       <c r="B23" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457761</v>
+        <v>457833</v>
       </c>
       <c r="R23" t="n">
-        <v>6748133</v>
+        <v>6748233</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,7 +3047,7 @@
         <v>129543038</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543045</v>
+        <v>129543005</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457912</v>
+        <v>457775</v>
       </c>
       <c r="R25" t="n">
-        <v>6748485</v>
+        <v>6748148</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129542996</v>
+        <v>129543051</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457833</v>
+        <v>458077</v>
       </c>
       <c r="R26" t="n">
-        <v>6748233</v>
+        <v>6748657</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,10 +3365,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543005</v>
+        <v>129543045</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457775</v>
+        <v>457912</v>
       </c>
       <c r="R27" t="n">
-        <v>6748148</v>
+        <v>6748485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,10 +3472,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543051</v>
+        <v>129543032</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458077</v>
+        <v>457821</v>
       </c>
       <c r="R28" t="n">
-        <v>6748657</v>
+        <v>6748297</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,10 +3579,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543032</v>
+        <v>129542982</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457821</v>
+        <v>457941</v>
       </c>
       <c r="R29" t="n">
-        <v>6748297</v>
+        <v>6748477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3659,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,10 +3691,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129542982</v>
+        <v>129542913</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3697,21 +3702,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3721,10 +3726,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457941</v>
+        <v>457761</v>
       </c>
       <c r="R30" t="n">
-        <v>6748477</v>
+        <v>6748133</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3756,7 +3761,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,12 +3771,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3798,32 +3798,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543063</v>
+        <v>129542942</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>97640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458116</v>
+        <v>457951</v>
       </c>
       <c r="R31" t="n">
-        <v>6748548</v>
+        <v>6748543</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3905,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543059</v>
+        <v>129543090</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,21 +3916,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458174</v>
+        <v>457883</v>
       </c>
       <c r="R32" t="n">
-        <v>6748599</v>
+        <v>6748264</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543021</v>
+        <v>129543018</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457756</v>
+        <v>457679</v>
       </c>
       <c r="R33" t="n">
-        <v>6748192</v>
+        <v>6748231</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,10 +4119,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543090</v>
+        <v>129543063</v>
       </c>
       <c r="B34" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,21 +4130,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457883</v>
+        <v>458116</v>
       </c>
       <c r="R34" t="n">
-        <v>6748264</v>
+        <v>6748548</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,10 +4226,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543018</v>
+        <v>129543059</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457679</v>
+        <v>458174</v>
       </c>
       <c r="R35" t="n">
-        <v>6748231</v>
+        <v>6748599</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,10 +4333,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129542966</v>
+        <v>129543021</v>
       </c>
       <c r="B36" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,21 +4344,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457938</v>
+        <v>457756</v>
       </c>
       <c r="R36" t="n">
-        <v>6748466</v>
+        <v>6748192</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,7 +4443,7 @@
         <v>129542993</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4547,32 +4547,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542942</v>
+        <v>129542966</v>
       </c>
       <c r="B38" t="n">
-        <v>97639</v>
+        <v>78833</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457951</v>
+        <v>457938</v>
       </c>
       <c r="R38" t="n">
-        <v>6748543</v>
+        <v>6748466</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543112</v>
+        <v>129543071</v>
       </c>
       <c r="B40" t="n">
-        <v>91644</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458029</v>
+        <v>457928</v>
       </c>
       <c r="R40" t="n">
-        <v>6748411</v>
+        <v>6748344</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4855,7 +4855,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4874,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129542927</v>
+        <v>129542998</v>
       </c>
       <c r="B41" t="n">
-        <v>57895</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4885,39 +4884,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458027</v>
+        <v>457876</v>
       </c>
       <c r="R41" t="n">
-        <v>6748413</v>
+        <v>6748240</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4949,7 +4943,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4959,7 +4953,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4986,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129542946</v>
+        <v>129543003</v>
       </c>
       <c r="B42" t="n">
-        <v>91640</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5021,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458035</v>
+        <v>457814</v>
       </c>
       <c r="R42" t="n">
-        <v>6748395</v>
+        <v>6748175</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5056,7 +5050,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5066,7 +5060,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5093,10 +5087,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543098</v>
+        <v>129543057</v>
       </c>
       <c r="B43" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,21 +5098,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5128,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457657</v>
+        <v>458134</v>
       </c>
       <c r="R43" t="n">
-        <v>6748066</v>
+        <v>6748614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,7 +5157,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5173,7 +5167,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5200,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543093</v>
+        <v>129542946</v>
       </c>
       <c r="B44" t="n">
-        <v>78741</v>
+        <v>91641</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5211,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5235,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457737</v>
+        <v>458035</v>
       </c>
       <c r="R44" t="n">
-        <v>6748103</v>
+        <v>6748395</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5270,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5280,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5307,32 +5301,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543071</v>
+        <v>129543112</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>91645</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5342,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457928</v>
+        <v>458029</v>
       </c>
       <c r="R45" t="n">
-        <v>6748344</v>
+        <v>6748411</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5377,7 +5371,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5387,7 +5381,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5396,6 +5390,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5409,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129542998</v>
+        <v>129542927</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>57896</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5425,34 +5420,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457876</v>
+        <v>458027</v>
       </c>
       <c r="R46" t="n">
-        <v>6748240</v>
+        <v>6748413</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5521,10 +5521,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543057</v>
+        <v>129543098</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458134</v>
+        <v>457657</v>
       </c>
       <c r="R47" t="n">
-        <v>6748614</v>
+        <v>6748066</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,10 +5628,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543003</v>
+        <v>129543093</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5639,21 +5639,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457814</v>
+        <v>457737</v>
       </c>
       <c r="R48" t="n">
-        <v>6748175</v>
+        <v>6748103</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5738,7 +5738,7 @@
         <v>129543082</v>
       </c>
       <c r="B49" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543010</v>
+        <v>129543078</v>
       </c>
       <c r="B50" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457656</v>
+        <v>457875</v>
       </c>
       <c r="R50" t="n">
-        <v>6748084</v>
+        <v>6748394</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543078</v>
+        <v>129543010</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457875</v>
+        <v>457656</v>
       </c>
       <c r="R51" t="n">
-        <v>6748394</v>
+        <v>6748084</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6059,7 +6059,7 @@
         <v>129543009</v>
       </c>
       <c r="B52" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>129543034</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543072</v>
+        <v>129543001</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457899</v>
+        <v>457838</v>
       </c>
       <c r="R54" t="n">
-        <v>6748357</v>
+        <v>6748208</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6377,10 +6377,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543035</v>
+        <v>129543064</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457845</v>
+        <v>458049</v>
       </c>
       <c r="R55" t="n">
-        <v>6748327</v>
+        <v>6748509</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6484,50 +6484,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129542950</v>
+        <v>129543072</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457695</v>
+        <v>457899</v>
       </c>
       <c r="R56" t="n">
-        <v>6748215</v>
+        <v>6748357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6559,7 +6554,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6569,7 +6564,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6596,50 +6591,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129542948</v>
+        <v>129543035</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457777</v>
+        <v>457845</v>
       </c>
       <c r="R57" t="n">
-        <v>6748294</v>
+        <v>6748327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6671,7 +6661,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6681,7 +6671,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6708,10 +6698,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543001</v>
+        <v>129543066</v>
       </c>
       <c r="B58" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6743,10 +6733,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457838</v>
+        <v>458042</v>
       </c>
       <c r="R58" t="n">
-        <v>6748208</v>
+        <v>6748499</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6778,7 +6768,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6788,7 +6778,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6815,45 +6805,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543064</v>
+        <v>129542950</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458049</v>
+        <v>457695</v>
       </c>
       <c r="R59" t="n">
-        <v>6748509</v>
+        <v>6748215</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6885,7 +6880,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6895,7 +6890,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6922,45 +6917,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543042</v>
+        <v>129542948</v>
       </c>
       <c r="B60" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457922</v>
+        <v>457777</v>
       </c>
       <c r="R60" t="n">
-        <v>6748447</v>
+        <v>6748294</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543066</v>
+        <v>129543042</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458042</v>
+        <v>457922</v>
       </c>
       <c r="R61" t="n">
-        <v>6748499</v>
+        <v>6748447</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7139,7 +7139,7 @@
         <v>129542914</v>
       </c>
       <c r="B62" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7243,10 +7243,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543097</v>
+        <v>129542962</v>
       </c>
       <c r="B63" t="n">
-        <v>78741</v>
+        <v>78833</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457673</v>
+        <v>457762</v>
       </c>
       <c r="R63" t="n">
-        <v>6748071</v>
+        <v>6748208</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7350,10 +7350,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543073</v>
+        <v>129542961</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7361,21 +7361,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457917</v>
+        <v>457859</v>
       </c>
       <c r="R64" t="n">
-        <v>6748303</v>
+        <v>6748231</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543019</v>
+        <v>129543097</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457725</v>
+        <v>457673</v>
       </c>
       <c r="R65" t="n">
-        <v>6748208</v>
+        <v>6748071</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7564,10 +7564,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543060</v>
+        <v>129543073</v>
       </c>
       <c r="B66" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458177</v>
+        <v>457917</v>
       </c>
       <c r="R66" t="n">
-        <v>6748587</v>
+        <v>6748303</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7671,10 +7671,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543029</v>
+        <v>129543047</v>
       </c>
       <c r="B67" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457780</v>
+        <v>457952</v>
       </c>
       <c r="R67" t="n">
-        <v>6748311</v>
+        <v>6748501</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7778,10 +7778,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543002</v>
+        <v>129543019</v>
       </c>
       <c r="B68" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457813</v>
+        <v>457725</v>
       </c>
       <c r="R68" t="n">
-        <v>6748191</v>
+        <v>6748208</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7885,10 +7885,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543053</v>
+        <v>129543060</v>
       </c>
       <c r="B69" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458094</v>
+        <v>458177</v>
       </c>
       <c r="R69" t="n">
-        <v>6748667</v>
+        <v>6748587</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7992,10 +7992,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129542962</v>
+        <v>129543029</v>
       </c>
       <c r="B70" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8003,21 +8003,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457762</v>
+        <v>457780</v>
       </c>
       <c r="R70" t="n">
-        <v>6748208</v>
+        <v>6748311</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8099,10 +8099,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543047</v>
+        <v>129543002</v>
       </c>
       <c r="B71" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457952</v>
+        <v>457813</v>
       </c>
       <c r="R71" t="n">
-        <v>6748501</v>
+        <v>6748191</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8206,10 +8206,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129542961</v>
+        <v>129543053</v>
       </c>
       <c r="B72" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457859</v>
+        <v>458094</v>
       </c>
       <c r="R72" t="n">
-        <v>6748231</v>
+        <v>6748667</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8425,10 +8425,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129542933</v>
+        <v>129543101</v>
       </c>
       <c r="B74" t="n">
-        <v>57732</v>
+        <v>78742</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8436,39 +8436,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457753</v>
+        <v>457746</v>
       </c>
       <c r="R74" t="n">
-        <v>6748178</v>
+        <v>6748232</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8500,7 +8495,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8510,7 +8505,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8537,10 +8532,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543101</v>
+        <v>129543105</v>
       </c>
       <c r="B75" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8572,10 +8567,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457746</v>
+        <v>457993</v>
       </c>
       <c r="R75" t="n">
-        <v>6748232</v>
+        <v>6748571</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8607,7 +8602,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8617,7 +8612,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8644,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543105</v>
+        <v>129542933</v>
       </c>
       <c r="B76" t="n">
-        <v>78741</v>
+        <v>57733</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8655,34 +8650,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457993</v>
+        <v>457753</v>
       </c>
       <c r="R76" t="n">
-        <v>6748571</v>
+        <v>6748178</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8754,7 +8754,7 @@
         <v>129542997</v>
       </c>
       <c r="B77" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>129543000</v>
       </c>
       <c r="B78" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>129542999</v>
       </c>
       <c r="B79" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>129543075</v>
       </c>
       <c r="B80" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>129543103</v>
       </c>
       <c r="B81" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>129543088</v>
       </c>
       <c r="B82" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>129542991</v>
       </c>
       <c r="B83" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>129543065</v>
       </c>
       <c r="B84" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>129542964</v>
       </c>
       <c r="B85" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>129542968</v>
       </c>
       <c r="B86" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>129543085</v>
       </c>
       <c r="B87" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>129543076</v>
       </c>
       <c r="B88" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>129543049</v>
       </c>
       <c r="B89" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>129543028</v>
       </c>
       <c r="B90" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10254,45 +10254,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129542939</v>
+        <v>129542969</v>
       </c>
       <c r="B91" t="n">
-        <v>97639</v>
+        <v>98769</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457660</v>
+        <v>457879</v>
       </c>
       <c r="R91" t="n">
-        <v>6748092</v>
+        <v>6748454</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10324,7 +10333,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10334,7 +10343,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10361,54 +10370,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129542969</v>
+        <v>129542939</v>
       </c>
       <c r="B92" t="n">
-        <v>98768</v>
+        <v>97640</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457879</v>
+        <v>457660</v>
       </c>
       <c r="R92" t="n">
-        <v>6748454</v>
+        <v>6748092</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10477,10 +10477,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129542956</v>
+        <v>129543013</v>
       </c>
       <c r="B93" t="n">
-        <v>81060</v>
+        <v>79076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10488,21 +10488,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457662</v>
+        <v>457621</v>
       </c>
       <c r="R93" t="n">
-        <v>6748216</v>
+        <v>6748147</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10584,10 +10584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543099</v>
+        <v>129543014</v>
       </c>
       <c r="B94" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10595,21 +10595,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457650</v>
+        <v>457634</v>
       </c>
       <c r="R94" t="n">
-        <v>6748064</v>
+        <v>6748179</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10691,10 +10691,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543104</v>
+        <v>129543037</v>
       </c>
       <c r="B95" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10702,21 +10702,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457992</v>
+        <v>457830</v>
       </c>
       <c r="R95" t="n">
-        <v>6748556</v>
+        <v>6748350</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10798,10 +10798,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543083</v>
+        <v>129543030</v>
       </c>
       <c r="B96" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457757</v>
+        <v>457811</v>
       </c>
       <c r="R96" t="n">
-        <v>6748191</v>
+        <v>6748293</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10905,10 +10905,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543014</v>
+        <v>129543020</v>
       </c>
       <c r="B97" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457634</v>
+        <v>457738</v>
       </c>
       <c r="R97" t="n">
-        <v>6748179</v>
+        <v>6748205</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,10 +11012,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543039</v>
+        <v>129543016</v>
       </c>
       <c r="B98" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457830</v>
+        <v>457699</v>
       </c>
       <c r="R98" t="n">
-        <v>6748402</v>
+        <v>6748197</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543030</v>
+        <v>129543062</v>
       </c>
       <c r="B99" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11154,10 +11154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>457811</v>
+        <v>458140</v>
       </c>
       <c r="R99" t="n">
-        <v>6748293</v>
+        <v>6748536</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,10 +11226,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543016</v>
+        <v>129543039</v>
       </c>
       <c r="B100" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457699</v>
+        <v>457830</v>
       </c>
       <c r="R100" t="n">
-        <v>6748197</v>
+        <v>6748402</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,10 +11333,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543013</v>
+        <v>129543099</v>
       </c>
       <c r="B101" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11344,21 +11344,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11368,10 +11368,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457621</v>
+        <v>457650</v>
       </c>
       <c r="R101" t="n">
-        <v>6748147</v>
+        <v>6748064</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11440,10 +11440,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543037</v>
+        <v>129543104</v>
       </c>
       <c r="B102" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11451,21 +11451,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11475,10 +11475,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457830</v>
+        <v>457992</v>
       </c>
       <c r="R102" t="n">
-        <v>6748350</v>
+        <v>6748556</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11547,10 +11547,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543020</v>
+        <v>129543083</v>
       </c>
       <c r="B103" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11558,21 +11558,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11582,10 +11582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457738</v>
+        <v>457757</v>
       </c>
       <c r="R103" t="n">
-        <v>6748205</v>
+        <v>6748191</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11654,10 +11654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543062</v>
+        <v>129542956</v>
       </c>
       <c r="B104" t="n">
-        <v>79075</v>
+        <v>81061</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11689,10 +11689,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458140</v>
+        <v>457662</v>
       </c>
       <c r="R104" t="n">
-        <v>6748536</v>
+        <v>6748216</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11764,7 +11764,7 @@
         <v>129542960</v>
       </c>
       <c r="B105" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11873,32 +11873,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129542981</v>
+        <v>129543094</v>
       </c>
       <c r="B106" t="n">
-        <v>91760</v>
+        <v>78742</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457964</v>
+        <v>457728</v>
       </c>
       <c r="R106" t="n">
-        <v>6748415</v>
+        <v>6748093</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11980,10 +11980,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543094</v>
+        <v>129543095</v>
       </c>
       <c r="B107" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457728</v>
+        <v>457704</v>
       </c>
       <c r="R107" t="n">
-        <v>6748093</v>
+        <v>6748074</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12087,10 +12087,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129543095</v>
+        <v>129543096</v>
       </c>
       <c r="B108" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457704</v>
+        <v>457671</v>
       </c>
       <c r="R108" t="n">
-        <v>6748074</v>
+        <v>6748048</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12194,10 +12194,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543096</v>
+        <v>129543012</v>
       </c>
       <c r="B109" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12205,21 +12205,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12229,10 +12229,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457671</v>
+        <v>457625</v>
       </c>
       <c r="R109" t="n">
-        <v>6748048</v>
+        <v>6748127</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12301,32 +12301,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543012</v>
+        <v>129542981</v>
       </c>
       <c r="B110" t="n">
-        <v>79075</v>
+        <v>91761</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12336,10 +12336,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457625</v>
+        <v>457964</v>
       </c>
       <c r="R110" t="n">
-        <v>6748127</v>
+        <v>6748415</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12520,10 +12520,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129543011</v>
+        <v>129542935</v>
       </c>
       <c r="B112" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12531,34 +12531,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>457665</v>
+        <v>458060</v>
       </c>
       <c r="R112" t="n">
-        <v>6748082</v>
+        <v>6748631</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12590,7 +12595,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12600,7 +12605,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12627,32 +12632,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129543008</v>
+        <v>129542944</v>
       </c>
       <c r="B113" t="n">
-        <v>79075</v>
+        <v>97646</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12662,10 +12667,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457671</v>
+        <v>457654</v>
       </c>
       <c r="R113" t="n">
-        <v>6748048</v>
+        <v>6748070</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12697,7 +12702,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12707,7 +12712,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12734,10 +12739,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129542935</v>
+        <v>129542955</v>
       </c>
       <c r="B114" t="n">
-        <v>57732</v>
+        <v>92230</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12745,39 +12750,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>5454</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458060</v>
+        <v>458015</v>
       </c>
       <c r="R114" t="n">
-        <v>6748631</v>
+        <v>6748399</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12846,32 +12846,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129542944</v>
+        <v>129543011</v>
       </c>
       <c r="B115" t="n">
-        <v>97645</v>
+        <v>79076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12881,10 +12881,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457654</v>
+        <v>457665</v>
       </c>
       <c r="R115" t="n">
-        <v>6748070</v>
+        <v>6748082</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12953,10 +12953,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129542923</v>
+        <v>129543008</v>
       </c>
       <c r="B116" t="n">
-        <v>79170</v>
+        <v>79076</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12964,21 +12964,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457773</v>
+        <v>457671</v>
       </c>
       <c r="R116" t="n">
-        <v>6748248</v>
+        <v>6748048</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13060,10 +13060,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129542955</v>
+        <v>129542923</v>
       </c>
       <c r="B117" t="n">
-        <v>92229</v>
+        <v>79171</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13071,21 +13071,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5454</v>
+        <v>967</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>458015</v>
+        <v>457773</v>
       </c>
       <c r="R117" t="n">
-        <v>6748399</v>
+        <v>6748248</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13170,7 +13170,7 @@
         <v>129543054</v>
       </c>
       <c r="B118" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13274,45 +13274,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129543061</v>
+        <v>129542947</v>
       </c>
       <c r="B119" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458155</v>
+        <v>457929</v>
       </c>
       <c r="R119" t="n">
-        <v>6748548</v>
+        <v>6748484</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13344,7 +13349,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13354,7 +13359,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13381,50 +13386,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129542947</v>
+        <v>129543061</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>457929</v>
+        <v>458155</v>
       </c>
       <c r="R120" t="n">
-        <v>6748484</v>
+        <v>6748548</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13493,32 +13493,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129543048</v>
+        <v>129542940</v>
       </c>
       <c r="B121" t="n">
-        <v>79075</v>
+        <v>97640</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>457954</v>
+        <v>457879</v>
       </c>
       <c r="R121" t="n">
-        <v>6748541</v>
+        <v>6748455</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13600,10 +13600,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129543025</v>
+        <v>129543102</v>
       </c>
       <c r="B122" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13638,7 +13638,7 @@
         <v>457761</v>
       </c>
       <c r="R122" t="n">
-        <v>6748254</v>
+        <v>6748256</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13707,10 +13707,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129542978</v>
+        <v>129543046</v>
       </c>
       <c r="B123" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>457802</v>
+        <v>457946</v>
       </c>
       <c r="R123" t="n">
-        <v>6748301</v>
+        <v>6748493</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13814,10 +13814,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129543027</v>
+        <v>129543048</v>
       </c>
       <c r="B124" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>457756</v>
+        <v>457954</v>
       </c>
       <c r="R124" t="n">
-        <v>6748271</v>
+        <v>6748541</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13921,10 +13921,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129543046</v>
+        <v>129543004</v>
       </c>
       <c r="B125" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13956,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>457946</v>
+        <v>457802</v>
       </c>
       <c r="R125" t="n">
-        <v>6748493</v>
+        <v>6748157</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14028,10 +14028,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129542967</v>
+        <v>129543015</v>
       </c>
       <c r="B126" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14039,21 +14039,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457939</v>
+        <v>457689</v>
       </c>
       <c r="R126" t="n">
-        <v>6748494</v>
+        <v>6748165</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14135,10 +14135,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129543004</v>
+        <v>129542978</v>
       </c>
       <c r="B127" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>457802</v>
       </c>
       <c r="R127" t="n">
-        <v>6748157</v>
+        <v>6748301</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14242,10 +14242,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129543015</v>
+        <v>129543027</v>
       </c>
       <c r="B128" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457689</v>
+        <v>457756</v>
       </c>
       <c r="R128" t="n">
-        <v>6748165</v>
+        <v>6748271</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14349,10 +14349,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129542936</v>
+        <v>129542967</v>
       </c>
       <c r="B129" t="n">
-        <v>57732</v>
+        <v>78833</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14360,39 +14360,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>458155</v>
+        <v>457939</v>
       </c>
       <c r="R129" t="n">
-        <v>6748562</v>
+        <v>6748494</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14424,7 +14419,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14434,7 +14429,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14461,32 +14456,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129542940</v>
+        <v>129543025</v>
       </c>
       <c r="B130" t="n">
-        <v>97639</v>
+        <v>79076</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14496,10 +14491,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>457879</v>
+        <v>457761</v>
       </c>
       <c r="R130" t="n">
-        <v>6748455</v>
+        <v>6748254</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14531,7 +14526,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14541,7 +14536,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14568,10 +14563,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129543102</v>
+        <v>129542936</v>
       </c>
       <c r="B131" t="n">
-        <v>78741</v>
+        <v>57733</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14579,34 +14574,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>457761</v>
+        <v>458155</v>
       </c>
       <c r="R131" t="n">
-        <v>6748256</v>
+        <v>6748562</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14675,32 +14675,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129542920</v>
+        <v>129543040</v>
       </c>
       <c r="B132" t="n">
-        <v>91551</v>
+        <v>79076</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457964</v>
+        <v>457817</v>
       </c>
       <c r="R132" t="n">
-        <v>6748415</v>
+        <v>6748400</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14782,10 +14782,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129543077</v>
+        <v>129543044</v>
       </c>
       <c r="B133" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457938</v>
+        <v>457939</v>
       </c>
       <c r="R133" t="n">
-        <v>6748409</v>
+        <v>6748453</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14889,10 +14889,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129543040</v>
+        <v>129543036</v>
       </c>
       <c r="B134" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>457817</v>
+        <v>457843</v>
       </c>
       <c r="R134" t="n">
-        <v>6748400</v>
+        <v>6748341</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14996,32 +14996,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129543050</v>
+        <v>129542920</v>
       </c>
       <c r="B135" t="n">
-        <v>79075</v>
+        <v>91552</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>458067</v>
+        <v>457964</v>
       </c>
       <c r="R135" t="n">
-        <v>6748648</v>
+        <v>6748415</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15103,10 +15103,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129543044</v>
+        <v>129543058</v>
       </c>
       <c r="B136" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>457939</v>
+        <v>458143</v>
       </c>
       <c r="R136" t="n">
-        <v>6748453</v>
+        <v>6748611</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15210,10 +15210,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129542916</v>
+        <v>129543077</v>
       </c>
       <c r="B137" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15221,21 +15221,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>457750</v>
+        <v>457938</v>
       </c>
       <c r="R137" t="n">
-        <v>6748276</v>
+        <v>6748409</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15317,10 +15317,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129543036</v>
+        <v>129542916</v>
       </c>
       <c r="B138" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15328,21 +15328,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>457843</v>
+        <v>457750</v>
       </c>
       <c r="R138" t="n">
-        <v>6748341</v>
+        <v>6748276</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15424,10 +15424,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129543058</v>
+        <v>129543050</v>
       </c>
       <c r="B139" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>458143</v>
+        <v>458067</v>
       </c>
       <c r="R139" t="n">
-        <v>6748611</v>
+        <v>6748648</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15531,10 +15531,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129542958</v>
+        <v>129543089</v>
       </c>
       <c r="B140" t="n">
-        <v>81060</v>
+        <v>78742</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>458029</v>
+        <v>457809</v>
       </c>
       <c r="R140" t="n">
-        <v>6748402</v>
+        <v>6748254</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15638,10 +15638,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129543089</v>
+        <v>129543074</v>
       </c>
       <c r="B141" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457809</v>
+        <v>457905</v>
       </c>
       <c r="R141" t="n">
-        <v>6748254</v>
+        <v>6748321</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15745,10 +15745,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129542963</v>
+        <v>129543022</v>
       </c>
       <c r="B142" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15756,21 +15756,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457754</v>
+        <v>457761</v>
       </c>
       <c r="R142" t="n">
-        <v>6748230</v>
+        <v>6748192</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15852,10 +15852,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129543074</v>
+        <v>129543052</v>
       </c>
       <c r="B143" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457905</v>
+        <v>458081</v>
       </c>
       <c r="R143" t="n">
-        <v>6748321</v>
+        <v>6748667</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129542965</v>
+        <v>129542958</v>
       </c>
       <c r="B144" t="n">
-        <v>78832</v>
+        <v>81061</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15970,21 +15970,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457760</v>
+        <v>458029</v>
       </c>
       <c r="R144" t="n">
-        <v>6748255</v>
+        <v>6748402</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16066,10 +16066,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129543022</v>
+        <v>129542963</v>
       </c>
       <c r="B145" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16077,21 +16077,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>457761</v>
+        <v>457754</v>
       </c>
       <c r="R145" t="n">
-        <v>6748192</v>
+        <v>6748230</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16173,10 +16173,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129543052</v>
+        <v>129542965</v>
       </c>
       <c r="B146" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16184,21 +16184,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>458081</v>
+        <v>457760</v>
       </c>
       <c r="R146" t="n">
-        <v>6748667</v>
+        <v>6748255</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16280,10 +16280,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129542994</v>
+        <v>129543100</v>
       </c>
       <c r="B147" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16291,21 +16291,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457786</v>
+        <v>457631</v>
       </c>
       <c r="R147" t="n">
-        <v>6748280</v>
+        <v>6748174</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,10 +16387,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129543006</v>
+        <v>129543069</v>
       </c>
       <c r="B148" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457712</v>
+        <v>457930</v>
       </c>
       <c r="R148" t="n">
-        <v>6748081</v>
+        <v>6748385</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16494,10 +16494,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129543069</v>
+        <v>129542994</v>
       </c>
       <c r="B149" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457930</v>
+        <v>457786</v>
       </c>
       <c r="R149" t="n">
-        <v>6748385</v>
+        <v>6748280</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16601,10 +16601,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129543023</v>
+        <v>129543006</v>
       </c>
       <c r="B150" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457758</v>
+        <v>457712</v>
       </c>
       <c r="R150" t="n">
-        <v>6748213</v>
+        <v>6748081</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16708,32 +16708,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129542941</v>
+        <v>129543023</v>
       </c>
       <c r="B151" t="n">
-        <v>97639</v>
+        <v>79076</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16743,10 +16743,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457929</v>
+        <v>457758</v>
       </c>
       <c r="R151" t="n">
-        <v>6748448</v>
+        <v>6748213</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16815,32 +16815,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129543100</v>
+        <v>129542941</v>
       </c>
       <c r="B152" t="n">
-        <v>78741</v>
+        <v>97640</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457631</v>
+        <v>457929</v>
       </c>
       <c r="R152" t="n">
-        <v>6748174</v>
+        <v>6748448</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129543067</v>
+        <v>129542980</v>
       </c>
       <c r="B153" t="n">
-        <v>79075</v>
+        <v>91761</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>457946</v>
+        <v>458058</v>
       </c>
       <c r="R153" t="n">
-        <v>6748380</v>
+        <v>6748621</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17029,10 +17029,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129543068</v>
+        <v>129542959</v>
       </c>
       <c r="B154" t="n">
-        <v>79075</v>
+        <v>81061</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17040,21 +17040,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457935</v>
+        <v>457884</v>
       </c>
       <c r="R154" t="n">
-        <v>6748390</v>
+        <v>6748404</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17136,32 +17136,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129543033</v>
+        <v>129542945</v>
       </c>
       <c r="B155" t="n">
-        <v>79075</v>
+        <v>97646</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>457836</v>
+        <v>457654</v>
       </c>
       <c r="R155" t="n">
-        <v>6748291</v>
+        <v>6748079</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542980</v>
+        <v>129542943</v>
       </c>
       <c r="B156" t="n">
-        <v>91760</v>
+        <v>97640</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1503</v>
+        <v>221945</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>458058</v>
+        <v>457999</v>
       </c>
       <c r="R156" t="n">
-        <v>6748621</v>
+        <v>6748381</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17350,10 +17350,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129542959</v>
+        <v>129543068</v>
       </c>
       <c r="B157" t="n">
-        <v>81060</v>
+        <v>79076</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17361,21 +17361,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457884</v>
+        <v>457935</v>
       </c>
       <c r="R157" t="n">
-        <v>6748404</v>
+        <v>6748390</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17457,32 +17457,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129542945</v>
+        <v>129543067</v>
       </c>
       <c r="B158" t="n">
-        <v>97645</v>
+        <v>79076</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457654</v>
+        <v>457946</v>
       </c>
       <c r="R158" t="n">
-        <v>6748079</v>
+        <v>6748380</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17564,32 +17564,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129542943</v>
+        <v>129543033</v>
       </c>
       <c r="B159" t="n">
-        <v>97639</v>
+        <v>79076</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457999</v>
+        <v>457836</v>
       </c>
       <c r="R159" t="n">
-        <v>6748381</v>
+        <v>6748291</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -3798,32 +3798,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129542942</v>
+        <v>129543090</v>
       </c>
       <c r="B31" t="n">
-        <v>97640</v>
+        <v>78742</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457951</v>
+        <v>457883</v>
       </c>
       <c r="R31" t="n">
-        <v>6748543</v>
+        <v>6748264</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3905,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543090</v>
+        <v>129543018</v>
       </c>
       <c r="B32" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,21 +3916,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457883</v>
+        <v>457679</v>
       </c>
       <c r="R32" t="n">
-        <v>6748264</v>
+        <v>6748231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,7 +4012,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543018</v>
+        <v>129543063</v>
       </c>
       <c r="B33" t="n">
         <v>79076</v>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457679</v>
+        <v>458116</v>
       </c>
       <c r="R33" t="n">
-        <v>6748231</v>
+        <v>6748548</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4119,7 +4119,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543063</v>
+        <v>129543059</v>
       </c>
       <c r="B34" t="n">
         <v>79076</v>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458116</v>
+        <v>458174</v>
       </c>
       <c r="R34" t="n">
-        <v>6748548</v>
+        <v>6748599</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,7 +4226,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543059</v>
+        <v>129543021</v>
       </c>
       <c r="B35" t="n">
         <v>79076</v>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458174</v>
+        <v>457756</v>
       </c>
       <c r="R35" t="n">
-        <v>6748599</v>
+        <v>6748192</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543021</v>
+        <v>129542993</v>
       </c>
       <c r="B36" t="n">
         <v>79076</v>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457756</v>
+        <v>457763</v>
       </c>
       <c r="R36" t="n">
-        <v>6748192</v>
+        <v>6748294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,45 +4440,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129542993</v>
+        <v>129542949</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457763</v>
+        <v>457627</v>
       </c>
       <c r="R37" t="n">
-        <v>6748294</v>
+        <v>6748161</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4510,7 +4515,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4520,7 +4525,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4654,10 +4659,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129542949</v>
+        <v>129542942</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>97640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4665,39 +4670,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457627</v>
+        <v>457951</v>
       </c>
       <c r="R39" t="n">
-        <v>6748161</v>
+        <v>6748543</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -7243,10 +7243,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129542962</v>
+        <v>129543097</v>
       </c>
       <c r="B63" t="n">
-        <v>78833</v>
+        <v>78742</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457762</v>
+        <v>457673</v>
       </c>
       <c r="R63" t="n">
-        <v>6748208</v>
+        <v>6748071</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7350,10 +7350,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129542961</v>
+        <v>129543073</v>
       </c>
       <c r="B64" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7361,21 +7361,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457859</v>
+        <v>457917</v>
       </c>
       <c r="R64" t="n">
-        <v>6748231</v>
+        <v>6748303</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543097</v>
+        <v>129543047</v>
       </c>
       <c r="B65" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457673</v>
+        <v>457952</v>
       </c>
       <c r="R65" t="n">
-        <v>6748071</v>
+        <v>6748501</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7564,7 +7564,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543073</v>
+        <v>129543019</v>
       </c>
       <c r="B66" t="n">
         <v>79076</v>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457917</v>
+        <v>457725</v>
       </c>
       <c r="R66" t="n">
-        <v>6748303</v>
+        <v>6748208</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7671,7 +7671,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543047</v>
+        <v>129543060</v>
       </c>
       <c r="B67" t="n">
         <v>79076</v>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457952</v>
+        <v>458177</v>
       </c>
       <c r="R67" t="n">
-        <v>6748501</v>
+        <v>6748587</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7778,7 +7778,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543019</v>
+        <v>129543029</v>
       </c>
       <c r="B68" t="n">
         <v>79076</v>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457725</v>
+        <v>457780</v>
       </c>
       <c r="R68" t="n">
-        <v>6748208</v>
+        <v>6748311</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7885,7 +7885,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543060</v>
+        <v>129543002</v>
       </c>
       <c r="B69" t="n">
         <v>79076</v>
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458177</v>
+        <v>457813</v>
       </c>
       <c r="R69" t="n">
-        <v>6748587</v>
+        <v>6748191</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7992,7 +7992,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543029</v>
+        <v>129543053</v>
       </c>
       <c r="B70" t="n">
         <v>79076</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457780</v>
+        <v>458094</v>
       </c>
       <c r="R70" t="n">
-        <v>6748311</v>
+        <v>6748667</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8099,10 +8099,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543002</v>
+        <v>129542962</v>
       </c>
       <c r="B71" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8110,21 +8110,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457813</v>
+        <v>457762</v>
       </c>
       <c r="R71" t="n">
-        <v>6748191</v>
+        <v>6748208</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8206,10 +8206,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543053</v>
+        <v>129542961</v>
       </c>
       <c r="B72" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458094</v>
+        <v>457859</v>
       </c>
       <c r="R72" t="n">
-        <v>6748667</v>
+        <v>6748231</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129542933</v>
+        <v>129542997</v>
       </c>
       <c r="B76" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8650,39 +8650,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457753</v>
+        <v>457863</v>
       </c>
       <c r="R76" t="n">
-        <v>6748178</v>
+        <v>6748231</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8714,7 +8709,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8724,7 +8719,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8751,7 +8746,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129542997</v>
+        <v>129543000</v>
       </c>
       <c r="B77" t="n">
         <v>79076</v>
@@ -8786,10 +8781,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457863</v>
+        <v>457846</v>
       </c>
       <c r="R77" t="n">
-        <v>6748231</v>
+        <v>6748214</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8821,7 +8816,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8831,7 +8826,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8858,7 +8853,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543000</v>
+        <v>129542999</v>
       </c>
       <c r="B78" t="n">
         <v>79076</v>
@@ -8893,10 +8888,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457846</v>
+        <v>457883</v>
       </c>
       <c r="R78" t="n">
-        <v>6748214</v>
+        <v>6748260</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8928,7 +8923,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8938,7 +8933,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8965,7 +8960,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129542999</v>
+        <v>129543075</v>
       </c>
       <c r="B79" t="n">
         <v>79076</v>
@@ -9000,10 +8995,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457883</v>
+        <v>457896</v>
       </c>
       <c r="R79" t="n">
-        <v>6748260</v>
+        <v>6748336</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9035,7 +9030,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9045,7 +9040,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9072,10 +9067,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543075</v>
+        <v>129542933</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9083,34 +9078,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457896</v>
+        <v>457753</v>
       </c>
       <c r="R80" t="n">
-        <v>6748336</v>
+        <v>6748178</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9179,10 +9179,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543103</v>
+        <v>129542991</v>
       </c>
       <c r="B81" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457842</v>
+        <v>457762</v>
       </c>
       <c r="R81" t="n">
-        <v>6748363</v>
+        <v>6748312</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9286,10 +9286,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543088</v>
+        <v>129543065</v>
       </c>
       <c r="B82" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457797</v>
+        <v>458039</v>
       </c>
       <c r="R82" t="n">
-        <v>6748261</v>
+        <v>6748504</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9393,10 +9393,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129542991</v>
+        <v>129542964</v>
       </c>
       <c r="B83" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9404,21 +9404,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457762</v>
+        <v>457767</v>
       </c>
       <c r="R83" t="n">
-        <v>6748312</v>
+        <v>6748250</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9500,10 +9500,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543065</v>
+        <v>129542968</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9511,21 +9511,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>458039</v>
+        <v>458060</v>
       </c>
       <c r="R84" t="n">
-        <v>6748504</v>
+        <v>6748629</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9607,10 +9607,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129542964</v>
+        <v>129543103</v>
       </c>
       <c r="B85" t="n">
-        <v>78833</v>
+        <v>78742</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9618,21 +9618,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>457767</v>
+        <v>457842</v>
       </c>
       <c r="R85" t="n">
-        <v>6748250</v>
+        <v>6748363</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9714,10 +9714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129542968</v>
+        <v>129543088</v>
       </c>
       <c r="B86" t="n">
-        <v>78833</v>
+        <v>78742</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9725,21 +9725,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458060</v>
+        <v>457797</v>
       </c>
       <c r="R86" t="n">
-        <v>6748629</v>
+        <v>6748261</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9933,45 +9933,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543076</v>
+        <v>129542969</v>
       </c>
       <c r="B88" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457917</v>
+        <v>457879</v>
       </c>
       <c r="R88" t="n">
-        <v>6748390</v>
+        <v>6748454</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10003,7 +10012,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10013,7 +10022,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10040,32 +10049,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543049</v>
+        <v>129542939</v>
       </c>
       <c r="B89" t="n">
-        <v>79076</v>
+        <v>97640</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10075,10 +10084,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458018</v>
+        <v>457660</v>
       </c>
       <c r="R89" t="n">
-        <v>6748602</v>
+        <v>6748092</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10110,7 +10119,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10120,7 +10129,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10147,7 +10156,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543028</v>
+        <v>129543076</v>
       </c>
       <c r="B90" t="n">
         <v>79076</v>
@@ -10182,10 +10191,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457753</v>
+        <v>457917</v>
       </c>
       <c r="R90" t="n">
-        <v>6748290</v>
+        <v>6748390</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10217,7 +10226,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10227,7 +10236,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10254,54 +10263,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129542969</v>
+        <v>129543049</v>
       </c>
       <c r="B91" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457879</v>
+        <v>458018</v>
       </c>
       <c r="R91" t="n">
-        <v>6748454</v>
+        <v>6748602</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10370,32 +10370,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129542939</v>
+        <v>129543028</v>
       </c>
       <c r="B92" t="n">
-        <v>97640</v>
+        <v>79076</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457660</v>
+        <v>457753</v>
       </c>
       <c r="R92" t="n">
-        <v>6748092</v>
+        <v>6748290</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11873,32 +11873,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543094</v>
+        <v>129542981</v>
       </c>
       <c r="B106" t="n">
-        <v>78742</v>
+        <v>91761</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457728</v>
+        <v>457964</v>
       </c>
       <c r="R106" t="n">
-        <v>6748093</v>
+        <v>6748415</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11980,45 +11980,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543095</v>
+        <v>129543111</v>
       </c>
       <c r="B107" t="n">
-        <v>78742</v>
+        <v>5177</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457704</v>
+        <v>457665</v>
       </c>
       <c r="R107" t="n">
-        <v>6748074</v>
+        <v>6748081</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12050,7 +12055,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12060,7 +12065,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12087,7 +12092,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129543096</v>
+        <v>129543094</v>
       </c>
       <c r="B108" t="n">
         <v>78742</v>
@@ -12122,10 +12127,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457671</v>
+        <v>457728</v>
       </c>
       <c r="R108" t="n">
-        <v>6748048</v>
+        <v>6748093</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,7 +12162,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12167,7 +12172,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12194,10 +12199,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543012</v>
+        <v>129543095</v>
       </c>
       <c r="B109" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12205,21 +12210,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12229,10 +12234,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457625</v>
+        <v>457704</v>
       </c>
       <c r="R109" t="n">
-        <v>6748127</v>
+        <v>6748074</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12264,7 +12269,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12274,7 +12279,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12301,32 +12306,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129542981</v>
+        <v>129543096</v>
       </c>
       <c r="B110" t="n">
-        <v>91761</v>
+        <v>78742</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12336,10 +12341,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457964</v>
+        <v>457671</v>
       </c>
       <c r="R110" t="n">
-        <v>6748415</v>
+        <v>6748048</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12371,7 +12376,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12381,7 +12386,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12408,50 +12413,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543111</v>
+        <v>129543012</v>
       </c>
       <c r="B111" t="n">
-        <v>5177</v>
+        <v>79076</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457665</v>
+        <v>457625</v>
       </c>
       <c r="R111" t="n">
-        <v>6748081</v>
+        <v>6748127</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15531,10 +15531,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129543089</v>
+        <v>129542963</v>
       </c>
       <c r="B140" t="n">
-        <v>78742</v>
+        <v>78833</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>457809</v>
+        <v>457754</v>
       </c>
       <c r="R140" t="n">
-        <v>6748254</v>
+        <v>6748230</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15638,10 +15638,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129543074</v>
+        <v>129542965</v>
       </c>
       <c r="B141" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457905</v>
+        <v>457760</v>
       </c>
       <c r="R141" t="n">
-        <v>6748321</v>
+        <v>6748255</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15745,10 +15745,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129543022</v>
+        <v>129543089</v>
       </c>
       <c r="B142" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15756,21 +15756,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457761</v>
+        <v>457809</v>
       </c>
       <c r="R142" t="n">
-        <v>6748192</v>
+        <v>6748254</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15852,7 +15852,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129543052</v>
+        <v>129543074</v>
       </c>
       <c r="B143" t="n">
         <v>79076</v>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>458081</v>
+        <v>457905</v>
       </c>
       <c r="R143" t="n">
-        <v>6748667</v>
+        <v>6748321</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15959,10 +15959,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129542958</v>
+        <v>129543022</v>
       </c>
       <c r="B144" t="n">
-        <v>81061</v>
+        <v>79076</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15970,21 +15970,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>458029</v>
+        <v>457761</v>
       </c>
       <c r="R144" t="n">
-        <v>6748402</v>
+        <v>6748192</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16066,10 +16066,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129542963</v>
+        <v>129543052</v>
       </c>
       <c r="B145" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16077,21 +16077,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>457754</v>
+        <v>458081</v>
       </c>
       <c r="R145" t="n">
-        <v>6748230</v>
+        <v>6748667</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16173,10 +16173,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129542965</v>
+        <v>129542958</v>
       </c>
       <c r="B146" t="n">
-        <v>78833</v>
+        <v>81061</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16184,21 +16184,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>457760</v>
+        <v>458029</v>
       </c>
       <c r="R146" t="n">
-        <v>6748255</v>
+        <v>6748402</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16280,32 +16280,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129543100</v>
+        <v>129542941</v>
       </c>
       <c r="B147" t="n">
-        <v>78742</v>
+        <v>97640</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457631</v>
+        <v>457929</v>
       </c>
       <c r="R147" t="n">
-        <v>6748174</v>
+        <v>6748448</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,10 +16387,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129543069</v>
+        <v>129543100</v>
       </c>
       <c r="B148" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16398,21 +16398,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457930</v>
+        <v>457631</v>
       </c>
       <c r="R148" t="n">
-        <v>6748385</v>
+        <v>6748174</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16494,7 +16494,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129542994</v>
+        <v>129543069</v>
       </c>
       <c r="B149" t="n">
         <v>79076</v>
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457786</v>
+        <v>457930</v>
       </c>
       <c r="R149" t="n">
-        <v>6748280</v>
+        <v>6748385</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16601,7 +16601,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129543006</v>
+        <v>129542994</v>
       </c>
       <c r="B150" t="n">
         <v>79076</v>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457712</v>
+        <v>457786</v>
       </c>
       <c r="R150" t="n">
-        <v>6748081</v>
+        <v>6748280</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16708,7 +16708,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129543023</v>
+        <v>129543006</v>
       </c>
       <c r="B151" t="n">
         <v>79076</v>
@@ -16743,10 +16743,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457758</v>
+        <v>457712</v>
       </c>
       <c r="R151" t="n">
-        <v>6748213</v>
+        <v>6748081</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16815,32 +16815,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129542941</v>
+        <v>129543023</v>
       </c>
       <c r="B152" t="n">
-        <v>97640</v>
+        <v>79076</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457929</v>
+        <v>457758</v>
       </c>
       <c r="R152" t="n">
-        <v>6748448</v>
+        <v>6748213</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129542980</v>
+        <v>129543068</v>
       </c>
       <c r="B153" t="n">
-        <v>91761</v>
+        <v>79076</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>458058</v>
+        <v>457935</v>
       </c>
       <c r="R153" t="n">
-        <v>6748621</v>
+        <v>6748390</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17029,10 +17029,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129542959</v>
+        <v>129543067</v>
       </c>
       <c r="B154" t="n">
-        <v>81061</v>
+        <v>79076</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17040,21 +17040,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457884</v>
+        <v>457946</v>
       </c>
       <c r="R154" t="n">
-        <v>6748404</v>
+        <v>6748380</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17136,32 +17136,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129542945</v>
+        <v>129543033</v>
       </c>
       <c r="B155" t="n">
-        <v>97646</v>
+        <v>79076</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>457654</v>
+        <v>457836</v>
       </c>
       <c r="R155" t="n">
-        <v>6748079</v>
+        <v>6748291</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542943</v>
+        <v>129542980</v>
       </c>
       <c r="B156" t="n">
-        <v>97640</v>
+        <v>91761</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221945</v>
+        <v>1503</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>457999</v>
+        <v>458058</v>
       </c>
       <c r="R156" t="n">
-        <v>6748381</v>
+        <v>6748621</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17350,10 +17350,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129543068</v>
+        <v>129542959</v>
       </c>
       <c r="B157" t="n">
-        <v>79076</v>
+        <v>81061</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17361,21 +17361,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457935</v>
+        <v>457884</v>
       </c>
       <c r="R157" t="n">
-        <v>6748390</v>
+        <v>6748404</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17457,32 +17457,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129543067</v>
+        <v>129542945</v>
       </c>
       <c r="B158" t="n">
-        <v>79076</v>
+        <v>97646</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457946</v>
+        <v>457654</v>
       </c>
       <c r="R158" t="n">
-        <v>6748380</v>
+        <v>6748079</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17564,32 +17564,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129543033</v>
+        <v>129542943</v>
       </c>
       <c r="B159" t="n">
-        <v>79076</v>
+        <v>97640</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457836</v>
+        <v>457999</v>
       </c>
       <c r="R159" t="n">
-        <v>6748291</v>
+        <v>6748381</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129542925</v>
+        <v>129542951</v>
       </c>
       <c r="B2" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457896</v>
+        <v>457817</v>
       </c>
       <c r="R2" t="n">
-        <v>6748335</v>
+        <v>6748352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>129543108</v>
       </c>
       <c r="B3" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543007</v>
+        <v>129543024</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457677</v>
+        <v>457755</v>
       </c>
       <c r="R4" t="n">
-        <v>6748051</v>
+        <v>6748219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,17 +994,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543031</v>
+        <v>129543007</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457809</v>
+        <v>457677</v>
       </c>
       <c r="R5" t="n">
-        <v>6748286</v>
+        <v>6748051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,17 +1101,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543024</v>
+        <v>129543031</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457755</v>
+        <v>457809</v>
       </c>
       <c r="R6" t="n">
-        <v>6748219</v>
+        <v>6748286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>129543041</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
         <v>129543026</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>129543056</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,17 +1529,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129542951</v>
+        <v>129542925</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>56926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,27 +1547,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457817</v>
+        <v>457896</v>
       </c>
       <c r="R10" t="n">
-        <v>6748352</v>
+        <v>6748335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543081</v>
+        <v>129543091</v>
       </c>
       <c r="B11" t="n">
-        <v>91861</v>
+        <v>78747</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458131</v>
+        <v>457817</v>
       </c>
       <c r="R11" t="n">
-        <v>6748547</v>
+        <v>6748202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543091</v>
+        <v>129543092</v>
       </c>
       <c r="B12" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457817</v>
+        <v>457785</v>
       </c>
       <c r="R12" t="n">
-        <v>6748202</v>
+        <v>6748160</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543092</v>
+        <v>129542924</v>
       </c>
       <c r="B13" t="n">
-        <v>78742</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457785</v>
+        <v>457899</v>
       </c>
       <c r="R13" t="n">
-        <v>6748160</v>
+        <v>6748444</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129543043</v>
+        <v>129542915</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457927</v>
+        <v>457754</v>
       </c>
       <c r="R14" t="n">
-        <v>6748447</v>
+        <v>6748230</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129542992</v>
+        <v>129542995</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457763</v>
+        <v>457809</v>
       </c>
       <c r="R15" t="n">
-        <v>6748301</v>
+        <v>6748246</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543017</v>
+        <v>129543081</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>91866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457657</v>
+        <v>458131</v>
       </c>
       <c r="R16" t="n">
-        <v>6748226</v>
+        <v>6748547</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543070</v>
+        <v>129543043</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457936</v>
+        <v>457927</v>
       </c>
       <c r="R17" t="n">
-        <v>6748379</v>
+        <v>6748447</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,17 +2390,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129542915</v>
+        <v>129542992</v>
       </c>
       <c r="B18" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457754</v>
+        <v>457763</v>
       </c>
       <c r="R18" t="n">
-        <v>6748230</v>
+        <v>6748301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129542924</v>
+        <v>129543017</v>
       </c>
       <c r="B19" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457899</v>
+        <v>457657</v>
       </c>
       <c r="R19" t="n">
-        <v>6748444</v>
+        <v>6748226</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,17 +2604,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129542928</v>
+        <v>129543070</v>
       </c>
       <c r="B20" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,39 +2622,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457940</v>
+        <v>457936</v>
       </c>
       <c r="R20" t="n">
-        <v>6748387</v>
+        <v>6748379</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2716,17 +2711,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129542995</v>
+        <v>129542928</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,34 +2729,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457809</v>
+        <v>457940</v>
       </c>
       <c r="R21" t="n">
-        <v>6748246</v>
+        <v>6748387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129543107</v>
+        <v>129542996</v>
       </c>
       <c r="B22" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458144</v>
+        <v>457833</v>
       </c>
       <c r="R22" t="n">
-        <v>6748538</v>
+        <v>6748233</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129542996</v>
+        <v>129542982</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457833</v>
+        <v>457941</v>
       </c>
       <c r="R23" t="n">
-        <v>6748233</v>
+        <v>6748477</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +3017,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543038</v>
+        <v>129542913</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,21 +3060,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457829</v>
+        <v>457761</v>
       </c>
       <c r="R24" t="n">
-        <v>6748366</v>
+        <v>6748133</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543005</v>
+        <v>129543038</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457775</v>
+        <v>457829</v>
       </c>
       <c r="R25" t="n">
-        <v>6748148</v>
+        <v>6748366</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3251,17 +3256,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543051</v>
+        <v>129543005</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3293,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458077</v>
+        <v>457775</v>
       </c>
       <c r="R26" t="n">
-        <v>6748657</v>
+        <v>6748148</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3343,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3358,17 +3363,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543045</v>
+        <v>129543051</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457912</v>
+        <v>458077</v>
       </c>
       <c r="R27" t="n">
-        <v>6748485</v>
+        <v>6748657</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,7 +3440,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3445,7 +3450,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3465,17 +3470,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543032</v>
+        <v>129543045</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,10 +3512,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457821</v>
+        <v>457912</v>
       </c>
       <c r="R28" t="n">
-        <v>6748297</v>
+        <v>6748485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3552,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,17 +3577,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129542982</v>
+        <v>129543032</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,10 +3619,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457941</v>
+        <v>457821</v>
       </c>
       <c r="R29" t="n">
-        <v>6748477</v>
+        <v>6748297</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,7 +3654,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,12 +3664,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129542913</v>
+        <v>129543107</v>
       </c>
       <c r="B30" t="n">
-        <v>79695</v>
+        <v>78747</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3702,21 +3702,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457761</v>
+        <v>458144</v>
       </c>
       <c r="R30" t="n">
-        <v>6748133</v>
+        <v>6748538</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3798,45 +3798,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543090</v>
+        <v>129542949</v>
       </c>
       <c r="B31" t="n">
-        <v>78742</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457883</v>
+        <v>457627</v>
       </c>
       <c r="R31" t="n">
-        <v>6748264</v>
+        <v>6748161</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3878,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3905,10 +3910,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543018</v>
+        <v>129543090</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,21 +3921,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457679</v>
+        <v>457883</v>
       </c>
       <c r="R32" t="n">
-        <v>6748231</v>
+        <v>6748264</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543063</v>
+        <v>129543021</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4047,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458116</v>
+        <v>457756</v>
       </c>
       <c r="R33" t="n">
-        <v>6748548</v>
+        <v>6748192</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4092,7 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,17 +4117,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129543059</v>
+        <v>129543018</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,10 +4159,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458174</v>
+        <v>457679</v>
       </c>
       <c r="R34" t="n">
-        <v>6748599</v>
+        <v>6748231</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4199,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4219,17 +4224,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543021</v>
+        <v>129542966</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4237,21 +4242,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4261,10 +4266,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457756</v>
+        <v>457938</v>
       </c>
       <c r="R35" t="n">
-        <v>6748192</v>
+        <v>6748466</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4306,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4333,10 +4338,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129542993</v>
+        <v>129543063</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,10 +4373,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457763</v>
+        <v>458116</v>
       </c>
       <c r="R36" t="n">
-        <v>6748294</v>
+        <v>6748548</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,7 +4408,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4418,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4433,57 +4438,52 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129542949</v>
+        <v>129543059</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457627</v>
+        <v>458174</v>
       </c>
       <c r="R37" t="n">
-        <v>6748161</v>
+        <v>6748599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,17 +4545,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542966</v>
+        <v>129542993</v>
       </c>
       <c r="B38" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,21 +4563,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457938</v>
+        <v>457763</v>
       </c>
       <c r="R38" t="n">
-        <v>6748466</v>
+        <v>6748294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4662,7 +4662,7 @@
         <v>129542942</v>
       </c>
       <c r="B39" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543071</v>
+        <v>129543098</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457928</v>
+        <v>457657</v>
       </c>
       <c r="R40" t="n">
-        <v>6748344</v>
+        <v>6748066</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129542998</v>
+        <v>129543093</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457876</v>
+        <v>457737</v>
       </c>
       <c r="R41" t="n">
-        <v>6748240</v>
+        <v>6748103</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4980,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543003</v>
+        <v>129542946</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>91646</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457814</v>
+        <v>458035</v>
       </c>
       <c r="R42" t="n">
-        <v>6748175</v>
+        <v>6748395</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5090,7 +5090,7 @@
         <v>129543057</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5187,17 +5187,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129542946</v>
+        <v>129543071</v>
       </c>
       <c r="B44" t="n">
-        <v>91641</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458035</v>
+        <v>457928</v>
       </c>
       <c r="R44" t="n">
-        <v>6748395</v>
+        <v>6748344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,39 +5294,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129543112</v>
+        <v>129542998</v>
       </c>
       <c r="B45" t="n">
-        <v>91645</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>458029</v>
+        <v>457876</v>
       </c>
       <c r="R45" t="n">
-        <v>6748411</v>
+        <v>6748240</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,7 +5390,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5402,57 +5401,52 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129542927</v>
+        <v>129543112</v>
       </c>
       <c r="B46" t="n">
-        <v>57896</v>
+        <v>91650</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>5321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458027</v>
+        <v>458029</v>
       </c>
       <c r="R46" t="n">
-        <v>6748413</v>
+        <v>6748411</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5503,6 +5497,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5521,10 +5516,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543098</v>
+        <v>129543003</v>
       </c>
       <c r="B47" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5532,21 +5527,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5556,10 +5551,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457657</v>
+        <v>457814</v>
       </c>
       <c r="R47" t="n">
-        <v>6748066</v>
+        <v>6748175</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5591,7 +5586,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5601,7 +5596,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5621,17 +5616,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129543093</v>
+        <v>129542927</v>
       </c>
       <c r="B48" t="n">
-        <v>78742</v>
+        <v>57896</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5639,34 +5634,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457737</v>
+        <v>458027</v>
       </c>
       <c r="R48" t="n">
-        <v>6748103</v>
+        <v>6748413</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543082</v>
+        <v>129543009</v>
       </c>
       <c r="B49" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457792</v>
+        <v>457654</v>
       </c>
       <c r="R49" t="n">
-        <v>6748260</v>
+        <v>6748079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5845,7 +5845,7 @@
         <v>129543078</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5952,7 +5952,7 @@
         <v>129543010</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6049,17 +6049,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543009</v>
+        <v>129543082</v>
       </c>
       <c r="B52" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6067,21 +6067,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457654</v>
+        <v>457792</v>
       </c>
       <c r="R52" t="n">
-        <v>6748079</v>
+        <v>6748260</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6156,17 +6156,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543034</v>
+        <v>129543042</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457852</v>
+        <v>457922</v>
       </c>
       <c r="R53" t="n">
-        <v>6748316</v>
+        <v>6748447</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6263,17 +6263,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543001</v>
+        <v>129543072</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457838</v>
+        <v>457899</v>
       </c>
       <c r="R54" t="n">
-        <v>6748208</v>
+        <v>6748357</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6370,52 +6370,57 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543064</v>
+        <v>129542950</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458049</v>
+        <v>457695</v>
       </c>
       <c r="R55" t="n">
-        <v>6748509</v>
+        <v>6748215</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6447,7 +6452,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6457,7 +6462,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6484,10 +6489,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543072</v>
+        <v>129542914</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6495,21 +6500,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6519,10 +6524,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457899</v>
+        <v>457650</v>
       </c>
       <c r="R56" t="n">
-        <v>6748357</v>
+        <v>6748064</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6554,7 +6559,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6564,7 +6569,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,10 +6596,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543035</v>
+        <v>129543064</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6626,10 +6631,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457845</v>
+        <v>458049</v>
       </c>
       <c r="R57" t="n">
-        <v>6748327</v>
+        <v>6748509</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6666,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6671,7 +6676,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6691,17 +6696,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543066</v>
+        <v>129543035</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6733,10 +6738,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458042</v>
+        <v>457845</v>
       </c>
       <c r="R58" t="n">
-        <v>6748499</v>
+        <v>6748327</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6768,7 +6773,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6778,7 +6783,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6798,57 +6803,52 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129542950</v>
+        <v>129543066</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457695</v>
+        <v>458042</v>
       </c>
       <c r="R59" t="n">
-        <v>6748215</v>
+        <v>6748499</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6910,57 +6910,52 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129542948</v>
+        <v>129543034</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457777</v>
+        <v>457852</v>
       </c>
       <c r="R60" t="n">
-        <v>6748294</v>
+        <v>6748316</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6992,7 +6987,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7002,7 +6997,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7022,17 +7017,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543042</v>
+        <v>129543001</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7064,10 +7059,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457922</v>
+        <v>457838</v>
       </c>
       <c r="R61" t="n">
-        <v>6748447</v>
+        <v>6748208</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7099,7 +7094,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7109,7 +7104,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7129,52 +7124,57 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129542914</v>
+        <v>129542948</v>
       </c>
       <c r="B62" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457650</v>
+        <v>457777</v>
       </c>
       <c r="R62" t="n">
-        <v>6748064</v>
+        <v>6748294</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7246,7 +7246,7 @@
         <v>129543097</v>
       </c>
       <c r="B63" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7350,10 +7350,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543073</v>
+        <v>129543019</v>
       </c>
       <c r="B64" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457917</v>
+        <v>457725</v>
       </c>
       <c r="R64" t="n">
-        <v>6748303</v>
+        <v>6748208</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7450,17 +7450,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543047</v>
+        <v>129542961</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457952</v>
+        <v>457859</v>
       </c>
       <c r="R65" t="n">
-        <v>6748501</v>
+        <v>6748231</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7564,10 +7564,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543019</v>
+        <v>129542962</v>
       </c>
       <c r="B66" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7575,21 +7575,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457725</v>
+        <v>457762</v>
       </c>
       <c r="R66" t="n">
         <v>6748208</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7671,10 +7671,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543060</v>
+        <v>129543002</v>
       </c>
       <c r="B67" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458177</v>
+        <v>457813</v>
       </c>
       <c r="R67" t="n">
-        <v>6748587</v>
+        <v>6748191</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7771,17 +7771,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543029</v>
+        <v>129543073</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457780</v>
+        <v>457917</v>
       </c>
       <c r="R68" t="n">
-        <v>6748311</v>
+        <v>6748303</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7878,17 +7878,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543002</v>
+        <v>129543047</v>
       </c>
       <c r="B69" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457813</v>
+        <v>457952</v>
       </c>
       <c r="R69" t="n">
-        <v>6748191</v>
+        <v>6748501</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7985,17 +7985,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543053</v>
+        <v>129543060</v>
       </c>
       <c r="B70" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458094</v>
+        <v>458177</v>
       </c>
       <c r="R70" t="n">
-        <v>6748667</v>
+        <v>6748587</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8092,17 +8092,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129542962</v>
+        <v>129543029</v>
       </c>
       <c r="B71" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8110,21 +8110,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457762</v>
+        <v>457780</v>
       </c>
       <c r="R71" t="n">
-        <v>6748208</v>
+        <v>6748311</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8199,17 +8199,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129542961</v>
+        <v>129543053</v>
       </c>
       <c r="B72" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457859</v>
+        <v>458094</v>
       </c>
       <c r="R72" t="n">
-        <v>6748231</v>
+        <v>6748667</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8428,7 +8428,7 @@
         <v>129543101</v>
       </c>
       <c r="B74" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>129543105</v>
       </c>
       <c r="B75" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129542997</v>
+        <v>129543000</v>
       </c>
       <c r="B76" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8674,10 +8674,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457863</v>
+        <v>457846</v>
       </c>
       <c r="R76" t="n">
-        <v>6748231</v>
+        <v>6748214</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8739,17 +8739,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543000</v>
+        <v>129542997</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457846</v>
+        <v>457863</v>
       </c>
       <c r="R77" t="n">
-        <v>6748214</v>
+        <v>6748231</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8853,10 +8853,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129542999</v>
+        <v>129543075</v>
       </c>
       <c r="B78" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457883</v>
+        <v>457896</v>
       </c>
       <c r="R78" t="n">
-        <v>6748260</v>
+        <v>6748336</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8953,17 +8953,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543075</v>
+        <v>129542933</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8971,34 +8971,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457896</v>
+        <v>457753</v>
       </c>
       <c r="R79" t="n">
-        <v>6748336</v>
+        <v>6748178</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,7 +9035,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9040,7 +9045,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9067,10 +9072,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129542933</v>
+        <v>129542999</v>
       </c>
       <c r="B80" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9078,39 +9083,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457753</v>
+        <v>457883</v>
       </c>
       <c r="R80" t="n">
-        <v>6748178</v>
+        <v>6748260</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9182,7 +9182,7 @@
         <v>129542991</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>129543065</v>
       </c>
       <c r="B82" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9386,17 +9386,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129542964</v>
+        <v>129543103</v>
       </c>
       <c r="B83" t="n">
-        <v>78833</v>
+        <v>78747</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9404,21 +9404,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457767</v>
+        <v>457842</v>
       </c>
       <c r="R83" t="n">
-        <v>6748250</v>
+        <v>6748363</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9500,10 +9500,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129542968</v>
+        <v>129543088</v>
       </c>
       <c r="B84" t="n">
-        <v>78833</v>
+        <v>78747</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9511,21 +9511,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>458060</v>
+        <v>457797</v>
       </c>
       <c r="R84" t="n">
-        <v>6748629</v>
+        <v>6748261</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9600,17 +9600,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543103</v>
+        <v>129542968</v>
       </c>
       <c r="B85" t="n">
-        <v>78742</v>
+        <v>78838</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9618,21 +9618,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>457842</v>
+        <v>458060</v>
       </c>
       <c r="R85" t="n">
-        <v>6748363</v>
+        <v>6748629</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9714,10 +9714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543088</v>
+        <v>129542964</v>
       </c>
       <c r="B86" t="n">
-        <v>78742</v>
+        <v>78838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9725,21 +9725,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457797</v>
+        <v>457767</v>
       </c>
       <c r="R86" t="n">
-        <v>6748261</v>
+        <v>6748250</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9824,7 +9824,7 @@
         <v>129543085</v>
       </c>
       <c r="B87" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,61 +9926,52 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129542969</v>
+        <v>129543076</v>
       </c>
       <c r="B88" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457879</v>
+        <v>457917</v>
       </c>
       <c r="R88" t="n">
-        <v>6748454</v>
+        <v>6748390</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10012,7 +10003,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10022,7 +10013,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10042,39 +10033,39 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129542939</v>
+        <v>129543049</v>
       </c>
       <c r="B89" t="n">
-        <v>97640</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10084,10 +10075,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457660</v>
+        <v>458018</v>
       </c>
       <c r="R89" t="n">
-        <v>6748092</v>
+        <v>6748602</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10119,7 +10110,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10129,7 +10120,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10149,17 +10140,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543076</v>
+        <v>129543028</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10191,10 +10182,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457917</v>
+        <v>457753</v>
       </c>
       <c r="R90" t="n">
-        <v>6748390</v>
+        <v>6748290</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10226,7 +10217,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10236,7 +10227,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10256,39 +10247,39 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129543049</v>
+        <v>129542939</v>
       </c>
       <c r="B91" t="n">
-        <v>79076</v>
+        <v>97645</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10298,10 +10289,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458018</v>
+        <v>457660</v>
       </c>
       <c r="R91" t="n">
-        <v>6748602</v>
+        <v>6748092</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10333,7 +10324,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10343,7 +10334,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10370,45 +10361,54 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543028</v>
+        <v>129542969</v>
       </c>
       <c r="B92" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457753</v>
+        <v>457879</v>
       </c>
       <c r="R92" t="n">
-        <v>6748290</v>
+        <v>6748454</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10477,10 +10477,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543013</v>
+        <v>129543014</v>
       </c>
       <c r="B93" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457621</v>
+        <v>457634</v>
       </c>
       <c r="R93" t="n">
-        <v>6748147</v>
+        <v>6748179</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10577,17 +10577,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543014</v>
+        <v>129543013</v>
       </c>
       <c r="B94" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457634</v>
+        <v>457621</v>
       </c>
       <c r="R94" t="n">
-        <v>6748179</v>
+        <v>6748147</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10684,17 +10684,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543037</v>
+        <v>129543062</v>
       </c>
       <c r="B95" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457830</v>
+        <v>458140</v>
       </c>
       <c r="R95" t="n">
-        <v>6748350</v>
+        <v>6748536</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10801,7 +10801,7 @@
         <v>129543030</v>
       </c>
       <c r="B96" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10898,39 +10898,39 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543020</v>
+        <v>129542960</v>
       </c>
       <c r="B97" t="n">
-        <v>79076</v>
+        <v>80146</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457738</v>
+        <v>458029</v>
       </c>
       <c r="R97" t="n">
-        <v>6748205</v>
+        <v>6748413</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10985,7 +10985,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt på jätteasp</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,10 +11017,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543016</v>
+        <v>129543099</v>
       </c>
       <c r="B98" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11023,21 +11028,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11047,10 +11052,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457699</v>
+        <v>457650</v>
       </c>
       <c r="R98" t="n">
-        <v>6748197</v>
+        <v>6748064</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,7 +11087,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11092,7 +11097,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11124,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543062</v>
+        <v>129543104</v>
       </c>
       <c r="B99" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11130,21 +11135,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11154,10 +11159,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458140</v>
+        <v>457992</v>
       </c>
       <c r="R99" t="n">
-        <v>6748536</v>
+        <v>6748556</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,7 +11194,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11199,7 +11204,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11226,10 +11231,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543039</v>
+        <v>129542956</v>
       </c>
       <c r="B100" t="n">
-        <v>79076</v>
+        <v>81066</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11237,21 +11242,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11261,10 +11266,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>457830</v>
+        <v>457662</v>
       </c>
       <c r="R100" t="n">
-        <v>6748402</v>
+        <v>6748216</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11296,7 +11301,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11306,7 +11311,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,10 +11338,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543099</v>
+        <v>129543083</v>
       </c>
       <c r="B101" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11368,10 +11373,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>457650</v>
+        <v>457757</v>
       </c>
       <c r="R101" t="n">
-        <v>6748064</v>
+        <v>6748191</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,7 +11408,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11413,7 +11418,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11433,17 +11438,17 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543104</v>
+        <v>129543037</v>
       </c>
       <c r="B102" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11451,21 +11456,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11475,10 +11480,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>457992</v>
+        <v>457830</v>
       </c>
       <c r="R102" t="n">
-        <v>6748556</v>
+        <v>6748350</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11510,7 +11515,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11520,7 +11525,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11540,17 +11545,17 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543083</v>
+        <v>129543039</v>
       </c>
       <c r="B103" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11558,21 +11563,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11582,10 +11587,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>457757</v>
+        <v>457830</v>
       </c>
       <c r="R103" t="n">
-        <v>6748191</v>
+        <v>6748402</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,7 +11622,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11627,7 +11632,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11647,17 +11652,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129542956</v>
+        <v>129543020</v>
       </c>
       <c r="B104" t="n">
-        <v>81061</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11665,21 +11670,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11689,10 +11694,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>457662</v>
+        <v>457738</v>
       </c>
       <c r="R104" t="n">
-        <v>6748216</v>
+        <v>6748205</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11724,7 +11729,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11734,7 +11739,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11754,39 +11759,39 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129542960</v>
+        <v>129543016</v>
       </c>
       <c r="B105" t="n">
-        <v>80141</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11796,10 +11801,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458029</v>
+        <v>457699</v>
       </c>
       <c r="R105" t="n">
-        <v>6748413</v>
+        <v>6748197</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11831,7 +11836,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11841,12 +11846,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Rikligt på jätteasp</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11866,39 +11866,39 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129542981</v>
+        <v>129543094</v>
       </c>
       <c r="B106" t="n">
-        <v>91761</v>
+        <v>78747</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>457964</v>
+        <v>457728</v>
       </c>
       <c r="R106" t="n">
-        <v>6748415</v>
+        <v>6748093</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11980,50 +11980,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543111</v>
+        <v>129542981</v>
       </c>
       <c r="B107" t="n">
-        <v>5177</v>
+        <v>91766</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100526</v>
+        <v>1503</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>457665</v>
+        <v>457964</v>
       </c>
       <c r="R107" t="n">
-        <v>6748081</v>
+        <v>6748415</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12055,7 +12050,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12065,7 +12060,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12092,10 +12087,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129543094</v>
+        <v>129543095</v>
       </c>
       <c r="B108" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12127,10 +12122,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>457728</v>
+        <v>457704</v>
       </c>
       <c r="R108" t="n">
-        <v>6748093</v>
+        <v>6748074</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12162,7 +12157,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12172,7 +12167,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12199,10 +12194,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543095</v>
+        <v>129543096</v>
       </c>
       <c r="B109" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12234,10 +12229,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>457704</v>
+        <v>457671</v>
       </c>
       <c r="R109" t="n">
-        <v>6748074</v>
+        <v>6748048</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12269,7 +12264,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12279,7 +12274,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12306,10 +12301,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543096</v>
+        <v>129543012</v>
       </c>
       <c r="B110" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12317,21 +12312,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12341,10 +12336,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>457671</v>
+        <v>457625</v>
       </c>
       <c r="R110" t="n">
-        <v>6748048</v>
+        <v>6748127</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12376,7 +12371,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12386,7 +12381,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12406,52 +12401,57 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543012</v>
+        <v>129543111</v>
       </c>
       <c r="B111" t="n">
-        <v>79076</v>
+        <v>5177</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>457625</v>
+        <v>457665</v>
       </c>
       <c r="R111" t="n">
-        <v>6748127</v>
+        <v>6748081</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12520,10 +12520,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129542935</v>
+        <v>129542955</v>
       </c>
       <c r="B112" t="n">
-        <v>57733</v>
+        <v>92235</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12531,39 +12531,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>5454</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458060</v>
+        <v>458015</v>
       </c>
       <c r="R112" t="n">
-        <v>6748631</v>
+        <v>6748399</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12595,7 +12590,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12605,7 +12600,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12632,32 +12627,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129542944</v>
+        <v>129543011</v>
       </c>
       <c r="B113" t="n">
-        <v>97646</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12667,10 +12662,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>457654</v>
+        <v>457665</v>
       </c>
       <c r="R113" t="n">
-        <v>6748070</v>
+        <v>6748082</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12702,7 +12697,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12712,7 +12707,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12732,17 +12727,17 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129542955</v>
+        <v>129542923</v>
       </c>
       <c r="B114" t="n">
-        <v>92230</v>
+        <v>79176</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12750,21 +12745,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5454</v>
+        <v>967</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12774,10 +12769,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458015</v>
+        <v>457773</v>
       </c>
       <c r="R114" t="n">
-        <v>6748399</v>
+        <v>6748248</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12809,7 +12804,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12819,7 +12814,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12846,10 +12841,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129543011</v>
+        <v>129543008</v>
       </c>
       <c r="B115" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12881,10 +12876,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457665</v>
+        <v>457671</v>
       </c>
       <c r="R115" t="n">
-        <v>6748082</v>
+        <v>6748048</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12911,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12926,7 +12921,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12946,17 +12941,17 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129543008</v>
+        <v>129542935</v>
       </c>
       <c r="B116" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12964,34 +12959,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457671</v>
+        <v>458060</v>
       </c>
       <c r="R116" t="n">
-        <v>6748048</v>
+        <v>6748631</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13060,32 +13060,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129542923</v>
+        <v>129542944</v>
       </c>
       <c r="B117" t="n">
-        <v>79171</v>
+        <v>97651</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>967</v>
+        <v>221941</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457773</v>
+        <v>457654</v>
       </c>
       <c r="R117" t="n">
-        <v>6748248</v>
+        <v>6748070</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13167,10 +13167,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129543054</v>
+        <v>129543061</v>
       </c>
       <c r="B118" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458097</v>
+        <v>458155</v>
       </c>
       <c r="R118" t="n">
-        <v>6748662</v>
+        <v>6748548</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13267,57 +13267,52 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129542947</v>
+        <v>129543054</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>457929</v>
+        <v>458097</v>
       </c>
       <c r="R119" t="n">
-        <v>6748484</v>
+        <v>6748662</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13349,7 +13344,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13359,7 +13354,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13379,52 +13374,57 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129543061</v>
+        <v>129542947</v>
       </c>
       <c r="B120" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>458155</v>
+        <v>457929</v>
       </c>
       <c r="R120" t="n">
-        <v>6748548</v>
+        <v>6748484</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13493,32 +13493,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129542940</v>
+        <v>129543102</v>
       </c>
       <c r="B121" t="n">
-        <v>97640</v>
+        <v>78747</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>457879</v>
+        <v>457761</v>
       </c>
       <c r="R121" t="n">
-        <v>6748455</v>
+        <v>6748256</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13600,10 +13600,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129543102</v>
+        <v>129542978</v>
       </c>
       <c r="B122" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13611,21 +13611,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>457761</v>
+        <v>457802</v>
       </c>
       <c r="R122" t="n">
-        <v>6748256</v>
+        <v>6748301</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13707,10 +13707,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129543046</v>
+        <v>129543004</v>
       </c>
       <c r="B123" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>457946</v>
+        <v>457802</v>
       </c>
       <c r="R123" t="n">
-        <v>6748493</v>
+        <v>6748157</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13807,17 +13807,17 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129543048</v>
+        <v>129543046</v>
       </c>
       <c r="B124" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>457954</v>
+        <v>457946</v>
       </c>
       <c r="R124" t="n">
-        <v>6748541</v>
+        <v>6748493</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13914,17 +13914,17 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129543004</v>
+        <v>129543027</v>
       </c>
       <c r="B125" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13956,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>457802</v>
+        <v>457756</v>
       </c>
       <c r="R125" t="n">
-        <v>6748157</v>
+        <v>6748271</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14021,17 +14021,17 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129543015</v>
+        <v>129543048</v>
       </c>
       <c r="B126" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457689</v>
+        <v>457954</v>
       </c>
       <c r="R126" t="n">
-        <v>6748165</v>
+        <v>6748541</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14128,17 +14128,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129542978</v>
+        <v>129542967</v>
       </c>
       <c r="B127" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14146,21 +14146,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>457802</v>
+        <v>457939</v>
       </c>
       <c r="R127" t="n">
-        <v>6748301</v>
+        <v>6748494</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14242,10 +14242,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129543027</v>
+        <v>129543015</v>
       </c>
       <c r="B128" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457756</v>
+        <v>457689</v>
       </c>
       <c r="R128" t="n">
-        <v>6748271</v>
+        <v>6748165</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14342,17 +14342,17 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129542967</v>
+        <v>129542936</v>
       </c>
       <c r="B129" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14360,34 +14360,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>457939</v>
+        <v>458155</v>
       </c>
       <c r="R129" t="n">
-        <v>6748494</v>
+        <v>6748562</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14419,7 +14424,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14429,7 +14434,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14459,7 +14464,7 @@
         <v>129543025</v>
       </c>
       <c r="B130" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14556,57 +14561,52 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129542936</v>
+        <v>129542940</v>
       </c>
       <c r="B131" t="n">
-        <v>57733</v>
+        <v>97645</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>458155</v>
+        <v>457879</v>
       </c>
       <c r="R131" t="n">
-        <v>6748562</v>
+        <v>6748455</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14675,10 +14675,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129543040</v>
+        <v>129542916</v>
       </c>
       <c r="B132" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14686,21 +14686,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457817</v>
+        <v>457750</v>
       </c>
       <c r="R132" t="n">
-        <v>6748400</v>
+        <v>6748276</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14782,10 +14782,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129543044</v>
+        <v>129543077</v>
       </c>
       <c r="B133" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457939</v>
+        <v>457938</v>
       </c>
       <c r="R133" t="n">
-        <v>6748453</v>
+        <v>6748409</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14882,17 +14882,17 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129543036</v>
+        <v>129543040</v>
       </c>
       <c r="B134" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14924,10 +14924,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>457843</v>
+        <v>457817</v>
       </c>
       <c r="R134" t="n">
-        <v>6748341</v>
+        <v>6748400</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14989,39 +14989,39 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129542920</v>
+        <v>129543044</v>
       </c>
       <c r="B135" t="n">
-        <v>91552</v>
+        <v>79081</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457964</v>
+        <v>457939</v>
       </c>
       <c r="R135" t="n">
-        <v>6748415</v>
+        <v>6748453</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129543058</v>
+        <v>129543050</v>
       </c>
       <c r="B136" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>458143</v>
+        <v>458067</v>
       </c>
       <c r="R136" t="n">
-        <v>6748611</v>
+        <v>6748648</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15203,17 +15203,17 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129543077</v>
+        <v>129543036</v>
       </c>
       <c r="B137" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>457938</v>
+        <v>457843</v>
       </c>
       <c r="R137" t="n">
-        <v>6748409</v>
+        <v>6748341</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15310,39 +15310,39 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129542916</v>
+        <v>129542920</v>
       </c>
       <c r="B138" t="n">
-        <v>79695</v>
+        <v>91557</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>457750</v>
+        <v>457964</v>
       </c>
       <c r="R138" t="n">
-        <v>6748276</v>
+        <v>6748415</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15424,10 +15424,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129543050</v>
+        <v>129543058</v>
       </c>
       <c r="B139" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>458067</v>
+        <v>458143</v>
       </c>
       <c r="R139" t="n">
-        <v>6748648</v>
+        <v>6748611</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15524,17 +15524,17 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129542963</v>
+        <v>129543089</v>
       </c>
       <c r="B140" t="n">
-        <v>78833</v>
+        <v>78747</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15542,21 +15542,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>457754</v>
+        <v>457809</v>
       </c>
       <c r="R140" t="n">
-        <v>6748230</v>
+        <v>6748254</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15631,17 +15631,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129542965</v>
+        <v>129542958</v>
       </c>
       <c r="B141" t="n">
-        <v>78833</v>
+        <v>81066</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15649,21 +15649,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457760</v>
+        <v>458029</v>
       </c>
       <c r="R141" t="n">
-        <v>6748255</v>
+        <v>6748402</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15745,10 +15745,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129543089</v>
+        <v>129543074</v>
       </c>
       <c r="B142" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15756,21 +15756,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457809</v>
+        <v>457905</v>
       </c>
       <c r="R142" t="n">
-        <v>6748254</v>
+        <v>6748321</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15845,17 +15845,17 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129543074</v>
+        <v>129543022</v>
       </c>
       <c r="B143" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>457905</v>
+        <v>457761</v>
       </c>
       <c r="R143" t="n">
-        <v>6748321</v>
+        <v>6748192</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15952,17 +15952,17 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129543022</v>
+        <v>129543052</v>
       </c>
       <c r="B144" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>457761</v>
+        <v>458081</v>
       </c>
       <c r="R144" t="n">
-        <v>6748192</v>
+        <v>6748667</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16059,17 +16059,17 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129543052</v>
+        <v>129542965</v>
       </c>
       <c r="B145" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16077,21 +16077,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>458081</v>
+        <v>457760</v>
       </c>
       <c r="R145" t="n">
-        <v>6748667</v>
+        <v>6748255</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16173,10 +16173,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129542958</v>
+        <v>129542963</v>
       </c>
       <c r="B146" t="n">
-        <v>81061</v>
+        <v>78838</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16184,21 +16184,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>458029</v>
+        <v>457754</v>
       </c>
       <c r="R146" t="n">
-        <v>6748402</v>
+        <v>6748230</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16280,32 +16280,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129542941</v>
+        <v>129543100</v>
       </c>
       <c r="B147" t="n">
-        <v>97640</v>
+        <v>78747</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>457929</v>
+        <v>457631</v>
       </c>
       <c r="R147" t="n">
-        <v>6748448</v>
+        <v>6748174</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16387,10 +16387,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129543100</v>
+        <v>129542994</v>
       </c>
       <c r="B148" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16398,21 +16398,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16422,10 +16422,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457631</v>
+        <v>457786</v>
       </c>
       <c r="R148" t="n">
-        <v>6748174</v>
+        <v>6748280</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16497,7 +16497,7 @@
         <v>129543069</v>
       </c>
       <c r="B149" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16594,17 +16594,17 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129542994</v>
+        <v>129543006</v>
       </c>
       <c r="B150" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16636,10 +16636,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457786</v>
+        <v>457712</v>
       </c>
       <c r="R150" t="n">
-        <v>6748280</v>
+        <v>6748081</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16701,17 +16701,17 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129543006</v>
+        <v>129543023</v>
       </c>
       <c r="B151" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16743,10 +16743,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457712</v>
+        <v>457758</v>
       </c>
       <c r="R151" t="n">
-        <v>6748081</v>
+        <v>6748213</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16808,39 +16808,39 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129543023</v>
+        <v>129542941</v>
       </c>
       <c r="B152" t="n">
-        <v>79076</v>
+        <v>97645</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457758</v>
+        <v>457929</v>
       </c>
       <c r="R152" t="n">
-        <v>6748213</v>
+        <v>6748448</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129543068</v>
+        <v>129542980</v>
       </c>
       <c r="B153" t="n">
-        <v>79076</v>
+        <v>91766</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>457935</v>
+        <v>458058</v>
       </c>
       <c r="R153" t="n">
-        <v>6748390</v>
+        <v>6748621</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17029,10 +17029,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129543067</v>
+        <v>129542959</v>
       </c>
       <c r="B154" t="n">
-        <v>79076</v>
+        <v>81066</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17040,21 +17040,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>457946</v>
+        <v>457884</v>
       </c>
       <c r="R154" t="n">
-        <v>6748380</v>
+        <v>6748404</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17139,7 +17139,7 @@
         <v>129543033</v>
       </c>
       <c r="B155" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17236,39 +17236,39 @@
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542980</v>
+        <v>129542945</v>
       </c>
       <c r="B156" t="n">
-        <v>91761</v>
+        <v>97651</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>458058</v>
+        <v>457654</v>
       </c>
       <c r="R156" t="n">
-        <v>6748621</v>
+        <v>6748079</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17350,32 +17350,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129542959</v>
+        <v>129542943</v>
       </c>
       <c r="B157" t="n">
-        <v>81061</v>
+        <v>97645</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1049</v>
+        <v>221945</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457884</v>
+        <v>457999</v>
       </c>
       <c r="R157" t="n">
-        <v>6748404</v>
+        <v>6748381</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17457,32 +17457,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129542945</v>
+        <v>129543068</v>
       </c>
       <c r="B158" t="n">
-        <v>97646</v>
+        <v>79081</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457654</v>
+        <v>457935</v>
       </c>
       <c r="R158" t="n">
-        <v>6748079</v>
+        <v>6748390</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17557,39 +17557,39 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129542943</v>
+        <v>129543067</v>
       </c>
       <c r="B159" t="n">
-        <v>97640</v>
+        <v>79081</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457999</v>
+        <v>457946</v>
       </c>
       <c r="R159" t="n">
-        <v>6748381</v>
+        <v>6748380</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129542951</v>
+        <v>129543108</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>78747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457817</v>
+        <v>458131</v>
       </c>
       <c r="R2" t="n">
-        <v>6748352</v>
+        <v>6748548</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129543108</v>
+        <v>129543007</v>
       </c>
       <c r="B3" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458131</v>
+        <v>457677</v>
       </c>
       <c r="R3" t="n">
-        <v>6748548</v>
+        <v>6748051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129543024</v>
+        <v>129543056</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457755</v>
+        <v>458120</v>
       </c>
       <c r="R4" t="n">
-        <v>6748219</v>
+        <v>6748624</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,14 +989,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543007</v>
+        <v>129543024</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457677</v>
+        <v>457755</v>
       </c>
       <c r="R5" t="n">
-        <v>6748051</v>
+        <v>6748219</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1422,52 +1417,57 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543056</v>
+        <v>129542925</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458120</v>
+        <v>457896</v>
       </c>
       <c r="R9" t="n">
-        <v>6748624</v>
+        <v>6748335</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129542925</v>
+        <v>129542951</v>
       </c>
       <c r="B10" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,27 +1547,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457896</v>
+        <v>457817</v>
       </c>
       <c r="R10" t="n">
-        <v>6748335</v>
+        <v>6748352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543091</v>
+        <v>129542924</v>
       </c>
       <c r="B11" t="n">
-        <v>78747</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457817</v>
+        <v>457899</v>
       </c>
       <c r="R11" t="n">
-        <v>6748202</v>
+        <v>6748444</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543092</v>
+        <v>129543081</v>
       </c>
       <c r="B12" t="n">
-        <v>78747</v>
+        <v>91866</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457785</v>
+        <v>458131</v>
       </c>
       <c r="R12" t="n">
-        <v>6748160</v>
+        <v>6748547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129542924</v>
+        <v>129543091</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>78747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457899</v>
+        <v>457817</v>
       </c>
       <c r="R13" t="n">
-        <v>6748444</v>
+        <v>6748202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129542915</v>
+        <v>129543092</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457754</v>
+        <v>457785</v>
       </c>
       <c r="R14" t="n">
-        <v>6748230</v>
+        <v>6748160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129542995</v>
+        <v>129542915</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457809</v>
+        <v>457754</v>
       </c>
       <c r="R15" t="n">
-        <v>6748246</v>
+        <v>6748230</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129543081</v>
+        <v>129542992</v>
       </c>
       <c r="B16" t="n">
-        <v>91866</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458131</v>
+        <v>457763</v>
       </c>
       <c r="R16" t="n">
-        <v>6748547</v>
+        <v>6748301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,14 +2283,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543043</v>
+        <v>129543070</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457927</v>
+        <v>457936</v>
       </c>
       <c r="R17" t="n">
-        <v>6748447</v>
+        <v>6748379</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,14 +2390,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129542992</v>
+        <v>129543017</v>
       </c>
       <c r="B18" t="n">
         <v>79081</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457763</v>
+        <v>457657</v>
       </c>
       <c r="R18" t="n">
-        <v>6748301</v>
+        <v>6748226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,7 +2504,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543017</v>
+        <v>129542995</v>
       </c>
       <c r="B19" t="n">
         <v>79081</v>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457657</v>
+        <v>457809</v>
       </c>
       <c r="R19" t="n">
-        <v>6748226</v>
+        <v>6748246</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,14 +2604,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543070</v>
+        <v>129543043</v>
       </c>
       <c r="B20" t="n">
         <v>79081</v>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457936</v>
+        <v>457927</v>
       </c>
       <c r="R20" t="n">
-        <v>6748379</v>
+        <v>6748447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129542996</v>
+        <v>129543032</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457833</v>
+        <v>457821</v>
       </c>
       <c r="R22" t="n">
-        <v>6748233</v>
+        <v>6748297</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129542982</v>
+        <v>129542996</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457941</v>
+        <v>457833</v>
       </c>
       <c r="R23" t="n">
-        <v>6748477</v>
+        <v>6748233</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,12 +3017,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129542913</v>
+        <v>129543045</v>
       </c>
       <c r="B24" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,21 +3055,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457761</v>
+        <v>457912</v>
       </c>
       <c r="R24" t="n">
-        <v>6748133</v>
+        <v>6748485</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,7 +3151,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543038</v>
+        <v>129542982</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3191,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457829</v>
+        <v>457941</v>
       </c>
       <c r="R25" t="n">
-        <v>6748366</v>
+        <v>6748477</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3231,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,14 +3256,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543005</v>
+        <v>129543038</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457775</v>
+        <v>457829</v>
       </c>
       <c r="R26" t="n">
-        <v>6748148</v>
+        <v>6748366</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543051</v>
+        <v>129542913</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3381,21 +3381,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458077</v>
+        <v>457761</v>
       </c>
       <c r="R27" t="n">
-        <v>6748657</v>
+        <v>6748133</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3470,14 +3470,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543045</v>
+        <v>129543051</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457912</v>
+        <v>458077</v>
       </c>
       <c r="R28" t="n">
-        <v>6748485</v>
+        <v>6748657</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543032</v>
+        <v>129543005</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457821</v>
+        <v>457775</v>
       </c>
       <c r="R29" t="n">
-        <v>6748297</v>
+        <v>6748148</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3798,50 +3798,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129542949</v>
+        <v>129543090</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>78747</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457627</v>
+        <v>457883</v>
       </c>
       <c r="R31" t="n">
-        <v>6748161</v>
+        <v>6748264</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3873,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543090</v>
+        <v>129543021</v>
       </c>
       <c r="B32" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3921,21 +3916,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3945,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457883</v>
+        <v>457756</v>
       </c>
       <c r="R32" t="n">
-        <v>6748264</v>
+        <v>6748192</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3980,7 +3975,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3985,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,7 +4012,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543021</v>
+        <v>129543063</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -4052,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457756</v>
+        <v>458116</v>
       </c>
       <c r="R33" t="n">
-        <v>6748192</v>
+        <v>6748548</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4087,7 +4082,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,7 +4092,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4117,7 +4112,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4224,17 +4219,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129542966</v>
+        <v>129542993</v>
       </c>
       <c r="B35" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,21 +4237,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4266,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457938</v>
+        <v>457763</v>
       </c>
       <c r="R35" t="n">
-        <v>6748466</v>
+        <v>6748294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4301,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4311,7 +4306,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4338,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543063</v>
+        <v>129543059</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4373,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458116</v>
+        <v>458174</v>
       </c>
       <c r="R36" t="n">
-        <v>6748548</v>
+        <v>6748599</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4408,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4418,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4438,17 +4433,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129543059</v>
+        <v>129542966</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4456,21 +4451,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4480,10 +4475,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458174</v>
+        <v>457938</v>
       </c>
       <c r="R37" t="n">
-        <v>6748599</v>
+        <v>6748466</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4515,7 +4510,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4525,7 +4520,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,52 +4540,57 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542993</v>
+        <v>129542949</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457763</v>
+        <v>457627</v>
       </c>
       <c r="R38" t="n">
-        <v>6748294</v>
+        <v>6748161</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4766,10 +4766,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543098</v>
+        <v>129542927</v>
       </c>
       <c r="B40" t="n">
-        <v>78747</v>
+        <v>57896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4777,34 +4777,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457657</v>
+        <v>458027</v>
       </c>
       <c r="R40" t="n">
-        <v>6748066</v>
+        <v>6748413</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4846,7 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4873,10 +4878,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543093</v>
+        <v>129542946</v>
       </c>
       <c r="B41" t="n">
-        <v>78747</v>
+        <v>91646</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4889,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4913,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457737</v>
+        <v>458035</v>
       </c>
       <c r="R41" t="n">
-        <v>6748103</v>
+        <v>6748395</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4953,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4980,32 +4985,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129542946</v>
+        <v>129543112</v>
       </c>
       <c r="B42" t="n">
-        <v>91646</v>
+        <v>91650</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>5321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5020,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458035</v>
+        <v>458029</v>
       </c>
       <c r="R42" t="n">
-        <v>6748395</v>
+        <v>6748411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5050,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5060,7 +5065,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5069,6 +5074,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5087,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543057</v>
+        <v>129543098</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5098,21 +5104,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5122,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>458134</v>
+        <v>457657</v>
       </c>
       <c r="R43" t="n">
-        <v>6748614</v>
+        <v>6748066</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5157,7 +5163,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5167,7 +5173,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5187,17 +5193,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543071</v>
+        <v>129543093</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5211,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5235,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457928</v>
+        <v>457737</v>
       </c>
       <c r="R44" t="n">
-        <v>6748344</v>
+        <v>6748103</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5264,7 +5270,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5280,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,14 +5300,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129542998</v>
+        <v>129543057</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5336,10 +5342,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457876</v>
+        <v>458134</v>
       </c>
       <c r="R45" t="n">
-        <v>6748240</v>
+        <v>6748614</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5371,7 +5377,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5381,7 +5387,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5401,39 +5407,39 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129543112</v>
+        <v>129543003</v>
       </c>
       <c r="B46" t="n">
-        <v>91650</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5443,10 +5449,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458029</v>
+        <v>457814</v>
       </c>
       <c r="R46" t="n">
-        <v>6748411</v>
+        <v>6748175</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5478,7 +5484,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5488,7 +5494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5497,7 +5503,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5516,7 +5521,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129543003</v>
+        <v>129542998</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5551,10 +5556,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457814</v>
+        <v>457876</v>
       </c>
       <c r="R47" t="n">
-        <v>6748175</v>
+        <v>6748240</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5586,7 +5591,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5596,7 +5601,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,17 +5621,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129542927</v>
+        <v>129543071</v>
       </c>
       <c r="B48" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5634,39 +5639,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>458027</v>
+        <v>457928</v>
       </c>
       <c r="R48" t="n">
-        <v>6748413</v>
+        <v>6748344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129543009</v>
+        <v>129543082</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457654</v>
+        <v>457792</v>
       </c>
       <c r="R49" t="n">
-        <v>6748079</v>
+        <v>6748260</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5835,14 +5835,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543078</v>
+        <v>129543010</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457875</v>
+        <v>457656</v>
       </c>
       <c r="R50" t="n">
-        <v>6748394</v>
+        <v>6748084</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@